--- a/src/spz/templates/export/spanisch.xlsx
+++ b/src/spz/templates/export/spanisch.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr updateLinks="never" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\04_Hiwi\Datenbank\excel_templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\urvdp\Documents\Datenbank\excel_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A1A22B3-AF8E-4D17-9E90-640F556CD3A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="RAWDATA" sheetId="11" r:id="rId1"/>
@@ -24,12 +23,12 @@
   </sheets>
   <definedNames>
     <definedName name="DOZENT">OFFSET(Einstellungen!$F$2,,,COUNTIF(Einstellungen!$F$2:$F$18,"&gt;"""),)</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">Extrapunkte!$A$1:$K$30</definedName>
     <definedName name="ECTS">OFFSET(Einstellungen!$H$2,,,COUNTIF(Einstellungen!$H$2:$H$18,"&gt;"""),)</definedName>
     <definedName name="KURSNAME">OFFSET(Einstellungen!$A$2,,,COUNTIF(Einstellungen!$A$2:$A$18,"&gt;"""),)</definedName>
     <definedName name="NIVEAU">OFFSET(Einstellungen!$D$2,,,COUNTIF(Einstellungen!$D$2:$D$20,"&gt;"""),)</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">Extrapunkte!$A$1:$K$30</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -50,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="132">
   <si>
     <t>Name</t>
   </si>
@@ -143,14 +142,6 @@
 nummer</t>
   </si>
   <si>
-    <t>Schein
-erhalten</t>
-  </si>
-  <si>
-    <t>Schein 
-erhalten</t>
-  </si>
-  <si>
     <t>NB</t>
   </si>
   <si>
@@ -160,14 +151,7 @@
     <t>Hoch-schule</t>
   </si>
   <si>
-    <t>Teilnahme-schein</t>
-  </si>
-  <si>
     <t>Prüfungs-schein</t>
-  </si>
-  <si>
-    <t>Teilnahme-
-schein</t>
   </si>
   <si>
     <t>Prüfungs-
@@ -525,7 +509,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -577,7 +561,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -610,12 +594,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -627,7 +605,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -750,17 +728,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -817,7 +784,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
@@ -902,18 +869,11 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1">
@@ -975,10 +935,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1017,30 +973,30 @@
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -1118,16 +1074,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Standard 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard 2" xfId="1"/>
   </cellStyles>
   <dxfs count="21">
     <dxf>
@@ -1223,7 +1173,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="de-DE"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1251,6 +1201,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1473,45 +1424,45 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DATA" displayName="DATA" ref="B1:L2" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
-  <autoFilter ref="B1:L2" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DATA" displayName="DATA" ref="B1:L2" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+  <autoFilter ref="B1:L2"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Nachname" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Vorname" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Hochschule" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Matrikelnummer" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Note" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="LP" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="E-Mail" dataDxfId="12"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Telefon" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="bestanden" dataDxfId="10"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Teilnahmeschein" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Schein erhalten" dataDxfId="8"/>
+    <tableColumn id="1" name="Nachname" dataDxfId="18"/>
+    <tableColumn id="2" name="Vorname" dataDxfId="17"/>
+    <tableColumn id="3" name="Hochschule" dataDxfId="16"/>
+    <tableColumn id="4" name="Matrikelnummer" dataDxfId="15"/>
+    <tableColumn id="7" name="Note" dataDxfId="14"/>
+    <tableColumn id="8" name="LP" dataDxfId="13"/>
+    <tableColumn id="5" name="E-Mail" dataDxfId="12"/>
+    <tableColumn id="10" name="Telefon" dataDxfId="11"/>
+    <tableColumn id="11" name="bestanden" dataDxfId="10"/>
+    <tableColumn id="9" name="Teilnahmeschein" dataDxfId="9"/>
+    <tableColumn id="6" name="Schein erhalten" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabelle1" displayName="Tabelle1" ref="A1:H26" totalsRowShown="0">
-  <autoFilter ref="A1:H26" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabelle1" displayName="Tabelle1" ref="A1:H26" totalsRowShown="0">
+  <autoFilter ref="A1:H26"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Matrikelnummer" dataDxfId="7" totalsRowDxfId="6">
+    <tableColumn id="1" name="Matrikelnummer" dataDxfId="7" totalsRowDxfId="6">
       <calculatedColumnFormula>IF(Notenliste!D2=0," ",Notenliste!D2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Status"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="LP" dataDxfId="5">
+    <tableColumn id="2" name="Status"/>
+    <tableColumn id="3" name="LP" dataDxfId="5">
       <calculatedColumnFormula>IF(Notenliste!D2&lt;&gt;0,IF(Notenliste!I2&lt;&gt;0,Notenliste!I2,Notenliste!$B$33)," ")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Note" dataDxfId="4" totalsRowDxfId="3">
+    <tableColumn id="4" name="Note" dataDxfId="4" totalsRowDxfId="3">
       <calculatedColumnFormula>IF(Notenliste!D2=0," ",IF(Notenliste!F2="KP"," ",IF(Notenliste!F2="NB","nicht bestanden",IF(OR(Notenliste!H2="x", Notenliste!H2="X"),"bestanden",Notenliste!F2))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Datum" dataDxfId="2">
+    <tableColumn id="5" name="Datum" dataDxfId="2">
       <calculatedColumnFormula>IF(Notenliste!D2&lt;&gt;0,Notenliste!$B$37," ")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Individueller Titel deutsch" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Individueller Titel englisch" dataDxfId="0"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Anmerkungen"/>
+    <tableColumn id="6" name="Individueller Titel deutsch" dataDxfId="1"/>
+    <tableColumn id="7" name="Individueller Titel englisch" dataDxfId="0"/>
+    <tableColumn id="8" name="Anmerkungen"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1803,307 +1754,307 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N26"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" zeroHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" style="39" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.44140625" style="39" customWidth="1"/>
-    <col min="3" max="3" width="26.109375" style="39" customWidth="1"/>
-    <col min="4" max="4" width="13.109375" style="39" customWidth="1"/>
-    <col min="5" max="5" width="17.6640625" style="40" customWidth="1"/>
-    <col min="6" max="7" width="7.109375" style="40" customWidth="1"/>
-    <col min="8" max="8" width="31.6640625" style="39" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="31.6640625" style="39" customWidth="1"/>
-    <col min="10" max="10" width="11.33203125" style="39" customWidth="1"/>
-    <col min="11" max="11" width="16.44140625" style="39" customWidth="1"/>
-    <col min="12" max="12" width="15" style="39" customWidth="1"/>
-    <col min="13" max="13" width="45.109375" style="39" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="9.44140625" style="39" hidden="1" customWidth="1"/>
-    <col min="15" max="16384" width="11.44140625" hidden="1"/>
+    <col min="1" max="1" width="3.7109375" style="37" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.42578125" style="37" customWidth="1"/>
+    <col min="3" max="3" width="26.140625" style="37" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" style="37" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" style="38" customWidth="1"/>
+    <col min="6" max="7" width="7.140625" style="38" customWidth="1"/>
+    <col min="8" max="8" width="31.7109375" style="37" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="31.7109375" style="37" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" style="37" customWidth="1"/>
+    <col min="11" max="11" width="16.42578125" style="37" customWidth="1"/>
+    <col min="12" max="12" width="15" style="37" customWidth="1"/>
+    <col min="13" max="13" width="45.140625" style="37" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="9.42578125" style="37" hidden="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.42578125" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" s="37" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="37" t="s">
+      <c r="B1" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="37" t="s">
+      <c r="C1" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="38" t="s">
+      <c r="E1" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="38" t="s">
+      <c r="F1" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="H1" s="37" t="s">
+      <c r="G1" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="37" t="s">
+      <c r="I1" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="J1" s="37" t="s">
-        <v>132</v>
-      </c>
-      <c r="K1" s="37" t="s">
+      <c r="J1" s="35" t="s">
         <v>128</v>
       </c>
-      <c r="L1" s="87" t="s">
-        <v>129</v>
-      </c>
-      <c r="M1" s="37" t="s">
+      <c r="K1" s="35" t="s">
+        <v>124</v>
+      </c>
+      <c r="L1" s="84" t="s">
+        <v>125</v>
+      </c>
+      <c r="M1" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="37" t="s">
+      <c r="N1" s="35" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="C2" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="D2" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="E2" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="F2" s="37" t="s">
+        <v>123</v>
+      </c>
+      <c r="G2" s="37" t="s">
+        <v>122</v>
+      </c>
+      <c r="H2" s="37" t="s">
         <v>100</v>
       </c>
-      <c r="C2" s="39" t="s">
+      <c r="I2" s="37" t="s">
         <v>101</v>
       </c>
-      <c r="D2" s="39" t="s">
-        <v>102</v>
-      </c>
-      <c r="E2" s="39" t="s">
-        <v>103</v>
-      </c>
-      <c r="F2" s="39" t="s">
+      <c r="J2" s="37" t="s">
+        <v>129</v>
+      </c>
+      <c r="K2" s="37" t="s">
+        <v>126</v>
+      </c>
+      <c r="L2" s="37" t="s">
         <v>127</v>
       </c>
-      <c r="G2" s="39" t="s">
-        <v>126</v>
-      </c>
-      <c r="H2" s="39" t="s">
-        <v>104</v>
-      </c>
-      <c r="I2" s="39" t="s">
-        <v>105</v>
-      </c>
-      <c r="J2" s="39" t="s">
-        <v>133</v>
-      </c>
-      <c r="K2" s="39" t="s">
-        <v>130</v>
-      </c>
-      <c r="L2" s="39" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="E4" s="39"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="39"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="37"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="39"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="39"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="37"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="37"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="E11" s="37"/>
+      <c r="F11" s="37"/>
+      <c r="G11" s="37"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="E12" s="41"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="41"/>
-      <c r="L12" s="41"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="L12" s="39"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
-      <c r="L13" s="41"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="39"/>
+      <c r="L13" s="39"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="E14" s="41"/>
-      <c r="F14" s="41"/>
-      <c r="G14" s="41"/>
-      <c r="L14" s="41"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="L14" s="39"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="L15" s="41"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="L15" s="39"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="E16" s="41"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
-      <c r="L16" s="41"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="L16" s="39"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="E17" s="41"/>
-      <c r="F17" s="41"/>
-      <c r="G17" s="41"/>
-      <c r="L17" s="41"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="L17" s="39"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="E18" s="41"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="41"/>
-      <c r="I18" s="41"/>
-      <c r="J18" s="41"/>
-      <c r="K18" s="41"/>
-      <c r="L18" s="41"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="39"/>
+      <c r="K18" s="39"/>
+      <c r="L18" s="39"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="41"/>
-      <c r="I19" s="41"/>
-      <c r="J19" s="41"/>
-      <c r="K19" s="41"/>
-      <c r="L19" s="41"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="39"/>
+      <c r="K19" s="39"/>
+      <c r="L19" s="39"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="E20" s="41"/>
-      <c r="F20" s="41"/>
-      <c r="G20" s="41"/>
-      <c r="H20" s="41"/>
-      <c r="I20" s="41"/>
-      <c r="J20" s="41"/>
-      <c r="K20" s="41"/>
-      <c r="L20" s="41"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="39"/>
+      <c r="K20" s="39"/>
+      <c r="L20" s="39"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="E21" s="41"/>
-      <c r="F21" s="41"/>
-      <c r="G21" s="41"/>
-      <c r="H21" s="41"/>
-      <c r="I21" s="41"/>
-      <c r="J21" s="41"/>
-      <c r="K21" s="41"/>
-      <c r="L21" s="41"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="39"/>
+      <c r="K21" s="39"/>
+      <c r="L21" s="39"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2123,552 +2074,549 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:WVY59"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="13.2" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="12.75" zeroHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.44140625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" style="3" customWidth="1"/>
     <col min="4" max="4" width="14" style="3" customWidth="1"/>
-    <col min="5" max="5" width="22.33203125" style="12" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="5.33203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="5.6640625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="5.6640625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="5.6640625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="5.6640625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="2.6640625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="3" style="1" customWidth="1"/>
-    <col min="15" max="15" width="6.44140625" style="1" hidden="1"/>
-    <col min="16" max="16" width="5.109375" style="1" hidden="1"/>
-    <col min="17" max="17" width="6.6640625" style="2" hidden="1"/>
-    <col min="18" max="18" width="17.6640625" style="1" hidden="1"/>
-    <col min="19" max="19" width="16" style="1" hidden="1"/>
-    <col min="20" max="20" width="17.6640625" style="1" hidden="1"/>
-    <col min="21" max="245" width="11.44140625" style="1" hidden="1"/>
-    <col min="246" max="246" width="15.44140625" style="1" hidden="1"/>
-    <col min="247" max="247" width="11.44140625" style="1" hidden="1"/>
-    <col min="248" max="248" width="15.6640625" style="1" hidden="1"/>
-    <col min="249" max="249" width="21.6640625" style="1" hidden="1"/>
-    <col min="250" max="252" width="11.44140625" style="1" hidden="1"/>
-    <col min="253" max="253" width="16" style="1" hidden="1"/>
-    <col min="254" max="254" width="20.44140625" style="1" hidden="1"/>
-    <col min="255" max="501" width="11.44140625" style="1" hidden="1"/>
-    <col min="502" max="502" width="15.44140625" style="1" hidden="1"/>
-    <col min="503" max="503" width="11.44140625" style="1" hidden="1"/>
-    <col min="504" max="504" width="15.6640625" style="1" hidden="1"/>
-    <col min="505" max="505" width="21.6640625" style="1" hidden="1"/>
-    <col min="506" max="508" width="11.44140625" style="1" hidden="1"/>
-    <col min="509" max="509" width="16" style="1" hidden="1"/>
-    <col min="510" max="510" width="20.44140625" style="1" hidden="1"/>
-    <col min="511" max="757" width="11.44140625" style="1" hidden="1"/>
-    <col min="758" max="758" width="15.44140625" style="1" hidden="1"/>
-    <col min="759" max="759" width="11.44140625" style="1" hidden="1"/>
-    <col min="760" max="760" width="15.6640625" style="1" hidden="1"/>
-    <col min="761" max="761" width="21.6640625" style="1" hidden="1"/>
-    <col min="762" max="764" width="11.44140625" style="1" hidden="1"/>
-    <col min="765" max="765" width="16" style="1" hidden="1"/>
-    <col min="766" max="766" width="20.44140625" style="1" hidden="1"/>
-    <col min="767" max="1013" width="11.44140625" style="1" hidden="1"/>
-    <col min="1014" max="1014" width="15.44140625" style="1" hidden="1"/>
-    <col min="1015" max="1015" width="11.44140625" style="1" hidden="1"/>
-    <col min="1016" max="1016" width="15.6640625" style="1" hidden="1"/>
-    <col min="1017" max="1017" width="21.6640625" style="1" hidden="1"/>
-    <col min="1018" max="1020" width="11.44140625" style="1" hidden="1"/>
-    <col min="1021" max="1021" width="16" style="1" hidden="1"/>
-    <col min="1022" max="1022" width="20.44140625" style="1" hidden="1"/>
-    <col min="1023" max="1269" width="11.44140625" style="1" hidden="1"/>
-    <col min="1270" max="1270" width="15.44140625" style="1" hidden="1"/>
-    <col min="1271" max="1271" width="11.44140625" style="1" hidden="1"/>
-    <col min="1272" max="1272" width="15.6640625" style="1" hidden="1"/>
-    <col min="1273" max="1273" width="21.6640625" style="1" hidden="1"/>
-    <col min="1274" max="1276" width="11.44140625" style="1" hidden="1"/>
-    <col min="1277" max="1277" width="16" style="1" hidden="1"/>
-    <col min="1278" max="1278" width="20.44140625" style="1" hidden="1"/>
-    <col min="1279" max="1525" width="11.44140625" style="1" hidden="1"/>
-    <col min="1526" max="1526" width="15.44140625" style="1" hidden="1"/>
-    <col min="1527" max="1527" width="11.44140625" style="1" hidden="1"/>
-    <col min="1528" max="1528" width="15.6640625" style="1" hidden="1"/>
-    <col min="1529" max="1529" width="21.6640625" style="1" hidden="1"/>
-    <col min="1530" max="1532" width="11.44140625" style="1" hidden="1"/>
-    <col min="1533" max="1533" width="16" style="1" hidden="1"/>
-    <col min="1534" max="1534" width="20.44140625" style="1" hidden="1"/>
-    <col min="1535" max="1781" width="11.44140625" style="1" hidden="1"/>
-    <col min="1782" max="1782" width="15.44140625" style="1" hidden="1"/>
-    <col min="1783" max="1783" width="11.44140625" style="1" hidden="1"/>
-    <col min="1784" max="1784" width="15.6640625" style="1" hidden="1"/>
-    <col min="1785" max="1785" width="21.6640625" style="1" hidden="1"/>
-    <col min="1786" max="1788" width="11.44140625" style="1" hidden="1"/>
-    <col min="1789" max="1789" width="16" style="1" hidden="1"/>
-    <col min="1790" max="1790" width="20.44140625" style="1" hidden="1"/>
-    <col min="1791" max="2037" width="11.44140625" style="1" hidden="1"/>
-    <col min="2038" max="2038" width="15.44140625" style="1" hidden="1"/>
-    <col min="2039" max="2039" width="11.44140625" style="1" hidden="1"/>
-    <col min="2040" max="2040" width="15.6640625" style="1" hidden="1"/>
-    <col min="2041" max="2041" width="21.6640625" style="1" hidden="1"/>
-    <col min="2042" max="2044" width="11.44140625" style="1" hidden="1"/>
-    <col min="2045" max="2045" width="16" style="1" hidden="1"/>
-    <col min="2046" max="2046" width="20.44140625" style="1" hidden="1"/>
-    <col min="2047" max="2293" width="11.44140625" style="1" hidden="1"/>
-    <col min="2294" max="2294" width="15.44140625" style="1" hidden="1"/>
-    <col min="2295" max="2295" width="11.44140625" style="1" hidden="1"/>
-    <col min="2296" max="2296" width="15.6640625" style="1" hidden="1"/>
-    <col min="2297" max="2297" width="21.6640625" style="1" hidden="1"/>
-    <col min="2298" max="2300" width="11.44140625" style="1" hidden="1"/>
-    <col min="2301" max="2301" width="16" style="1" hidden="1"/>
-    <col min="2302" max="2302" width="20.44140625" style="1" hidden="1"/>
-    <col min="2303" max="2549" width="11.44140625" style="1" hidden="1"/>
-    <col min="2550" max="2550" width="15.44140625" style="1" hidden="1"/>
-    <col min="2551" max="2551" width="11.44140625" style="1" hidden="1"/>
-    <col min="2552" max="2552" width="15.6640625" style="1" hidden="1"/>
-    <col min="2553" max="2553" width="21.6640625" style="1" hidden="1"/>
-    <col min="2554" max="2556" width="11.44140625" style="1" hidden="1"/>
-    <col min="2557" max="2557" width="16" style="1" hidden="1"/>
-    <col min="2558" max="2558" width="20.44140625" style="1" hidden="1"/>
-    <col min="2559" max="2805" width="11.44140625" style="1" hidden="1"/>
-    <col min="2806" max="2806" width="15.44140625" style="1" hidden="1"/>
-    <col min="2807" max="2807" width="11.44140625" style="1" hidden="1"/>
-    <col min="2808" max="2808" width="15.6640625" style="1" hidden="1"/>
-    <col min="2809" max="2809" width="21.6640625" style="1" hidden="1"/>
-    <col min="2810" max="2812" width="11.44140625" style="1" hidden="1"/>
-    <col min="2813" max="2813" width="16" style="1" hidden="1"/>
-    <col min="2814" max="2814" width="20.44140625" style="1" hidden="1"/>
-    <col min="2815" max="3061" width="11.44140625" style="1" hidden="1"/>
-    <col min="3062" max="3062" width="15.44140625" style="1" hidden="1"/>
-    <col min="3063" max="3063" width="11.44140625" style="1" hidden="1"/>
-    <col min="3064" max="3064" width="15.6640625" style="1" hidden="1"/>
-    <col min="3065" max="3065" width="21.6640625" style="1" hidden="1"/>
-    <col min="3066" max="3068" width="11.44140625" style="1" hidden="1"/>
-    <col min="3069" max="3069" width="16" style="1" hidden="1"/>
-    <col min="3070" max="3070" width="20.44140625" style="1" hidden="1"/>
-    <col min="3071" max="3317" width="11.44140625" style="1" hidden="1"/>
-    <col min="3318" max="3318" width="15.44140625" style="1" hidden="1"/>
-    <col min="3319" max="3319" width="11.44140625" style="1" hidden="1"/>
-    <col min="3320" max="3320" width="15.6640625" style="1" hidden="1"/>
-    <col min="3321" max="3321" width="21.6640625" style="1" hidden="1"/>
-    <col min="3322" max="3324" width="11.44140625" style="1" hidden="1"/>
-    <col min="3325" max="3325" width="16" style="1" hidden="1"/>
-    <col min="3326" max="3326" width="20.44140625" style="1" hidden="1"/>
-    <col min="3327" max="3573" width="11.44140625" style="1" hidden="1"/>
-    <col min="3574" max="3574" width="15.44140625" style="1" hidden="1"/>
-    <col min="3575" max="3575" width="11.44140625" style="1" hidden="1"/>
-    <col min="3576" max="3576" width="15.6640625" style="1" hidden="1"/>
-    <col min="3577" max="3577" width="21.6640625" style="1" hidden="1"/>
-    <col min="3578" max="3580" width="11.44140625" style="1" hidden="1"/>
-    <col min="3581" max="3581" width="16" style="1" hidden="1"/>
-    <col min="3582" max="3582" width="20.44140625" style="1" hidden="1"/>
-    <col min="3583" max="3829" width="11.44140625" style="1" hidden="1"/>
-    <col min="3830" max="3830" width="15.44140625" style="1" hidden="1"/>
-    <col min="3831" max="3831" width="11.44140625" style="1" hidden="1"/>
-    <col min="3832" max="3832" width="15.6640625" style="1" hidden="1"/>
-    <col min="3833" max="3833" width="21.6640625" style="1" hidden="1"/>
-    <col min="3834" max="3836" width="11.44140625" style="1" hidden="1"/>
-    <col min="3837" max="3837" width="16" style="1" hidden="1"/>
-    <col min="3838" max="3838" width="20.44140625" style="1" hidden="1"/>
-    <col min="3839" max="4085" width="11.44140625" style="1" hidden="1"/>
-    <col min="4086" max="4086" width="15.44140625" style="1" hidden="1"/>
-    <col min="4087" max="4087" width="11.44140625" style="1" hidden="1"/>
-    <col min="4088" max="4088" width="15.6640625" style="1" hidden="1"/>
-    <col min="4089" max="4089" width="21.6640625" style="1" hidden="1"/>
-    <col min="4090" max="4092" width="11.44140625" style="1" hidden="1"/>
-    <col min="4093" max="4093" width="16" style="1" hidden="1"/>
-    <col min="4094" max="4094" width="20.44140625" style="1" hidden="1"/>
-    <col min="4095" max="4341" width="11.44140625" style="1" hidden="1"/>
-    <col min="4342" max="4342" width="15.44140625" style="1" hidden="1"/>
-    <col min="4343" max="4343" width="11.44140625" style="1" hidden="1"/>
-    <col min="4344" max="4344" width="15.6640625" style="1" hidden="1"/>
-    <col min="4345" max="4345" width="21.6640625" style="1" hidden="1"/>
-    <col min="4346" max="4348" width="11.44140625" style="1" hidden="1"/>
-    <col min="4349" max="4349" width="16" style="1" hidden="1"/>
-    <col min="4350" max="4350" width="20.44140625" style="1" hidden="1"/>
-    <col min="4351" max="4597" width="11.44140625" style="1" hidden="1"/>
-    <col min="4598" max="4598" width="15.44140625" style="1" hidden="1"/>
-    <col min="4599" max="4599" width="11.44140625" style="1" hidden="1"/>
-    <col min="4600" max="4600" width="15.6640625" style="1" hidden="1"/>
-    <col min="4601" max="4601" width="21.6640625" style="1" hidden="1"/>
-    <col min="4602" max="4604" width="11.44140625" style="1" hidden="1"/>
-    <col min="4605" max="4605" width="16" style="1" hidden="1"/>
-    <col min="4606" max="4606" width="20.44140625" style="1" hidden="1"/>
-    <col min="4607" max="4853" width="11.44140625" style="1" hidden="1"/>
-    <col min="4854" max="4854" width="15.44140625" style="1" hidden="1"/>
-    <col min="4855" max="4855" width="11.44140625" style="1" hidden="1"/>
-    <col min="4856" max="4856" width="15.6640625" style="1" hidden="1"/>
-    <col min="4857" max="4857" width="21.6640625" style="1" hidden="1"/>
-    <col min="4858" max="4860" width="11.44140625" style="1" hidden="1"/>
-    <col min="4861" max="4861" width="16" style="1" hidden="1"/>
-    <col min="4862" max="4862" width="20.44140625" style="1" hidden="1"/>
-    <col min="4863" max="5109" width="11.44140625" style="1" hidden="1"/>
-    <col min="5110" max="5110" width="15.44140625" style="1" hidden="1"/>
-    <col min="5111" max="5111" width="11.44140625" style="1" hidden="1"/>
-    <col min="5112" max="5112" width="15.6640625" style="1" hidden="1"/>
-    <col min="5113" max="5113" width="21.6640625" style="1" hidden="1"/>
-    <col min="5114" max="5116" width="11.44140625" style="1" hidden="1"/>
-    <col min="5117" max="5117" width="16" style="1" hidden="1"/>
-    <col min="5118" max="5118" width="20.44140625" style="1" hidden="1"/>
-    <col min="5119" max="5365" width="11.44140625" style="1" hidden="1"/>
-    <col min="5366" max="5366" width="15.44140625" style="1" hidden="1"/>
-    <col min="5367" max="5367" width="11.44140625" style="1" hidden="1"/>
-    <col min="5368" max="5368" width="15.6640625" style="1" hidden="1"/>
-    <col min="5369" max="5369" width="21.6640625" style="1" hidden="1"/>
-    <col min="5370" max="5372" width="11.44140625" style="1" hidden="1"/>
-    <col min="5373" max="5373" width="16" style="1" hidden="1"/>
-    <col min="5374" max="5374" width="20.44140625" style="1" hidden="1"/>
-    <col min="5375" max="5621" width="11.44140625" style="1" hidden="1"/>
-    <col min="5622" max="5622" width="15.44140625" style="1" hidden="1"/>
-    <col min="5623" max="5623" width="11.44140625" style="1" hidden="1"/>
-    <col min="5624" max="5624" width="15.6640625" style="1" hidden="1"/>
-    <col min="5625" max="5625" width="21.6640625" style="1" hidden="1"/>
-    <col min="5626" max="5628" width="11.44140625" style="1" hidden="1"/>
-    <col min="5629" max="5629" width="16" style="1" hidden="1"/>
-    <col min="5630" max="5630" width="20.44140625" style="1" hidden="1"/>
-    <col min="5631" max="5877" width="11.44140625" style="1" hidden="1"/>
-    <col min="5878" max="5878" width="15.44140625" style="1" hidden="1"/>
-    <col min="5879" max="5879" width="11.44140625" style="1" hidden="1"/>
-    <col min="5880" max="5880" width="15.6640625" style="1" hidden="1"/>
-    <col min="5881" max="5881" width="21.6640625" style="1" hidden="1"/>
-    <col min="5882" max="5884" width="11.44140625" style="1" hidden="1"/>
-    <col min="5885" max="5885" width="16" style="1" hidden="1"/>
-    <col min="5886" max="5886" width="20.44140625" style="1" hidden="1"/>
-    <col min="5887" max="6133" width="11.44140625" style="1" hidden="1"/>
-    <col min="6134" max="6134" width="15.44140625" style="1" hidden="1"/>
-    <col min="6135" max="6135" width="11.44140625" style="1" hidden="1"/>
-    <col min="6136" max="6136" width="15.6640625" style="1" hidden="1"/>
-    <col min="6137" max="6137" width="21.6640625" style="1" hidden="1"/>
-    <col min="6138" max="6140" width="11.44140625" style="1" hidden="1"/>
-    <col min="6141" max="6141" width="16" style="1" hidden="1"/>
-    <col min="6142" max="6142" width="20.44140625" style="1" hidden="1"/>
-    <col min="6143" max="6389" width="11.44140625" style="1" hidden="1"/>
-    <col min="6390" max="6390" width="15.44140625" style="1" hidden="1"/>
-    <col min="6391" max="6391" width="11.44140625" style="1" hidden="1"/>
-    <col min="6392" max="6392" width="15.6640625" style="1" hidden="1"/>
-    <col min="6393" max="6393" width="21.6640625" style="1" hidden="1"/>
-    <col min="6394" max="6396" width="11.44140625" style="1" hidden="1"/>
-    <col min="6397" max="6397" width="16" style="1" hidden="1"/>
-    <col min="6398" max="6398" width="20.44140625" style="1" hidden="1"/>
-    <col min="6399" max="6645" width="11.44140625" style="1" hidden="1"/>
-    <col min="6646" max="6646" width="15.44140625" style="1" hidden="1"/>
-    <col min="6647" max="6647" width="11.44140625" style="1" hidden="1"/>
-    <col min="6648" max="6648" width="15.6640625" style="1" hidden="1"/>
-    <col min="6649" max="6649" width="21.6640625" style="1" hidden="1"/>
-    <col min="6650" max="6652" width="11.44140625" style="1" hidden="1"/>
-    <col min="6653" max="6653" width="16" style="1" hidden="1"/>
-    <col min="6654" max="6654" width="20.44140625" style="1" hidden="1"/>
-    <col min="6655" max="6901" width="11.44140625" style="1" hidden="1"/>
-    <col min="6902" max="6902" width="15.44140625" style="1" hidden="1"/>
-    <col min="6903" max="6903" width="11.44140625" style="1" hidden="1"/>
-    <col min="6904" max="6904" width="15.6640625" style="1" hidden="1"/>
-    <col min="6905" max="6905" width="21.6640625" style="1" hidden="1"/>
-    <col min="6906" max="6908" width="11.44140625" style="1" hidden="1"/>
-    <col min="6909" max="6909" width="16" style="1" hidden="1"/>
-    <col min="6910" max="6910" width="20.44140625" style="1" hidden="1"/>
-    <col min="6911" max="7157" width="11.44140625" style="1" hidden="1"/>
-    <col min="7158" max="7158" width="15.44140625" style="1" hidden="1"/>
-    <col min="7159" max="7159" width="11.44140625" style="1" hidden="1"/>
-    <col min="7160" max="7160" width="15.6640625" style="1" hidden="1"/>
-    <col min="7161" max="7161" width="21.6640625" style="1" hidden="1"/>
-    <col min="7162" max="7164" width="11.44140625" style="1" hidden="1"/>
-    <col min="7165" max="7165" width="16" style="1" hidden="1"/>
-    <col min="7166" max="7166" width="20.44140625" style="1" hidden="1"/>
-    <col min="7167" max="7413" width="11.44140625" style="1" hidden="1"/>
-    <col min="7414" max="7414" width="15.44140625" style="1" hidden="1"/>
-    <col min="7415" max="7415" width="11.44140625" style="1" hidden="1"/>
-    <col min="7416" max="7416" width="15.6640625" style="1" hidden="1"/>
-    <col min="7417" max="7417" width="21.6640625" style="1" hidden="1"/>
-    <col min="7418" max="7420" width="11.44140625" style="1" hidden="1"/>
-    <col min="7421" max="7421" width="16" style="1" hidden="1"/>
-    <col min="7422" max="7422" width="20.44140625" style="1" hidden="1"/>
-    <col min="7423" max="7669" width="11.44140625" style="1" hidden="1"/>
-    <col min="7670" max="7670" width="15.44140625" style="1" hidden="1"/>
-    <col min="7671" max="7671" width="11.44140625" style="1" hidden="1"/>
-    <col min="7672" max="7672" width="15.6640625" style="1" hidden="1"/>
-    <col min="7673" max="7673" width="21.6640625" style="1" hidden="1"/>
-    <col min="7674" max="7676" width="11.44140625" style="1" hidden="1"/>
-    <col min="7677" max="7677" width="16" style="1" hidden="1"/>
-    <col min="7678" max="7678" width="20.44140625" style="1" hidden="1"/>
-    <col min="7679" max="7925" width="11.44140625" style="1" hidden="1"/>
-    <col min="7926" max="7926" width="15.44140625" style="1" hidden="1"/>
-    <col min="7927" max="7927" width="11.44140625" style="1" hidden="1"/>
-    <col min="7928" max="7928" width="15.6640625" style="1" hidden="1"/>
-    <col min="7929" max="7929" width="21.6640625" style="1" hidden="1"/>
-    <col min="7930" max="7932" width="11.44140625" style="1" hidden="1"/>
-    <col min="7933" max="7933" width="16" style="1" hidden="1"/>
-    <col min="7934" max="7934" width="20.44140625" style="1" hidden="1"/>
-    <col min="7935" max="8181" width="11.44140625" style="1" hidden="1"/>
-    <col min="8182" max="8182" width="15.44140625" style="1" hidden="1"/>
-    <col min="8183" max="8183" width="11.44140625" style="1" hidden="1"/>
-    <col min="8184" max="8184" width="15.6640625" style="1" hidden="1"/>
-    <col min="8185" max="8185" width="21.6640625" style="1" hidden="1"/>
-    <col min="8186" max="8188" width="11.44140625" style="1" hidden="1"/>
-    <col min="8189" max="8189" width="16" style="1" hidden="1"/>
-    <col min="8190" max="8190" width="20.44140625" style="1" hidden="1"/>
-    <col min="8191" max="8437" width="11.44140625" style="1" hidden="1"/>
-    <col min="8438" max="8438" width="15.44140625" style="1" hidden="1"/>
-    <col min="8439" max="8439" width="11.44140625" style="1" hidden="1"/>
-    <col min="8440" max="8440" width="15.6640625" style="1" hidden="1"/>
-    <col min="8441" max="8441" width="21.6640625" style="1" hidden="1"/>
-    <col min="8442" max="8444" width="11.44140625" style="1" hidden="1"/>
-    <col min="8445" max="8445" width="16" style="1" hidden="1"/>
-    <col min="8446" max="8446" width="20.44140625" style="1" hidden="1"/>
-    <col min="8447" max="8693" width="11.44140625" style="1" hidden="1"/>
-    <col min="8694" max="8694" width="15.44140625" style="1" hidden="1"/>
-    <col min="8695" max="8695" width="11.44140625" style="1" hidden="1"/>
-    <col min="8696" max="8696" width="15.6640625" style="1" hidden="1"/>
-    <col min="8697" max="8697" width="21.6640625" style="1" hidden="1"/>
-    <col min="8698" max="8700" width="11.44140625" style="1" hidden="1"/>
-    <col min="8701" max="8701" width="16" style="1" hidden="1"/>
-    <col min="8702" max="8702" width="20.44140625" style="1" hidden="1"/>
-    <col min="8703" max="8949" width="11.44140625" style="1" hidden="1"/>
-    <col min="8950" max="8950" width="15.44140625" style="1" hidden="1"/>
-    <col min="8951" max="8951" width="11.44140625" style="1" hidden="1"/>
-    <col min="8952" max="8952" width="15.6640625" style="1" hidden="1"/>
-    <col min="8953" max="8953" width="21.6640625" style="1" hidden="1"/>
-    <col min="8954" max="8956" width="11.44140625" style="1" hidden="1"/>
-    <col min="8957" max="8957" width="16" style="1" hidden="1"/>
-    <col min="8958" max="8958" width="20.44140625" style="1" hidden="1"/>
-    <col min="8959" max="9205" width="11.44140625" style="1" hidden="1"/>
-    <col min="9206" max="9206" width="15.44140625" style="1" hidden="1"/>
-    <col min="9207" max="9207" width="11.44140625" style="1" hidden="1"/>
-    <col min="9208" max="9208" width="15.6640625" style="1" hidden="1"/>
-    <col min="9209" max="9209" width="21.6640625" style="1" hidden="1"/>
-    <col min="9210" max="9212" width="11.44140625" style="1" hidden="1"/>
-    <col min="9213" max="9213" width="16" style="1" hidden="1"/>
-    <col min="9214" max="9214" width="20.44140625" style="1" hidden="1"/>
-    <col min="9215" max="9461" width="11.44140625" style="1" hidden="1"/>
-    <col min="9462" max="9462" width="15.44140625" style="1" hidden="1"/>
-    <col min="9463" max="9463" width="11.44140625" style="1" hidden="1"/>
-    <col min="9464" max="9464" width="15.6640625" style="1" hidden="1"/>
-    <col min="9465" max="9465" width="21.6640625" style="1" hidden="1"/>
-    <col min="9466" max="9468" width="11.44140625" style="1" hidden="1"/>
-    <col min="9469" max="9469" width="16" style="1" hidden="1"/>
-    <col min="9470" max="9470" width="20.44140625" style="1" hidden="1"/>
-    <col min="9471" max="9717" width="11.44140625" style="1" hidden="1"/>
-    <col min="9718" max="9718" width="15.44140625" style="1" hidden="1"/>
-    <col min="9719" max="9719" width="11.44140625" style="1" hidden="1"/>
-    <col min="9720" max="9720" width="15.6640625" style="1" hidden="1"/>
-    <col min="9721" max="9721" width="21.6640625" style="1" hidden="1"/>
-    <col min="9722" max="9724" width="11.44140625" style="1" hidden="1"/>
-    <col min="9725" max="9725" width="16" style="1" hidden="1"/>
-    <col min="9726" max="9726" width="20.44140625" style="1" hidden="1"/>
-    <col min="9727" max="9973" width="11.44140625" style="1" hidden="1"/>
-    <col min="9974" max="9974" width="15.44140625" style="1" hidden="1"/>
-    <col min="9975" max="9975" width="11.44140625" style="1" hidden="1"/>
-    <col min="9976" max="9976" width="15.6640625" style="1" hidden="1"/>
-    <col min="9977" max="9977" width="21.6640625" style="1" hidden="1"/>
-    <col min="9978" max="9980" width="11.44140625" style="1" hidden="1"/>
-    <col min="9981" max="9981" width="16" style="1" hidden="1"/>
-    <col min="9982" max="9982" width="20.44140625" style="1" hidden="1"/>
-    <col min="9983" max="10229" width="11.44140625" style="1" hidden="1"/>
-    <col min="10230" max="10230" width="15.44140625" style="1" hidden="1"/>
-    <col min="10231" max="10231" width="11.44140625" style="1" hidden="1"/>
-    <col min="10232" max="10232" width="15.6640625" style="1" hidden="1"/>
-    <col min="10233" max="10233" width="21.6640625" style="1" hidden="1"/>
-    <col min="10234" max="10236" width="11.44140625" style="1" hidden="1"/>
-    <col min="10237" max="10237" width="16" style="1" hidden="1"/>
-    <col min="10238" max="10238" width="20.44140625" style="1" hidden="1"/>
-    <col min="10239" max="10485" width="11.44140625" style="1" hidden="1"/>
-    <col min="10486" max="10486" width="15.44140625" style="1" hidden="1"/>
-    <col min="10487" max="10487" width="11.44140625" style="1" hidden="1"/>
-    <col min="10488" max="10488" width="15.6640625" style="1" hidden="1"/>
-    <col min="10489" max="10489" width="21.6640625" style="1" hidden="1"/>
-    <col min="10490" max="10492" width="11.44140625" style="1" hidden="1"/>
-    <col min="10493" max="10493" width="16" style="1" hidden="1"/>
-    <col min="10494" max="10494" width="20.44140625" style="1" hidden="1"/>
-    <col min="10495" max="10741" width="11.44140625" style="1" hidden="1"/>
-    <col min="10742" max="10742" width="15.44140625" style="1" hidden="1"/>
-    <col min="10743" max="10743" width="11.44140625" style="1" hidden="1"/>
-    <col min="10744" max="10744" width="15.6640625" style="1" hidden="1"/>
-    <col min="10745" max="10745" width="21.6640625" style="1" hidden="1"/>
-    <col min="10746" max="10748" width="11.44140625" style="1" hidden="1"/>
-    <col min="10749" max="10749" width="16" style="1" hidden="1"/>
-    <col min="10750" max="10750" width="20.44140625" style="1" hidden="1"/>
-    <col min="10751" max="10997" width="11.44140625" style="1" hidden="1"/>
-    <col min="10998" max="10998" width="15.44140625" style="1" hidden="1"/>
-    <col min="10999" max="10999" width="11.44140625" style="1" hidden="1"/>
-    <col min="11000" max="11000" width="15.6640625" style="1" hidden="1"/>
-    <col min="11001" max="11001" width="21.6640625" style="1" hidden="1"/>
-    <col min="11002" max="11004" width="11.44140625" style="1" hidden="1"/>
-    <col min="11005" max="11005" width="16" style="1" hidden="1"/>
-    <col min="11006" max="11006" width="20.44140625" style="1" hidden="1"/>
-    <col min="11007" max="11253" width="11.44140625" style="1" hidden="1"/>
-    <col min="11254" max="11254" width="15.44140625" style="1" hidden="1"/>
-    <col min="11255" max="11255" width="11.44140625" style="1" hidden="1"/>
-    <col min="11256" max="11256" width="15.6640625" style="1" hidden="1"/>
-    <col min="11257" max="11257" width="21.6640625" style="1" hidden="1"/>
-    <col min="11258" max="11260" width="11.44140625" style="1" hidden="1"/>
-    <col min="11261" max="11261" width="16" style="1" hidden="1"/>
-    <col min="11262" max="11262" width="20.44140625" style="1" hidden="1"/>
-    <col min="11263" max="11509" width="11.44140625" style="1" hidden="1"/>
-    <col min="11510" max="11510" width="15.44140625" style="1" hidden="1"/>
-    <col min="11511" max="11511" width="11.44140625" style="1" hidden="1"/>
-    <col min="11512" max="11512" width="15.6640625" style="1" hidden="1"/>
-    <col min="11513" max="11513" width="21.6640625" style="1" hidden="1"/>
-    <col min="11514" max="11516" width="11.44140625" style="1" hidden="1"/>
-    <col min="11517" max="11517" width="16" style="1" hidden="1"/>
-    <col min="11518" max="11518" width="20.44140625" style="1" hidden="1"/>
-    <col min="11519" max="11765" width="11.44140625" style="1" hidden="1"/>
-    <col min="11766" max="11766" width="15.44140625" style="1" hidden="1"/>
-    <col min="11767" max="11767" width="11.44140625" style="1" hidden="1"/>
-    <col min="11768" max="11768" width="15.6640625" style="1" hidden="1"/>
-    <col min="11769" max="11769" width="21.6640625" style="1" hidden="1"/>
-    <col min="11770" max="11772" width="11.44140625" style="1" hidden="1"/>
-    <col min="11773" max="11773" width="16" style="1" hidden="1"/>
-    <col min="11774" max="11774" width="20.44140625" style="1" hidden="1"/>
-    <col min="11775" max="12021" width="11.44140625" style="1" hidden="1"/>
-    <col min="12022" max="12022" width="15.44140625" style="1" hidden="1"/>
-    <col min="12023" max="12023" width="11.44140625" style="1" hidden="1"/>
-    <col min="12024" max="12024" width="15.6640625" style="1" hidden="1"/>
-    <col min="12025" max="12025" width="21.6640625" style="1" hidden="1"/>
-    <col min="12026" max="12028" width="11.44140625" style="1" hidden="1"/>
-    <col min="12029" max="12029" width="16" style="1" hidden="1"/>
-    <col min="12030" max="12030" width="20.44140625" style="1" hidden="1"/>
-    <col min="12031" max="12277" width="11.44140625" style="1" hidden="1"/>
-    <col min="12278" max="12278" width="15.44140625" style="1" hidden="1"/>
-    <col min="12279" max="12279" width="11.44140625" style="1" hidden="1"/>
-    <col min="12280" max="12280" width="15.6640625" style="1" hidden="1"/>
-    <col min="12281" max="12281" width="21.6640625" style="1" hidden="1"/>
-    <col min="12282" max="12284" width="11.44140625" style="1" hidden="1"/>
-    <col min="12285" max="12285" width="16" style="1" hidden="1"/>
-    <col min="12286" max="12286" width="20.44140625" style="1" hidden="1"/>
-    <col min="12287" max="12533" width="11.44140625" style="1" hidden="1"/>
-    <col min="12534" max="12534" width="15.44140625" style="1" hidden="1"/>
-    <col min="12535" max="12535" width="11.44140625" style="1" hidden="1"/>
-    <col min="12536" max="12536" width="15.6640625" style="1" hidden="1"/>
-    <col min="12537" max="12537" width="21.6640625" style="1" hidden="1"/>
-    <col min="12538" max="12540" width="11.44140625" style="1" hidden="1"/>
-    <col min="12541" max="12541" width="16" style="1" hidden="1"/>
-    <col min="12542" max="12542" width="20.44140625" style="1" hidden="1"/>
-    <col min="12543" max="12789" width="11.44140625" style="1" hidden="1"/>
-    <col min="12790" max="12790" width="15.44140625" style="1" hidden="1"/>
-    <col min="12791" max="12791" width="11.44140625" style="1" hidden="1"/>
-    <col min="12792" max="12792" width="15.6640625" style="1" hidden="1"/>
-    <col min="12793" max="12793" width="21.6640625" style="1" hidden="1"/>
-    <col min="12794" max="12796" width="11.44140625" style="1" hidden="1"/>
-    <col min="12797" max="12797" width="16" style="1" hidden="1"/>
-    <col min="12798" max="12798" width="20.44140625" style="1" hidden="1"/>
-    <col min="12799" max="13045" width="11.44140625" style="1" hidden="1"/>
-    <col min="13046" max="13046" width="15.44140625" style="1" hidden="1"/>
-    <col min="13047" max="13047" width="11.44140625" style="1" hidden="1"/>
-    <col min="13048" max="13048" width="15.6640625" style="1" hidden="1"/>
-    <col min="13049" max="13049" width="21.6640625" style="1" hidden="1"/>
-    <col min="13050" max="13052" width="11.44140625" style="1" hidden="1"/>
-    <col min="13053" max="13053" width="16" style="1" hidden="1"/>
-    <col min="13054" max="13054" width="20.44140625" style="1" hidden="1"/>
-    <col min="13055" max="13301" width="11.44140625" style="1" hidden="1"/>
-    <col min="13302" max="13302" width="15.44140625" style="1" hidden="1"/>
-    <col min="13303" max="13303" width="11.44140625" style="1" hidden="1"/>
-    <col min="13304" max="13304" width="15.6640625" style="1" hidden="1"/>
-    <col min="13305" max="13305" width="21.6640625" style="1" hidden="1"/>
-    <col min="13306" max="13308" width="11.44140625" style="1" hidden="1"/>
-    <col min="13309" max="13309" width="16" style="1" hidden="1"/>
-    <col min="13310" max="13310" width="20.44140625" style="1" hidden="1"/>
-    <col min="13311" max="13557" width="11.44140625" style="1" hidden="1"/>
-    <col min="13558" max="13558" width="15.44140625" style="1" hidden="1"/>
-    <col min="13559" max="13559" width="11.44140625" style="1" hidden="1"/>
-    <col min="13560" max="13560" width="15.6640625" style="1" hidden="1"/>
-    <col min="13561" max="13561" width="21.6640625" style="1" hidden="1"/>
-    <col min="13562" max="13564" width="11.44140625" style="1" hidden="1"/>
-    <col min="13565" max="13565" width="16" style="1" hidden="1"/>
-    <col min="13566" max="13566" width="20.44140625" style="1" hidden="1"/>
-    <col min="13567" max="13813" width="11.44140625" style="1" hidden="1"/>
-    <col min="13814" max="13814" width="15.44140625" style="1" hidden="1"/>
-    <col min="13815" max="13815" width="11.44140625" style="1" hidden="1"/>
-    <col min="13816" max="13816" width="15.6640625" style="1" hidden="1"/>
-    <col min="13817" max="13817" width="21.6640625" style="1" hidden="1"/>
-    <col min="13818" max="13820" width="11.44140625" style="1" hidden="1"/>
-    <col min="13821" max="13821" width="16" style="1" hidden="1"/>
-    <col min="13822" max="13822" width="20.44140625" style="1" hidden="1"/>
-    <col min="13823" max="14069" width="11.44140625" style="1" hidden="1"/>
-    <col min="14070" max="14070" width="15.44140625" style="1" hidden="1"/>
-    <col min="14071" max="14071" width="11.44140625" style="1" hidden="1"/>
-    <col min="14072" max="14072" width="15.6640625" style="1" hidden="1"/>
-    <col min="14073" max="14073" width="21.6640625" style="1" hidden="1"/>
-    <col min="14074" max="14076" width="11.44140625" style="1" hidden="1"/>
-    <col min="14077" max="14077" width="16" style="1" hidden="1"/>
-    <col min="14078" max="14078" width="20.44140625" style="1" hidden="1"/>
-    <col min="14079" max="14325" width="11.44140625" style="1" hidden="1"/>
-    <col min="14326" max="14326" width="15.44140625" style="1" hidden="1"/>
-    <col min="14327" max="14327" width="11.44140625" style="1" hidden="1"/>
-    <col min="14328" max="14328" width="15.6640625" style="1" hidden="1"/>
-    <col min="14329" max="14329" width="21.6640625" style="1" hidden="1"/>
-    <col min="14330" max="14332" width="11.44140625" style="1" hidden="1"/>
-    <col min="14333" max="14333" width="16" style="1" hidden="1"/>
-    <col min="14334" max="14334" width="20.44140625" style="1" hidden="1"/>
-    <col min="14335" max="14581" width="11.44140625" style="1" hidden="1"/>
-    <col min="14582" max="14582" width="15.44140625" style="1" hidden="1"/>
-    <col min="14583" max="14583" width="11.44140625" style="1" hidden="1"/>
-    <col min="14584" max="14584" width="15.6640625" style="1" hidden="1"/>
-    <col min="14585" max="14585" width="21.6640625" style="1" hidden="1"/>
-    <col min="14586" max="14588" width="11.44140625" style="1" hidden="1"/>
-    <col min="14589" max="14589" width="16" style="1" hidden="1"/>
-    <col min="14590" max="14590" width="20.44140625" style="1" hidden="1"/>
-    <col min="14591" max="14837" width="11.44140625" style="1" hidden="1"/>
-    <col min="14838" max="14838" width="15.44140625" style="1" hidden="1"/>
-    <col min="14839" max="14839" width="11.44140625" style="1" hidden="1"/>
-    <col min="14840" max="14840" width="15.6640625" style="1" hidden="1"/>
-    <col min="14841" max="14841" width="21.6640625" style="1" hidden="1"/>
-    <col min="14842" max="14844" width="11.44140625" style="1" hidden="1"/>
-    <col min="14845" max="14845" width="16" style="1" hidden="1"/>
-    <col min="14846" max="14846" width="20.44140625" style="1" hidden="1"/>
-    <col min="14847" max="15093" width="11.44140625" style="1" hidden="1"/>
-    <col min="15094" max="15094" width="15.44140625" style="1" hidden="1"/>
-    <col min="15095" max="15095" width="11.44140625" style="1" hidden="1"/>
-    <col min="15096" max="15096" width="15.6640625" style="1" hidden="1"/>
-    <col min="15097" max="15097" width="21.6640625" style="1" hidden="1"/>
-    <col min="15098" max="15100" width="11.44140625" style="1" hidden="1"/>
-    <col min="15101" max="15101" width="16" style="1" hidden="1"/>
-    <col min="15102" max="15102" width="20.44140625" style="1" hidden="1"/>
-    <col min="15103" max="15349" width="11.44140625" style="1" hidden="1"/>
-    <col min="15350" max="15350" width="15.44140625" style="1" hidden="1"/>
-    <col min="15351" max="15351" width="11.44140625" style="1" hidden="1"/>
-    <col min="15352" max="15352" width="15.6640625" style="1" hidden="1"/>
-    <col min="15353" max="15353" width="21.6640625" style="1" hidden="1"/>
-    <col min="15354" max="15356" width="11.44140625" style="1" hidden="1"/>
-    <col min="15357" max="15357" width="16" style="1" hidden="1"/>
-    <col min="15358" max="15358" width="20.44140625" style="1" hidden="1"/>
-    <col min="15359" max="15605" width="11.44140625" style="1" hidden="1"/>
-    <col min="15606" max="15606" width="15.44140625" style="1" hidden="1"/>
-    <col min="15607" max="15607" width="11.44140625" style="1" hidden="1"/>
-    <col min="15608" max="15608" width="15.6640625" style="1" hidden="1"/>
-    <col min="15609" max="15609" width="21.6640625" style="1" hidden="1"/>
-    <col min="15610" max="15612" width="11.44140625" style="1" hidden="1"/>
-    <col min="15613" max="15613" width="16" style="1" hidden="1"/>
-    <col min="15614" max="15614" width="20.44140625" style="1" hidden="1"/>
-    <col min="15615" max="15861" width="11.44140625" style="1" hidden="1"/>
-    <col min="15862" max="15862" width="15.44140625" style="1" hidden="1"/>
-    <col min="15863" max="15863" width="11.44140625" style="1" hidden="1"/>
-    <col min="15864" max="15864" width="15.6640625" style="1" hidden="1"/>
-    <col min="15865" max="15865" width="21.6640625" style="1" hidden="1"/>
-    <col min="15866" max="15868" width="11.44140625" style="1" hidden="1"/>
-    <col min="15869" max="15869" width="16" style="1" hidden="1"/>
-    <col min="15870" max="15870" width="20.44140625" style="1" hidden="1"/>
-    <col min="15871" max="16117" width="11.44140625" style="1" hidden="1"/>
-    <col min="16118" max="16118" width="15.44140625" style="1" hidden="1"/>
-    <col min="16119" max="16119" width="11.44140625" style="1" hidden="1"/>
-    <col min="16120" max="16120" width="15.6640625" style="1" hidden="1"/>
-    <col min="16121" max="16121" width="21.6640625" style="1" hidden="1"/>
-    <col min="16122" max="16124" width="11.44140625" style="1" hidden="1"/>
-    <col min="16125" max="16125" width="16" style="1" hidden="1"/>
-    <col min="16126" max="16126" width="20.44140625" style="1" hidden="1"/>
-    <col min="16127" max="16129" width="11.44140625" style="1" hidden="1"/>
-    <col min="16130" max="16130" width="15.44140625" style="1" hidden="1"/>
-    <col min="16131" max="16131" width="11.44140625" style="1" hidden="1"/>
-    <col min="16132" max="16132" width="15.6640625" style="1" hidden="1"/>
-    <col min="16133" max="16133" width="21.6640625" style="1" hidden="1"/>
-    <col min="16134" max="16136" width="11.44140625" style="1" hidden="1"/>
-    <col min="16137" max="16137" width="16" style="1" hidden="1"/>
-    <col min="16138" max="16139" width="20.44140625" style="1" hidden="1"/>
-    <col min="16140" max="16141" width="11.44140625" style="1" hidden="1"/>
-    <col min="16142" max="16142" width="16" style="1" hidden="1"/>
-    <col min="16143" max="16145" width="20.44140625" style="1" hidden="1"/>
-    <col min="16146" max="16384" width="11.44140625" style="1" hidden="1"/>
+    <col min="5" max="5" width="22.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="2.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="5.28515625" style="1" customWidth="1"/>
+    <col min="9" max="10" width="5.7109375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="2.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="3" style="1" customWidth="1"/>
+    <col min="13" max="13" width="6.42578125" style="1" hidden="1"/>
+    <col min="14" max="14" width="5.140625" style="1" hidden="1"/>
+    <col min="15" max="15" width="6.7109375" style="2" hidden="1"/>
+    <col min="16" max="16" width="17.7109375" style="1" hidden="1"/>
+    <col min="17" max="17" width="16" style="1" hidden="1"/>
+    <col min="18" max="18" width="17.7109375" style="1" hidden="1"/>
+    <col min="19" max="243" width="11.42578125" style="1" hidden="1"/>
+    <col min="244" max="244" width="15.42578125" style="1" hidden="1"/>
+    <col min="245" max="245" width="11.42578125" style="1" hidden="1"/>
+    <col min="246" max="246" width="15.7109375" style="1" hidden="1"/>
+    <col min="247" max="247" width="21.7109375" style="1" hidden="1"/>
+    <col min="248" max="250" width="11.42578125" style="1" hidden="1"/>
+    <col min="251" max="251" width="16" style="1" hidden="1"/>
+    <col min="252" max="252" width="20.42578125" style="1" hidden="1"/>
+    <col min="253" max="499" width="11.42578125" style="1" hidden="1"/>
+    <col min="500" max="500" width="15.42578125" style="1" hidden="1"/>
+    <col min="501" max="501" width="11.42578125" style="1" hidden="1"/>
+    <col min="502" max="502" width="15.7109375" style="1" hidden="1"/>
+    <col min="503" max="503" width="21.7109375" style="1" hidden="1"/>
+    <col min="504" max="506" width="11.42578125" style="1" hidden="1"/>
+    <col min="507" max="507" width="16" style="1" hidden="1"/>
+    <col min="508" max="508" width="20.42578125" style="1" hidden="1"/>
+    <col min="509" max="755" width="11.42578125" style="1" hidden="1"/>
+    <col min="756" max="756" width="15.42578125" style="1" hidden="1"/>
+    <col min="757" max="757" width="11.42578125" style="1" hidden="1"/>
+    <col min="758" max="758" width="15.7109375" style="1" hidden="1"/>
+    <col min="759" max="759" width="21.7109375" style="1" hidden="1"/>
+    <col min="760" max="762" width="11.42578125" style="1" hidden="1"/>
+    <col min="763" max="763" width="16" style="1" hidden="1"/>
+    <col min="764" max="764" width="20.42578125" style="1" hidden="1"/>
+    <col min="765" max="1011" width="11.42578125" style="1" hidden="1"/>
+    <col min="1012" max="1012" width="15.42578125" style="1" hidden="1"/>
+    <col min="1013" max="1013" width="11.42578125" style="1" hidden="1"/>
+    <col min="1014" max="1014" width="15.7109375" style="1" hidden="1"/>
+    <col min="1015" max="1015" width="21.7109375" style="1" hidden="1"/>
+    <col min="1016" max="1018" width="11.42578125" style="1" hidden="1"/>
+    <col min="1019" max="1019" width="16" style="1" hidden="1"/>
+    <col min="1020" max="1020" width="20.42578125" style="1" hidden="1"/>
+    <col min="1021" max="1267" width="11.42578125" style="1" hidden="1"/>
+    <col min="1268" max="1268" width="15.42578125" style="1" hidden="1"/>
+    <col min="1269" max="1269" width="11.42578125" style="1" hidden="1"/>
+    <col min="1270" max="1270" width="15.7109375" style="1" hidden="1"/>
+    <col min="1271" max="1271" width="21.7109375" style="1" hidden="1"/>
+    <col min="1272" max="1274" width="11.42578125" style="1" hidden="1"/>
+    <col min="1275" max="1275" width="16" style="1" hidden="1"/>
+    <col min="1276" max="1276" width="20.42578125" style="1" hidden="1"/>
+    <col min="1277" max="1523" width="11.42578125" style="1" hidden="1"/>
+    <col min="1524" max="1524" width="15.42578125" style="1" hidden="1"/>
+    <col min="1525" max="1525" width="11.42578125" style="1" hidden="1"/>
+    <col min="1526" max="1526" width="15.7109375" style="1" hidden="1"/>
+    <col min="1527" max="1527" width="21.7109375" style="1" hidden="1"/>
+    <col min="1528" max="1530" width="11.42578125" style="1" hidden="1"/>
+    <col min="1531" max="1531" width="16" style="1" hidden="1"/>
+    <col min="1532" max="1532" width="20.42578125" style="1" hidden="1"/>
+    <col min="1533" max="1779" width="11.42578125" style="1" hidden="1"/>
+    <col min="1780" max="1780" width="15.42578125" style="1" hidden="1"/>
+    <col min="1781" max="1781" width="11.42578125" style="1" hidden="1"/>
+    <col min="1782" max="1782" width="15.7109375" style="1" hidden="1"/>
+    <col min="1783" max="1783" width="21.7109375" style="1" hidden="1"/>
+    <col min="1784" max="1786" width="11.42578125" style="1" hidden="1"/>
+    <col min="1787" max="1787" width="16" style="1" hidden="1"/>
+    <col min="1788" max="1788" width="20.42578125" style="1" hidden="1"/>
+    <col min="1789" max="2035" width="11.42578125" style="1" hidden="1"/>
+    <col min="2036" max="2036" width="15.42578125" style="1" hidden="1"/>
+    <col min="2037" max="2037" width="11.42578125" style="1" hidden="1"/>
+    <col min="2038" max="2038" width="15.7109375" style="1" hidden="1"/>
+    <col min="2039" max="2039" width="21.7109375" style="1" hidden="1"/>
+    <col min="2040" max="2042" width="11.42578125" style="1" hidden="1"/>
+    <col min="2043" max="2043" width="16" style="1" hidden="1"/>
+    <col min="2044" max="2044" width="20.42578125" style="1" hidden="1"/>
+    <col min="2045" max="2291" width="11.42578125" style="1" hidden="1"/>
+    <col min="2292" max="2292" width="15.42578125" style="1" hidden="1"/>
+    <col min="2293" max="2293" width="11.42578125" style="1" hidden="1"/>
+    <col min="2294" max="2294" width="15.7109375" style="1" hidden="1"/>
+    <col min="2295" max="2295" width="21.7109375" style="1" hidden="1"/>
+    <col min="2296" max="2298" width="11.42578125" style="1" hidden="1"/>
+    <col min="2299" max="2299" width="16" style="1" hidden="1"/>
+    <col min="2300" max="2300" width="20.42578125" style="1" hidden="1"/>
+    <col min="2301" max="2547" width="11.42578125" style="1" hidden="1"/>
+    <col min="2548" max="2548" width="15.42578125" style="1" hidden="1"/>
+    <col min="2549" max="2549" width="11.42578125" style="1" hidden="1"/>
+    <col min="2550" max="2550" width="15.7109375" style="1" hidden="1"/>
+    <col min="2551" max="2551" width="21.7109375" style="1" hidden="1"/>
+    <col min="2552" max="2554" width="11.42578125" style="1" hidden="1"/>
+    <col min="2555" max="2555" width="16" style="1" hidden="1"/>
+    <col min="2556" max="2556" width="20.42578125" style="1" hidden="1"/>
+    <col min="2557" max="2803" width="11.42578125" style="1" hidden="1"/>
+    <col min="2804" max="2804" width="15.42578125" style="1" hidden="1"/>
+    <col min="2805" max="2805" width="11.42578125" style="1" hidden="1"/>
+    <col min="2806" max="2806" width="15.7109375" style="1" hidden="1"/>
+    <col min="2807" max="2807" width="21.7109375" style="1" hidden="1"/>
+    <col min="2808" max="2810" width="11.42578125" style="1" hidden="1"/>
+    <col min="2811" max="2811" width="16" style="1" hidden="1"/>
+    <col min="2812" max="2812" width="20.42578125" style="1" hidden="1"/>
+    <col min="2813" max="3059" width="11.42578125" style="1" hidden="1"/>
+    <col min="3060" max="3060" width="15.42578125" style="1" hidden="1"/>
+    <col min="3061" max="3061" width="11.42578125" style="1" hidden="1"/>
+    <col min="3062" max="3062" width="15.7109375" style="1" hidden="1"/>
+    <col min="3063" max="3063" width="21.7109375" style="1" hidden="1"/>
+    <col min="3064" max="3066" width="11.42578125" style="1" hidden="1"/>
+    <col min="3067" max="3067" width="16" style="1" hidden="1"/>
+    <col min="3068" max="3068" width="20.42578125" style="1" hidden="1"/>
+    <col min="3069" max="3315" width="11.42578125" style="1" hidden="1"/>
+    <col min="3316" max="3316" width="15.42578125" style="1" hidden="1"/>
+    <col min="3317" max="3317" width="11.42578125" style="1" hidden="1"/>
+    <col min="3318" max="3318" width="15.7109375" style="1" hidden="1"/>
+    <col min="3319" max="3319" width="21.7109375" style="1" hidden="1"/>
+    <col min="3320" max="3322" width="11.42578125" style="1" hidden="1"/>
+    <col min="3323" max="3323" width="16" style="1" hidden="1"/>
+    <col min="3324" max="3324" width="20.42578125" style="1" hidden="1"/>
+    <col min="3325" max="3571" width="11.42578125" style="1" hidden="1"/>
+    <col min="3572" max="3572" width="15.42578125" style="1" hidden="1"/>
+    <col min="3573" max="3573" width="11.42578125" style="1" hidden="1"/>
+    <col min="3574" max="3574" width="15.7109375" style="1" hidden="1"/>
+    <col min="3575" max="3575" width="21.7109375" style="1" hidden="1"/>
+    <col min="3576" max="3578" width="11.42578125" style="1" hidden="1"/>
+    <col min="3579" max="3579" width="16" style="1" hidden="1"/>
+    <col min="3580" max="3580" width="20.42578125" style="1" hidden="1"/>
+    <col min="3581" max="3827" width="11.42578125" style="1" hidden="1"/>
+    <col min="3828" max="3828" width="15.42578125" style="1" hidden="1"/>
+    <col min="3829" max="3829" width="11.42578125" style="1" hidden="1"/>
+    <col min="3830" max="3830" width="15.7109375" style="1" hidden="1"/>
+    <col min="3831" max="3831" width="21.7109375" style="1" hidden="1"/>
+    <col min="3832" max="3834" width="11.42578125" style="1" hidden="1"/>
+    <col min="3835" max="3835" width="16" style="1" hidden="1"/>
+    <col min="3836" max="3836" width="20.42578125" style="1" hidden="1"/>
+    <col min="3837" max="4083" width="11.42578125" style="1" hidden="1"/>
+    <col min="4084" max="4084" width="15.42578125" style="1" hidden="1"/>
+    <col min="4085" max="4085" width="11.42578125" style="1" hidden="1"/>
+    <col min="4086" max="4086" width="15.7109375" style="1" hidden="1"/>
+    <col min="4087" max="4087" width="21.7109375" style="1" hidden="1"/>
+    <col min="4088" max="4090" width="11.42578125" style="1" hidden="1"/>
+    <col min="4091" max="4091" width="16" style="1" hidden="1"/>
+    <col min="4092" max="4092" width="20.42578125" style="1" hidden="1"/>
+    <col min="4093" max="4339" width="11.42578125" style="1" hidden="1"/>
+    <col min="4340" max="4340" width="15.42578125" style="1" hidden="1"/>
+    <col min="4341" max="4341" width="11.42578125" style="1" hidden="1"/>
+    <col min="4342" max="4342" width="15.7109375" style="1" hidden="1"/>
+    <col min="4343" max="4343" width="21.7109375" style="1" hidden="1"/>
+    <col min="4344" max="4346" width="11.42578125" style="1" hidden="1"/>
+    <col min="4347" max="4347" width="16" style="1" hidden="1"/>
+    <col min="4348" max="4348" width="20.42578125" style="1" hidden="1"/>
+    <col min="4349" max="4595" width="11.42578125" style="1" hidden="1"/>
+    <col min="4596" max="4596" width="15.42578125" style="1" hidden="1"/>
+    <col min="4597" max="4597" width="11.42578125" style="1" hidden="1"/>
+    <col min="4598" max="4598" width="15.7109375" style="1" hidden="1"/>
+    <col min="4599" max="4599" width="21.7109375" style="1" hidden="1"/>
+    <col min="4600" max="4602" width="11.42578125" style="1" hidden="1"/>
+    <col min="4603" max="4603" width="16" style="1" hidden="1"/>
+    <col min="4604" max="4604" width="20.42578125" style="1" hidden="1"/>
+    <col min="4605" max="4851" width="11.42578125" style="1" hidden="1"/>
+    <col min="4852" max="4852" width="15.42578125" style="1" hidden="1"/>
+    <col min="4853" max="4853" width="11.42578125" style="1" hidden="1"/>
+    <col min="4854" max="4854" width="15.7109375" style="1" hidden="1"/>
+    <col min="4855" max="4855" width="21.7109375" style="1" hidden="1"/>
+    <col min="4856" max="4858" width="11.42578125" style="1" hidden="1"/>
+    <col min="4859" max="4859" width="16" style="1" hidden="1"/>
+    <col min="4860" max="4860" width="20.42578125" style="1" hidden="1"/>
+    <col min="4861" max="5107" width="11.42578125" style="1" hidden="1"/>
+    <col min="5108" max="5108" width="15.42578125" style="1" hidden="1"/>
+    <col min="5109" max="5109" width="11.42578125" style="1" hidden="1"/>
+    <col min="5110" max="5110" width="15.7109375" style="1" hidden="1"/>
+    <col min="5111" max="5111" width="21.7109375" style="1" hidden="1"/>
+    <col min="5112" max="5114" width="11.42578125" style="1" hidden="1"/>
+    <col min="5115" max="5115" width="16" style="1" hidden="1"/>
+    <col min="5116" max="5116" width="20.42578125" style="1" hidden="1"/>
+    <col min="5117" max="5363" width="11.42578125" style="1" hidden="1"/>
+    <col min="5364" max="5364" width="15.42578125" style="1" hidden="1"/>
+    <col min="5365" max="5365" width="11.42578125" style="1" hidden="1"/>
+    <col min="5366" max="5366" width="15.7109375" style="1" hidden="1"/>
+    <col min="5367" max="5367" width="21.7109375" style="1" hidden="1"/>
+    <col min="5368" max="5370" width="11.42578125" style="1" hidden="1"/>
+    <col min="5371" max="5371" width="16" style="1" hidden="1"/>
+    <col min="5372" max="5372" width="20.42578125" style="1" hidden="1"/>
+    <col min="5373" max="5619" width="11.42578125" style="1" hidden="1"/>
+    <col min="5620" max="5620" width="15.42578125" style="1" hidden="1"/>
+    <col min="5621" max="5621" width="11.42578125" style="1" hidden="1"/>
+    <col min="5622" max="5622" width="15.7109375" style="1" hidden="1"/>
+    <col min="5623" max="5623" width="21.7109375" style="1" hidden="1"/>
+    <col min="5624" max="5626" width="11.42578125" style="1" hidden="1"/>
+    <col min="5627" max="5627" width="16" style="1" hidden="1"/>
+    <col min="5628" max="5628" width="20.42578125" style="1" hidden="1"/>
+    <col min="5629" max="5875" width="11.42578125" style="1" hidden="1"/>
+    <col min="5876" max="5876" width="15.42578125" style="1" hidden="1"/>
+    <col min="5877" max="5877" width="11.42578125" style="1" hidden="1"/>
+    <col min="5878" max="5878" width="15.7109375" style="1" hidden="1"/>
+    <col min="5879" max="5879" width="21.7109375" style="1" hidden="1"/>
+    <col min="5880" max="5882" width="11.42578125" style="1" hidden="1"/>
+    <col min="5883" max="5883" width="16" style="1" hidden="1"/>
+    <col min="5884" max="5884" width="20.42578125" style="1" hidden="1"/>
+    <col min="5885" max="6131" width="11.42578125" style="1" hidden="1"/>
+    <col min="6132" max="6132" width="15.42578125" style="1" hidden="1"/>
+    <col min="6133" max="6133" width="11.42578125" style="1" hidden="1"/>
+    <col min="6134" max="6134" width="15.7109375" style="1" hidden="1"/>
+    <col min="6135" max="6135" width="21.7109375" style="1" hidden="1"/>
+    <col min="6136" max="6138" width="11.42578125" style="1" hidden="1"/>
+    <col min="6139" max="6139" width="16" style="1" hidden="1"/>
+    <col min="6140" max="6140" width="20.42578125" style="1" hidden="1"/>
+    <col min="6141" max="6387" width="11.42578125" style="1" hidden="1"/>
+    <col min="6388" max="6388" width="15.42578125" style="1" hidden="1"/>
+    <col min="6389" max="6389" width="11.42578125" style="1" hidden="1"/>
+    <col min="6390" max="6390" width="15.7109375" style="1" hidden="1"/>
+    <col min="6391" max="6391" width="21.7109375" style="1" hidden="1"/>
+    <col min="6392" max="6394" width="11.42578125" style="1" hidden="1"/>
+    <col min="6395" max="6395" width="16" style="1" hidden="1"/>
+    <col min="6396" max="6396" width="20.42578125" style="1" hidden="1"/>
+    <col min="6397" max="6643" width="11.42578125" style="1" hidden="1"/>
+    <col min="6644" max="6644" width="15.42578125" style="1" hidden="1"/>
+    <col min="6645" max="6645" width="11.42578125" style="1" hidden="1"/>
+    <col min="6646" max="6646" width="15.7109375" style="1" hidden="1"/>
+    <col min="6647" max="6647" width="21.7109375" style="1" hidden="1"/>
+    <col min="6648" max="6650" width="11.42578125" style="1" hidden="1"/>
+    <col min="6651" max="6651" width="16" style="1" hidden="1"/>
+    <col min="6652" max="6652" width="20.42578125" style="1" hidden="1"/>
+    <col min="6653" max="6899" width="11.42578125" style="1" hidden="1"/>
+    <col min="6900" max="6900" width="15.42578125" style="1" hidden="1"/>
+    <col min="6901" max="6901" width="11.42578125" style="1" hidden="1"/>
+    <col min="6902" max="6902" width="15.7109375" style="1" hidden="1"/>
+    <col min="6903" max="6903" width="21.7109375" style="1" hidden="1"/>
+    <col min="6904" max="6906" width="11.42578125" style="1" hidden="1"/>
+    <col min="6907" max="6907" width="16" style="1" hidden="1"/>
+    <col min="6908" max="6908" width="20.42578125" style="1" hidden="1"/>
+    <col min="6909" max="7155" width="11.42578125" style="1" hidden="1"/>
+    <col min="7156" max="7156" width="15.42578125" style="1" hidden="1"/>
+    <col min="7157" max="7157" width="11.42578125" style="1" hidden="1"/>
+    <col min="7158" max="7158" width="15.7109375" style="1" hidden="1"/>
+    <col min="7159" max="7159" width="21.7109375" style="1" hidden="1"/>
+    <col min="7160" max="7162" width="11.42578125" style="1" hidden="1"/>
+    <col min="7163" max="7163" width="16" style="1" hidden="1"/>
+    <col min="7164" max="7164" width="20.42578125" style="1" hidden="1"/>
+    <col min="7165" max="7411" width="11.42578125" style="1" hidden="1"/>
+    <col min="7412" max="7412" width="15.42578125" style="1" hidden="1"/>
+    <col min="7413" max="7413" width="11.42578125" style="1" hidden="1"/>
+    <col min="7414" max="7414" width="15.7109375" style="1" hidden="1"/>
+    <col min="7415" max="7415" width="21.7109375" style="1" hidden="1"/>
+    <col min="7416" max="7418" width="11.42578125" style="1" hidden="1"/>
+    <col min="7419" max="7419" width="16" style="1" hidden="1"/>
+    <col min="7420" max="7420" width="20.42578125" style="1" hidden="1"/>
+    <col min="7421" max="7667" width="11.42578125" style="1" hidden="1"/>
+    <col min="7668" max="7668" width="15.42578125" style="1" hidden="1"/>
+    <col min="7669" max="7669" width="11.42578125" style="1" hidden="1"/>
+    <col min="7670" max="7670" width="15.7109375" style="1" hidden="1"/>
+    <col min="7671" max="7671" width="21.7109375" style="1" hidden="1"/>
+    <col min="7672" max="7674" width="11.42578125" style="1" hidden="1"/>
+    <col min="7675" max="7675" width="16" style="1" hidden="1"/>
+    <col min="7676" max="7676" width="20.42578125" style="1" hidden="1"/>
+    <col min="7677" max="7923" width="11.42578125" style="1" hidden="1"/>
+    <col min="7924" max="7924" width="15.42578125" style="1" hidden="1"/>
+    <col min="7925" max="7925" width="11.42578125" style="1" hidden="1"/>
+    <col min="7926" max="7926" width="15.7109375" style="1" hidden="1"/>
+    <col min="7927" max="7927" width="21.7109375" style="1" hidden="1"/>
+    <col min="7928" max="7930" width="11.42578125" style="1" hidden="1"/>
+    <col min="7931" max="7931" width="16" style="1" hidden="1"/>
+    <col min="7932" max="7932" width="20.42578125" style="1" hidden="1"/>
+    <col min="7933" max="8179" width="11.42578125" style="1" hidden="1"/>
+    <col min="8180" max="8180" width="15.42578125" style="1" hidden="1"/>
+    <col min="8181" max="8181" width="11.42578125" style="1" hidden="1"/>
+    <col min="8182" max="8182" width="15.7109375" style="1" hidden="1"/>
+    <col min="8183" max="8183" width="21.7109375" style="1" hidden="1"/>
+    <col min="8184" max="8186" width="11.42578125" style="1" hidden="1"/>
+    <col min="8187" max="8187" width="16" style="1" hidden="1"/>
+    <col min="8188" max="8188" width="20.42578125" style="1" hidden="1"/>
+    <col min="8189" max="8435" width="11.42578125" style="1" hidden="1"/>
+    <col min="8436" max="8436" width="15.42578125" style="1" hidden="1"/>
+    <col min="8437" max="8437" width="11.42578125" style="1" hidden="1"/>
+    <col min="8438" max="8438" width="15.7109375" style="1" hidden="1"/>
+    <col min="8439" max="8439" width="21.7109375" style="1" hidden="1"/>
+    <col min="8440" max="8442" width="11.42578125" style="1" hidden="1"/>
+    <col min="8443" max="8443" width="16" style="1" hidden="1"/>
+    <col min="8444" max="8444" width="20.42578125" style="1" hidden="1"/>
+    <col min="8445" max="8691" width="11.42578125" style="1" hidden="1"/>
+    <col min="8692" max="8692" width="15.42578125" style="1" hidden="1"/>
+    <col min="8693" max="8693" width="11.42578125" style="1" hidden="1"/>
+    <col min="8694" max="8694" width="15.7109375" style="1" hidden="1"/>
+    <col min="8695" max="8695" width="21.7109375" style="1" hidden="1"/>
+    <col min="8696" max="8698" width="11.42578125" style="1" hidden="1"/>
+    <col min="8699" max="8699" width="16" style="1" hidden="1"/>
+    <col min="8700" max="8700" width="20.42578125" style="1" hidden="1"/>
+    <col min="8701" max="8947" width="11.42578125" style="1" hidden="1"/>
+    <col min="8948" max="8948" width="15.42578125" style="1" hidden="1"/>
+    <col min="8949" max="8949" width="11.42578125" style="1" hidden="1"/>
+    <col min="8950" max="8950" width="15.7109375" style="1" hidden="1"/>
+    <col min="8951" max="8951" width="21.7109375" style="1" hidden="1"/>
+    <col min="8952" max="8954" width="11.42578125" style="1" hidden="1"/>
+    <col min="8955" max="8955" width="16" style="1" hidden="1"/>
+    <col min="8956" max="8956" width="20.42578125" style="1" hidden="1"/>
+    <col min="8957" max="9203" width="11.42578125" style="1" hidden="1"/>
+    <col min="9204" max="9204" width="15.42578125" style="1" hidden="1"/>
+    <col min="9205" max="9205" width="11.42578125" style="1" hidden="1"/>
+    <col min="9206" max="9206" width="15.7109375" style="1" hidden="1"/>
+    <col min="9207" max="9207" width="21.7109375" style="1" hidden="1"/>
+    <col min="9208" max="9210" width="11.42578125" style="1" hidden="1"/>
+    <col min="9211" max="9211" width="16" style="1" hidden="1"/>
+    <col min="9212" max="9212" width="20.42578125" style="1" hidden="1"/>
+    <col min="9213" max="9459" width="11.42578125" style="1" hidden="1"/>
+    <col min="9460" max="9460" width="15.42578125" style="1" hidden="1"/>
+    <col min="9461" max="9461" width="11.42578125" style="1" hidden="1"/>
+    <col min="9462" max="9462" width="15.7109375" style="1" hidden="1"/>
+    <col min="9463" max="9463" width="21.7109375" style="1" hidden="1"/>
+    <col min="9464" max="9466" width="11.42578125" style="1" hidden="1"/>
+    <col min="9467" max="9467" width="16" style="1" hidden="1"/>
+    <col min="9468" max="9468" width="20.42578125" style="1" hidden="1"/>
+    <col min="9469" max="9715" width="11.42578125" style="1" hidden="1"/>
+    <col min="9716" max="9716" width="15.42578125" style="1" hidden="1"/>
+    <col min="9717" max="9717" width="11.42578125" style="1" hidden="1"/>
+    <col min="9718" max="9718" width="15.7109375" style="1" hidden="1"/>
+    <col min="9719" max="9719" width="21.7109375" style="1" hidden="1"/>
+    <col min="9720" max="9722" width="11.42578125" style="1" hidden="1"/>
+    <col min="9723" max="9723" width="16" style="1" hidden="1"/>
+    <col min="9724" max="9724" width="20.42578125" style="1" hidden="1"/>
+    <col min="9725" max="9971" width="11.42578125" style="1" hidden="1"/>
+    <col min="9972" max="9972" width="15.42578125" style="1" hidden="1"/>
+    <col min="9973" max="9973" width="11.42578125" style="1" hidden="1"/>
+    <col min="9974" max="9974" width="15.7109375" style="1" hidden="1"/>
+    <col min="9975" max="9975" width="21.7109375" style="1" hidden="1"/>
+    <col min="9976" max="9978" width="11.42578125" style="1" hidden="1"/>
+    <col min="9979" max="9979" width="16" style="1" hidden="1"/>
+    <col min="9980" max="9980" width="20.42578125" style="1" hidden="1"/>
+    <col min="9981" max="10227" width="11.42578125" style="1" hidden="1"/>
+    <col min="10228" max="10228" width="15.42578125" style="1" hidden="1"/>
+    <col min="10229" max="10229" width="11.42578125" style="1" hidden="1"/>
+    <col min="10230" max="10230" width="15.7109375" style="1" hidden="1"/>
+    <col min="10231" max="10231" width="21.7109375" style="1" hidden="1"/>
+    <col min="10232" max="10234" width="11.42578125" style="1" hidden="1"/>
+    <col min="10235" max="10235" width="16" style="1" hidden="1"/>
+    <col min="10236" max="10236" width="20.42578125" style="1" hidden="1"/>
+    <col min="10237" max="10483" width="11.42578125" style="1" hidden="1"/>
+    <col min="10484" max="10484" width="15.42578125" style="1" hidden="1"/>
+    <col min="10485" max="10485" width="11.42578125" style="1" hidden="1"/>
+    <col min="10486" max="10486" width="15.7109375" style="1" hidden="1"/>
+    <col min="10487" max="10487" width="21.7109375" style="1" hidden="1"/>
+    <col min="10488" max="10490" width="11.42578125" style="1" hidden="1"/>
+    <col min="10491" max="10491" width="16" style="1" hidden="1"/>
+    <col min="10492" max="10492" width="20.42578125" style="1" hidden="1"/>
+    <col min="10493" max="10739" width="11.42578125" style="1" hidden="1"/>
+    <col min="10740" max="10740" width="15.42578125" style="1" hidden="1"/>
+    <col min="10741" max="10741" width="11.42578125" style="1" hidden="1"/>
+    <col min="10742" max="10742" width="15.7109375" style="1" hidden="1"/>
+    <col min="10743" max="10743" width="21.7109375" style="1" hidden="1"/>
+    <col min="10744" max="10746" width="11.42578125" style="1" hidden="1"/>
+    <col min="10747" max="10747" width="16" style="1" hidden="1"/>
+    <col min="10748" max="10748" width="20.42578125" style="1" hidden="1"/>
+    <col min="10749" max="10995" width="11.42578125" style="1" hidden="1"/>
+    <col min="10996" max="10996" width="15.42578125" style="1" hidden="1"/>
+    <col min="10997" max="10997" width="11.42578125" style="1" hidden="1"/>
+    <col min="10998" max="10998" width="15.7109375" style="1" hidden="1"/>
+    <col min="10999" max="10999" width="21.7109375" style="1" hidden="1"/>
+    <col min="11000" max="11002" width="11.42578125" style="1" hidden="1"/>
+    <col min="11003" max="11003" width="16" style="1" hidden="1"/>
+    <col min="11004" max="11004" width="20.42578125" style="1" hidden="1"/>
+    <col min="11005" max="11251" width="11.42578125" style="1" hidden="1"/>
+    <col min="11252" max="11252" width="15.42578125" style="1" hidden="1"/>
+    <col min="11253" max="11253" width="11.42578125" style="1" hidden="1"/>
+    <col min="11254" max="11254" width="15.7109375" style="1" hidden="1"/>
+    <col min="11255" max="11255" width="21.7109375" style="1" hidden="1"/>
+    <col min="11256" max="11258" width="11.42578125" style="1" hidden="1"/>
+    <col min="11259" max="11259" width="16" style="1" hidden="1"/>
+    <col min="11260" max="11260" width="20.42578125" style="1" hidden="1"/>
+    <col min="11261" max="11507" width="11.42578125" style="1" hidden="1"/>
+    <col min="11508" max="11508" width="15.42578125" style="1" hidden="1"/>
+    <col min="11509" max="11509" width="11.42578125" style="1" hidden="1"/>
+    <col min="11510" max="11510" width="15.7109375" style="1" hidden="1"/>
+    <col min="11511" max="11511" width="21.7109375" style="1" hidden="1"/>
+    <col min="11512" max="11514" width="11.42578125" style="1" hidden="1"/>
+    <col min="11515" max="11515" width="16" style="1" hidden="1"/>
+    <col min="11516" max="11516" width="20.42578125" style="1" hidden="1"/>
+    <col min="11517" max="11763" width="11.42578125" style="1" hidden="1"/>
+    <col min="11764" max="11764" width="15.42578125" style="1" hidden="1"/>
+    <col min="11765" max="11765" width="11.42578125" style="1" hidden="1"/>
+    <col min="11766" max="11766" width="15.7109375" style="1" hidden="1"/>
+    <col min="11767" max="11767" width="21.7109375" style="1" hidden="1"/>
+    <col min="11768" max="11770" width="11.42578125" style="1" hidden="1"/>
+    <col min="11771" max="11771" width="16" style="1" hidden="1"/>
+    <col min="11772" max="11772" width="20.42578125" style="1" hidden="1"/>
+    <col min="11773" max="12019" width="11.42578125" style="1" hidden="1"/>
+    <col min="12020" max="12020" width="15.42578125" style="1" hidden="1"/>
+    <col min="12021" max="12021" width="11.42578125" style="1" hidden="1"/>
+    <col min="12022" max="12022" width="15.7109375" style="1" hidden="1"/>
+    <col min="12023" max="12023" width="21.7109375" style="1" hidden="1"/>
+    <col min="12024" max="12026" width="11.42578125" style="1" hidden="1"/>
+    <col min="12027" max="12027" width="16" style="1" hidden="1"/>
+    <col min="12028" max="12028" width="20.42578125" style="1" hidden="1"/>
+    <col min="12029" max="12275" width="11.42578125" style="1" hidden="1"/>
+    <col min="12276" max="12276" width="15.42578125" style="1" hidden="1"/>
+    <col min="12277" max="12277" width="11.42578125" style="1" hidden="1"/>
+    <col min="12278" max="12278" width="15.7109375" style="1" hidden="1"/>
+    <col min="12279" max="12279" width="21.7109375" style="1" hidden="1"/>
+    <col min="12280" max="12282" width="11.42578125" style="1" hidden="1"/>
+    <col min="12283" max="12283" width="16" style="1" hidden="1"/>
+    <col min="12284" max="12284" width="20.42578125" style="1" hidden="1"/>
+    <col min="12285" max="12531" width="11.42578125" style="1" hidden="1"/>
+    <col min="12532" max="12532" width="15.42578125" style="1" hidden="1"/>
+    <col min="12533" max="12533" width="11.42578125" style="1" hidden="1"/>
+    <col min="12534" max="12534" width="15.7109375" style="1" hidden="1"/>
+    <col min="12535" max="12535" width="21.7109375" style="1" hidden="1"/>
+    <col min="12536" max="12538" width="11.42578125" style="1" hidden="1"/>
+    <col min="12539" max="12539" width="16" style="1" hidden="1"/>
+    <col min="12540" max="12540" width="20.42578125" style="1" hidden="1"/>
+    <col min="12541" max="12787" width="11.42578125" style="1" hidden="1"/>
+    <col min="12788" max="12788" width="15.42578125" style="1" hidden="1"/>
+    <col min="12789" max="12789" width="11.42578125" style="1" hidden="1"/>
+    <col min="12790" max="12790" width="15.7109375" style="1" hidden="1"/>
+    <col min="12791" max="12791" width="21.7109375" style="1" hidden="1"/>
+    <col min="12792" max="12794" width="11.42578125" style="1" hidden="1"/>
+    <col min="12795" max="12795" width="16" style="1" hidden="1"/>
+    <col min="12796" max="12796" width="20.42578125" style="1" hidden="1"/>
+    <col min="12797" max="13043" width="11.42578125" style="1" hidden="1"/>
+    <col min="13044" max="13044" width="15.42578125" style="1" hidden="1"/>
+    <col min="13045" max="13045" width="11.42578125" style="1" hidden="1"/>
+    <col min="13046" max="13046" width="15.7109375" style="1" hidden="1"/>
+    <col min="13047" max="13047" width="21.7109375" style="1" hidden="1"/>
+    <col min="13048" max="13050" width="11.42578125" style="1" hidden="1"/>
+    <col min="13051" max="13051" width="16" style="1" hidden="1"/>
+    <col min="13052" max="13052" width="20.42578125" style="1" hidden="1"/>
+    <col min="13053" max="13299" width="11.42578125" style="1" hidden="1"/>
+    <col min="13300" max="13300" width="15.42578125" style="1" hidden="1"/>
+    <col min="13301" max="13301" width="11.42578125" style="1" hidden="1"/>
+    <col min="13302" max="13302" width="15.7109375" style="1" hidden="1"/>
+    <col min="13303" max="13303" width="21.7109375" style="1" hidden="1"/>
+    <col min="13304" max="13306" width="11.42578125" style="1" hidden="1"/>
+    <col min="13307" max="13307" width="16" style="1" hidden="1"/>
+    <col min="13308" max="13308" width="20.42578125" style="1" hidden="1"/>
+    <col min="13309" max="13555" width="11.42578125" style="1" hidden="1"/>
+    <col min="13556" max="13556" width="15.42578125" style="1" hidden="1"/>
+    <col min="13557" max="13557" width="11.42578125" style="1" hidden="1"/>
+    <col min="13558" max="13558" width="15.7109375" style="1" hidden="1"/>
+    <col min="13559" max="13559" width="21.7109375" style="1" hidden="1"/>
+    <col min="13560" max="13562" width="11.42578125" style="1" hidden="1"/>
+    <col min="13563" max="13563" width="16" style="1" hidden="1"/>
+    <col min="13564" max="13564" width="20.42578125" style="1" hidden="1"/>
+    <col min="13565" max="13811" width="11.42578125" style="1" hidden="1"/>
+    <col min="13812" max="13812" width="15.42578125" style="1" hidden="1"/>
+    <col min="13813" max="13813" width="11.42578125" style="1" hidden="1"/>
+    <col min="13814" max="13814" width="15.7109375" style="1" hidden="1"/>
+    <col min="13815" max="13815" width="21.7109375" style="1" hidden="1"/>
+    <col min="13816" max="13818" width="11.42578125" style="1" hidden="1"/>
+    <col min="13819" max="13819" width="16" style="1" hidden="1"/>
+    <col min="13820" max="13820" width="20.42578125" style="1" hidden="1"/>
+    <col min="13821" max="14067" width="11.42578125" style="1" hidden="1"/>
+    <col min="14068" max="14068" width="15.42578125" style="1" hidden="1"/>
+    <col min="14069" max="14069" width="11.42578125" style="1" hidden="1"/>
+    <col min="14070" max="14070" width="15.7109375" style="1" hidden="1"/>
+    <col min="14071" max="14071" width="21.7109375" style="1" hidden="1"/>
+    <col min="14072" max="14074" width="11.42578125" style="1" hidden="1"/>
+    <col min="14075" max="14075" width="16" style="1" hidden="1"/>
+    <col min="14076" max="14076" width="20.42578125" style="1" hidden="1"/>
+    <col min="14077" max="14323" width="11.42578125" style="1" hidden="1"/>
+    <col min="14324" max="14324" width="15.42578125" style="1" hidden="1"/>
+    <col min="14325" max="14325" width="11.42578125" style="1" hidden="1"/>
+    <col min="14326" max="14326" width="15.7109375" style="1" hidden="1"/>
+    <col min="14327" max="14327" width="21.7109375" style="1" hidden="1"/>
+    <col min="14328" max="14330" width="11.42578125" style="1" hidden="1"/>
+    <col min="14331" max="14331" width="16" style="1" hidden="1"/>
+    <col min="14332" max="14332" width="20.42578125" style="1" hidden="1"/>
+    <col min="14333" max="14579" width="11.42578125" style="1" hidden="1"/>
+    <col min="14580" max="14580" width="15.42578125" style="1" hidden="1"/>
+    <col min="14581" max="14581" width="11.42578125" style="1" hidden="1"/>
+    <col min="14582" max="14582" width="15.7109375" style="1" hidden="1"/>
+    <col min="14583" max="14583" width="21.7109375" style="1" hidden="1"/>
+    <col min="14584" max="14586" width="11.42578125" style="1" hidden="1"/>
+    <col min="14587" max="14587" width="16" style="1" hidden="1"/>
+    <col min="14588" max="14588" width="20.42578125" style="1" hidden="1"/>
+    <col min="14589" max="14835" width="11.42578125" style="1" hidden="1"/>
+    <col min="14836" max="14836" width="15.42578125" style="1" hidden="1"/>
+    <col min="14837" max="14837" width="11.42578125" style="1" hidden="1"/>
+    <col min="14838" max="14838" width="15.7109375" style="1" hidden="1"/>
+    <col min="14839" max="14839" width="21.7109375" style="1" hidden="1"/>
+    <col min="14840" max="14842" width="11.42578125" style="1" hidden="1"/>
+    <col min="14843" max="14843" width="16" style="1" hidden="1"/>
+    <col min="14844" max="14844" width="20.42578125" style="1" hidden="1"/>
+    <col min="14845" max="15091" width="11.42578125" style="1" hidden="1"/>
+    <col min="15092" max="15092" width="15.42578125" style="1" hidden="1"/>
+    <col min="15093" max="15093" width="11.42578125" style="1" hidden="1"/>
+    <col min="15094" max="15094" width="15.7109375" style="1" hidden="1"/>
+    <col min="15095" max="15095" width="21.7109375" style="1" hidden="1"/>
+    <col min="15096" max="15098" width="11.42578125" style="1" hidden="1"/>
+    <col min="15099" max="15099" width="16" style="1" hidden="1"/>
+    <col min="15100" max="15100" width="20.42578125" style="1" hidden="1"/>
+    <col min="15101" max="15347" width="11.42578125" style="1" hidden="1"/>
+    <col min="15348" max="15348" width="15.42578125" style="1" hidden="1"/>
+    <col min="15349" max="15349" width="11.42578125" style="1" hidden="1"/>
+    <col min="15350" max="15350" width="15.7109375" style="1" hidden="1"/>
+    <col min="15351" max="15351" width="21.7109375" style="1" hidden="1"/>
+    <col min="15352" max="15354" width="11.42578125" style="1" hidden="1"/>
+    <col min="15355" max="15355" width="16" style="1" hidden="1"/>
+    <col min="15356" max="15356" width="20.42578125" style="1" hidden="1"/>
+    <col min="15357" max="15603" width="11.42578125" style="1" hidden="1"/>
+    <col min="15604" max="15604" width="15.42578125" style="1" hidden="1"/>
+    <col min="15605" max="15605" width="11.42578125" style="1" hidden="1"/>
+    <col min="15606" max="15606" width="15.7109375" style="1" hidden="1"/>
+    <col min="15607" max="15607" width="21.7109375" style="1" hidden="1"/>
+    <col min="15608" max="15610" width="11.42578125" style="1" hidden="1"/>
+    <col min="15611" max="15611" width="16" style="1" hidden="1"/>
+    <col min="15612" max="15612" width="20.42578125" style="1" hidden="1"/>
+    <col min="15613" max="15859" width="11.42578125" style="1" hidden="1"/>
+    <col min="15860" max="15860" width="15.42578125" style="1" hidden="1"/>
+    <col min="15861" max="15861" width="11.42578125" style="1" hidden="1"/>
+    <col min="15862" max="15862" width="15.7109375" style="1" hidden="1"/>
+    <col min="15863" max="15863" width="21.7109375" style="1" hidden="1"/>
+    <col min="15864" max="15866" width="11.42578125" style="1" hidden="1"/>
+    <col min="15867" max="15867" width="16" style="1" hidden="1"/>
+    <col min="15868" max="15868" width="20.42578125" style="1" hidden="1"/>
+    <col min="15869" max="16115" width="11.42578125" style="1" hidden="1"/>
+    <col min="16116" max="16116" width="15.42578125" style="1" hidden="1"/>
+    <col min="16117" max="16117" width="11.42578125" style="1" hidden="1"/>
+    <col min="16118" max="16118" width="15.7109375" style="1" hidden="1"/>
+    <col min="16119" max="16119" width="21.7109375" style="1" hidden="1"/>
+    <col min="16120" max="16122" width="11.42578125" style="1" hidden="1"/>
+    <col min="16123" max="16123" width="16" style="1" hidden="1"/>
+    <col min="16124" max="16124" width="20.42578125" style="1" hidden="1"/>
+    <col min="16125" max="16127" width="11.42578125" style="1" hidden="1"/>
+    <col min="16128" max="16128" width="15.42578125" style="1" hidden="1"/>
+    <col min="16129" max="16129" width="11.42578125" style="1" hidden="1"/>
+    <col min="16130" max="16130" width="15.7109375" style="1" hidden="1"/>
+    <col min="16131" max="16131" width="21.7109375" style="1" hidden="1"/>
+    <col min="16132" max="16134" width="11.42578125" style="1" hidden="1"/>
+    <col min="16135" max="16135" width="16" style="1" hidden="1"/>
+    <col min="16136" max="16137" width="20.42578125" style="1" hidden="1"/>
+    <col min="16138" max="16139" width="11.42578125" style="1" hidden="1"/>
+    <col min="16140" max="16140" width="16" style="1" hidden="1"/>
+    <col min="16141" max="16145" width="20.42578125" style="1" hidden="1"/>
+    <col min="16146" max="16384" width="11.42578125" style="1" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
@@ -2688,40 +2636,34 @@
         <v>4</v>
       </c>
       <c r="G1" s="4"/>
-      <c r="H1" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="I1" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="J1" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="K1" s="42" t="s">
-        <v>36</v>
-      </c>
-      <c r="L1" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="M1" s="4"/>
-      <c r="N1" s="22"/>
+      <c r="H1" s="40" t="s">
+        <v>130</v>
+      </c>
+      <c r="I1" s="40" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="K1" s="4"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>5</v>
+      </c>
       <c r="O1" s="5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="R1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="29" t="str">
         <f>RAWDATA!B2</f>
         <v>applicant.last_name</v>
@@ -2738,7 +2680,7 @@
         <f>RAWDATA!E2</f>
         <v>applicant.tag</v>
       </c>
-      <c r="E2" s="34" t="str">
+      <c r="E2" s="33" t="str">
         <f>RAWDATA!F2</f>
         <v>attendance.sanitized_grade</v>
       </c>
@@ -2747,50 +2689,42 @@
         <v>#N/A</v>
       </c>
       <c r="G2" s="4"/>
-      <c r="H2" s="89" t="str">
+      <c r="H2" s="86" t="str">
         <f>RAWDATA!J2</f>
         <v>attendance.hide_grade_str</v>
       </c>
-      <c r="I2" s="88" t="str">
+      <c r="I2" s="85" t="str">
         <f>RAWDATA!G2</f>
         <v>attendance.ects_points</v>
       </c>
-      <c r="J2" s="35" t="str">
-        <f>RAWDATA!K2</f>
-        <v>attendance.ts_requested_str</v>
-      </c>
-      <c r="K2" s="33" t="str">
-        <f t="shared" ref="K2:K26" si="0">IF(E2&gt;0,"X","")</f>
+      <c r="J2" s="32" t="str">
+        <f t="shared" ref="J2:J26" si="0">IF(E2&gt;0,"X","")</f>
         <v>X</v>
       </c>
-      <c r="L2" s="35" t="str">
-        <f>RAWDATA!L2</f>
-        <v>attendance.ts_received_str</v>
-      </c>
-      <c r="M2" s="4"/>
-      <c r="N2" s="22"/>
-      <c r="O2" s="2" t="str">
+      <c r="K2" s="4"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="2" t="str">
         <f>IF(E2&gt;0,$B$33,0)</f>
         <v>course.ects_points</v>
       </c>
-      <c r="P2" s="2" t="str">
+      <c r="N2" s="2" t="str">
         <f>IF(E2&gt;0,$B$32,0)</f>
         <v>course.ger</v>
       </c>
-      <c r="Q2" s="11" t="e">
+      <c r="O2" s="11" t="e">
         <f>IF(E2&gt;0,$F$28,0)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R2" s="1" t="str">
+      <c r="P2" s="1" t="str">
         <f>IF(E2&gt;0,$B$34,0)</f>
         <v>course.name</v>
       </c>
-      <c r="S2" s="1" t="str">
+      <c r="Q2" s="1" t="str">
         <f>IF(E2&gt;0,$B$31,0)</f>
         <v>course.teacher_name</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" s="29">
         <f>RAWDATA!B3</f>
         <v>0</v>
@@ -2807,7 +2741,7 @@
         <f>RAWDATA!E3</f>
         <v>0</v>
       </c>
-      <c r="E3" s="34">
+      <c r="E3" s="33">
         <f>RAWDATA!F3</f>
         <v>0</v>
       </c>
@@ -2816,50 +2750,42 @@
         <v>KP</v>
       </c>
       <c r="G3" s="4"/>
-      <c r="H3" s="89">
+      <c r="H3" s="86">
         <f>RAWDATA!J3</f>
         <v>0</v>
       </c>
-      <c r="I3" s="88">
+      <c r="I3" s="85">
         <f>RAWDATA!G3</f>
         <v>0</v>
       </c>
-      <c r="J3" s="35">
-        <f>RAWDATA!K3</f>
-        <v>0</v>
-      </c>
-      <c r="K3" s="33" t="str">
+      <c r="J3" s="32" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L3" s="35">
-        <f>RAWDATA!L3</f>
-        <v>0</v>
-      </c>
-      <c r="M3" s="4"/>
-      <c r="N3" s="22"/>
-      <c r="O3" s="2">
-        <f t="shared" ref="O3:O26" si="1">IF(E3&gt;0,$B$33,0)</f>
-        <v>0</v>
-      </c>
-      <c r="P3" s="2">
-        <f t="shared" ref="P3:P26" si="2">IF(E3&gt;0,$B$32,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q3" s="11">
-        <f t="shared" ref="Q3:Q26" si="3">IF(E3&gt;0,$F$28,0)</f>
-        <v>0</v>
-      </c>
-      <c r="R3" s="1">
-        <f t="shared" ref="R3:R26" si="4">IF(E3&gt;0,$B$34,0)</f>
-        <v>0</v>
-      </c>
-      <c r="S3" s="1">
-        <f t="shared" ref="S3:S26" si="5">IF(E3&gt;0,$B$31,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="K3" s="4"/>
+      <c r="L3" s="22"/>
+      <c r="M3" s="2">
+        <f t="shared" ref="M3:M26" si="1">IF(E3&gt;0,$B$33,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="2">
+        <f t="shared" ref="N3:N26" si="2">IF(E3&gt;0,$B$32,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O3" s="11">
+        <f t="shared" ref="O3:O26" si="3">IF(E3&gt;0,$F$28,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P3" s="1">
+        <f t="shared" ref="P3:P26" si="4">IF(E3&gt;0,$B$34,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q3" s="1">
+        <f t="shared" ref="Q3:Q26" si="5">IF(E3&gt;0,$B$31,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" s="29">
         <f>RAWDATA!B4</f>
         <v>0</v>
@@ -2876,7 +2802,7 @@
         <f>RAWDATA!E4</f>
         <v>0</v>
       </c>
-      <c r="E4" s="34">
+      <c r="E4" s="33">
         <f>RAWDATA!F4</f>
         <v>0</v>
       </c>
@@ -2885,50 +2811,42 @@
         <v>KP</v>
       </c>
       <c r="G4" s="4"/>
-      <c r="H4" s="89">
+      <c r="H4" s="86">
         <f>RAWDATA!J4</f>
         <v>0</v>
       </c>
-      <c r="I4" s="88">
+      <c r="I4" s="85">
         <f>RAWDATA!G4</f>
         <v>0</v>
       </c>
-      <c r="J4" s="35">
-        <f>RAWDATA!K4</f>
-        <v>0</v>
-      </c>
-      <c r="K4" s="33" t="str">
+      <c r="J4" s="32" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L4" s="35">
-        <f>RAWDATA!L4</f>
-        <v>0</v>
-      </c>
-      <c r="M4" s="4"/>
-      <c r="N4" s="22"/>
-      <c r="O4" s="2">
+      <c r="K4" s="4"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P4" s="2">
+      <c r="N4" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q4" s="11">
+      <c r="O4" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R4" s="1">
+      <c r="P4" s="1">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S4" s="1">
+      <c r="Q4" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="29">
         <f>RAWDATA!B5</f>
         <v>0</v>
@@ -2945,7 +2863,7 @@
         <f>RAWDATA!E5</f>
         <v>0</v>
       </c>
-      <c r="E5" s="34">
+      <c r="E5" s="33">
         <f>RAWDATA!F5</f>
         <v>0</v>
       </c>
@@ -2954,50 +2872,42 @@
         <v>KP</v>
       </c>
       <c r="G5" s="4"/>
-      <c r="H5" s="89">
+      <c r="H5" s="86">
         <f>RAWDATA!J5</f>
         <v>0</v>
       </c>
-      <c r="I5" s="88">
+      <c r="I5" s="85">
         <f>RAWDATA!G5</f>
         <v>0</v>
       </c>
-      <c r="J5" s="35">
-        <f>RAWDATA!K5</f>
-        <v>0</v>
-      </c>
-      <c r="K5" s="33" t="str">
+      <c r="J5" s="32" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L5" s="35">
-        <f>RAWDATA!L5</f>
-        <v>0</v>
-      </c>
-      <c r="M5" s="4"/>
-      <c r="N5" s="22"/>
-      <c r="O5" s="2">
+      <c r="K5" s="4"/>
+      <c r="L5" s="22"/>
+      <c r="M5" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P5" s="2">
+      <c r="N5" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q5" s="11">
+      <c r="O5" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R5" s="1">
+      <c r="P5" s="1">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S5" s="1">
+      <c r="Q5" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" s="29">
         <f>RAWDATA!B6</f>
         <v>0</v>
@@ -3014,7 +2924,7 @@
         <f>RAWDATA!E6</f>
         <v>0</v>
       </c>
-      <c r="E6" s="34">
+      <c r="E6" s="33">
         <f>RAWDATA!F6</f>
         <v>0</v>
       </c>
@@ -3023,50 +2933,42 @@
         <v>KP</v>
       </c>
       <c r="G6" s="4"/>
-      <c r="H6" s="89">
+      <c r="H6" s="86">
         <f>RAWDATA!J6</f>
         <v>0</v>
       </c>
-      <c r="I6" s="88">
+      <c r="I6" s="85">
         <f>RAWDATA!G6</f>
         <v>0</v>
       </c>
-      <c r="J6" s="35">
-        <f>RAWDATA!K6</f>
-        <v>0</v>
-      </c>
-      <c r="K6" s="33" t="str">
+      <c r="J6" s="32" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L6" s="35">
-        <f>RAWDATA!L6</f>
-        <v>0</v>
-      </c>
-      <c r="M6" s="4"/>
-      <c r="N6" s="22"/>
-      <c r="O6" s="2">
+      <c r="K6" s="4"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P6" s="2">
+      <c r="N6" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q6" s="11">
+      <c r="O6" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R6" s="1">
+      <c r="P6" s="1">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S6" s="1">
+      <c r="Q6" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" s="29">
         <f>RAWDATA!B7</f>
         <v>0</v>
@@ -3083,7 +2985,7 @@
         <f>RAWDATA!E7</f>
         <v>0</v>
       </c>
-      <c r="E7" s="34">
+      <c r="E7" s="33">
         <f>RAWDATA!F7</f>
         <v>0</v>
       </c>
@@ -3092,50 +2994,42 @@
         <v>KP</v>
       </c>
       <c r="G7" s="4"/>
-      <c r="H7" s="89">
+      <c r="H7" s="86">
         <f>RAWDATA!J7</f>
         <v>0</v>
       </c>
-      <c r="I7" s="88">
+      <c r="I7" s="85">
         <f>RAWDATA!G7</f>
         <v>0</v>
       </c>
-      <c r="J7" s="35">
-        <f>RAWDATA!K7</f>
-        <v>0</v>
-      </c>
-      <c r="K7" s="33" t="str">
+      <c r="J7" s="32" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L7" s="35">
-        <f>RAWDATA!L7</f>
-        <v>0</v>
-      </c>
-      <c r="M7" s="4"/>
-      <c r="N7" s="22"/>
-      <c r="O7" s="2">
+      <c r="K7" s="4"/>
+      <c r="L7" s="22"/>
+      <c r="M7" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P7" s="2">
+      <c r="N7" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q7" s="11">
+      <c r="O7" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R7" s="1">
+      <c r="P7" s="1">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S7" s="1">
+      <c r="Q7" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" s="29">
         <f>RAWDATA!B8</f>
         <v>0</v>
@@ -3152,7 +3046,7 @@
         <f>RAWDATA!E8</f>
         <v>0</v>
       </c>
-      <c r="E8" s="34">
+      <c r="E8" s="33">
         <f>RAWDATA!F8</f>
         <v>0</v>
       </c>
@@ -3161,50 +3055,42 @@
         <v>KP</v>
       </c>
       <c r="G8" s="4"/>
-      <c r="H8" s="89">
+      <c r="H8" s="86">
         <f>RAWDATA!J8</f>
         <v>0</v>
       </c>
-      <c r="I8" s="88">
+      <c r="I8" s="85">
         <f>RAWDATA!G8</f>
         <v>0</v>
       </c>
-      <c r="J8" s="35">
-        <f>RAWDATA!K8</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="33" t="str">
+      <c r="J8" s="32" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L8" s="35">
-        <f>RAWDATA!L8</f>
-        <v>0</v>
-      </c>
-      <c r="M8" s="4"/>
-      <c r="N8" s="22"/>
-      <c r="O8" s="2">
+      <c r="K8" s="4"/>
+      <c r="L8" s="22"/>
+      <c r="M8" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P8" s="2">
+      <c r="N8" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q8" s="11">
+      <c r="O8" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R8" s="1">
+      <c r="P8" s="1">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S8" s="1">
+      <c r="Q8" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" s="29">
         <f>RAWDATA!B9</f>
         <v>0</v>
@@ -3221,7 +3107,7 @@
         <f>RAWDATA!E9</f>
         <v>0</v>
       </c>
-      <c r="E9" s="34">
+      <c r="E9" s="33">
         <f>RAWDATA!F9</f>
         <v>0</v>
       </c>
@@ -3230,50 +3116,42 @@
         <v>KP</v>
       </c>
       <c r="G9" s="4"/>
-      <c r="H9" s="89">
+      <c r="H9" s="86">
         <f>RAWDATA!J9</f>
         <v>0</v>
       </c>
-      <c r="I9" s="88">
+      <c r="I9" s="85">
         <f>RAWDATA!G9</f>
         <v>0</v>
       </c>
-      <c r="J9" s="35">
-        <f>RAWDATA!K9</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="33" t="str">
+      <c r="J9" s="32" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L9" s="35">
-        <f>RAWDATA!L9</f>
-        <v>0</v>
-      </c>
-      <c r="M9" s="4"/>
-      <c r="N9" s="22"/>
-      <c r="O9" s="2">
+      <c r="K9" s="4"/>
+      <c r="L9" s="22"/>
+      <c r="M9" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P9" s="2">
+      <c r="N9" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q9" s="11">
+      <c r="O9" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R9" s="1">
+      <c r="P9" s="1">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S9" s="1">
+      <c r="Q9" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" s="29">
         <f>RAWDATA!B10</f>
         <v>0</v>
@@ -3290,7 +3168,7 @@
         <f>RAWDATA!E10</f>
         <v>0</v>
       </c>
-      <c r="E10" s="34">
+      <c r="E10" s="33">
         <f>RAWDATA!F10</f>
         <v>0</v>
       </c>
@@ -3299,50 +3177,42 @@
         <v>KP</v>
       </c>
       <c r="G10" s="4"/>
-      <c r="H10" s="89">
+      <c r="H10" s="86">
         <f>RAWDATA!J10</f>
         <v>0</v>
       </c>
-      <c r="I10" s="88">
+      <c r="I10" s="85">
         <f>RAWDATA!G10</f>
         <v>0</v>
       </c>
-      <c r="J10" s="35">
-        <f>RAWDATA!K10</f>
-        <v>0</v>
-      </c>
-      <c r="K10" s="33" t="str">
+      <c r="J10" s="32" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L10" s="35">
-        <f>RAWDATA!L10</f>
-        <v>0</v>
-      </c>
-      <c r="M10" s="4"/>
-      <c r="N10" s="22"/>
-      <c r="O10" s="2">
+      <c r="K10" s="4"/>
+      <c r="L10" s="22"/>
+      <c r="M10" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P10" s="2">
+      <c r="N10" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q10" s="11">
+      <c r="O10" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R10" s="1">
+      <c r="P10" s="1">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S10" s="1">
+      <c r="Q10" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" s="29">
         <f>RAWDATA!B11</f>
         <v>0</v>
@@ -3359,7 +3229,7 @@
         <f>RAWDATA!E11</f>
         <v>0</v>
       </c>
-      <c r="E11" s="34">
+      <c r="E11" s="33">
         <f>RAWDATA!F11</f>
         <v>0</v>
       </c>
@@ -3368,50 +3238,42 @@
         <v>KP</v>
       </c>
       <c r="G11" s="4"/>
-      <c r="H11" s="89">
+      <c r="H11" s="86">
         <f>RAWDATA!J11</f>
         <v>0</v>
       </c>
-      <c r="I11" s="88">
+      <c r="I11" s="85">
         <f>RAWDATA!G11</f>
         <v>0</v>
       </c>
-      <c r="J11" s="35">
-        <f>RAWDATA!K11</f>
-        <v>0</v>
-      </c>
-      <c r="K11" s="33" t="str">
+      <c r="J11" s="32" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L11" s="35">
-        <f>RAWDATA!L11</f>
-        <v>0</v>
-      </c>
-      <c r="M11" s="4"/>
-      <c r="N11" s="22"/>
-      <c r="O11" s="2">
+      <c r="K11" s="4"/>
+      <c r="L11" s="22"/>
+      <c r="M11" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P11" s="2">
+      <c r="N11" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q11" s="11">
+      <c r="O11" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R11" s="1">
+      <c r="P11" s="1">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S11" s="1">
+      <c r="Q11" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" s="29">
         <f>RAWDATA!B12</f>
         <v>0</v>
@@ -3428,7 +3290,7 @@
         <f>RAWDATA!E12</f>
         <v>0</v>
       </c>
-      <c r="E12" s="34">
+      <c r="E12" s="33">
         <f>RAWDATA!F12</f>
         <v>0</v>
       </c>
@@ -3437,50 +3299,42 @@
         <v>KP</v>
       </c>
       <c r="G12" s="4"/>
-      <c r="H12" s="89">
+      <c r="H12" s="86">
         <f>RAWDATA!J12</f>
         <v>0</v>
       </c>
-      <c r="I12" s="88">
+      <c r="I12" s="85">
         <f>RAWDATA!G12</f>
         <v>0</v>
       </c>
-      <c r="J12" s="35">
-        <f>RAWDATA!K12</f>
-        <v>0</v>
-      </c>
-      <c r="K12" s="33" t="str">
+      <c r="J12" s="32" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L12" s="35">
-        <f>RAWDATA!L12</f>
-        <v>0</v>
-      </c>
-      <c r="M12" s="4"/>
-      <c r="N12" s="22"/>
-      <c r="O12" s="2">
+      <c r="K12" s="4"/>
+      <c r="L12" s="22"/>
+      <c r="M12" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P12" s="2">
+      <c r="N12" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q12" s="11">
+      <c r="O12" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R12" s="1">
+      <c r="P12" s="1">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S12" s="1">
+      <c r="Q12" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" s="29">
         <f>RAWDATA!B13</f>
         <v>0</v>
@@ -3497,7 +3351,7 @@
         <f>RAWDATA!E13</f>
         <v>0</v>
       </c>
-      <c r="E13" s="34">
+      <c r="E13" s="33">
         <f>RAWDATA!F13</f>
         <v>0</v>
       </c>
@@ -3506,50 +3360,42 @@
         <v>KP</v>
       </c>
       <c r="G13" s="4"/>
-      <c r="H13" s="89">
+      <c r="H13" s="86">
         <f>RAWDATA!J13</f>
         <v>0</v>
       </c>
-      <c r="I13" s="88">
+      <c r="I13" s="85">
         <f>RAWDATA!G13</f>
         <v>0</v>
       </c>
-      <c r="J13" s="35">
-        <f>RAWDATA!K13</f>
-        <v>0</v>
-      </c>
-      <c r="K13" s="33" t="str">
+      <c r="J13" s="32" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L13" s="35">
-        <f>RAWDATA!L13</f>
-        <v>0</v>
-      </c>
-      <c r="M13" s="4"/>
-      <c r="N13" s="22"/>
-      <c r="O13" s="2">
+      <c r="K13" s="4"/>
+      <c r="L13" s="22"/>
+      <c r="M13" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P13" s="2">
+      <c r="N13" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q13" s="11">
+      <c r="O13" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R13" s="1">
+      <c r="P13" s="1">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S13" s="1">
+      <c r="Q13" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" s="29">
         <f>RAWDATA!B14</f>
         <v>0</v>
@@ -3566,7 +3412,7 @@
         <f>RAWDATA!E14</f>
         <v>0</v>
       </c>
-      <c r="E14" s="34">
+      <c r="E14" s="33">
         <f>RAWDATA!F14</f>
         <v>0</v>
       </c>
@@ -3575,50 +3421,42 @@
         <v>KP</v>
       </c>
       <c r="G14" s="4"/>
-      <c r="H14" s="89">
+      <c r="H14" s="86">
         <f>RAWDATA!J14</f>
         <v>0</v>
       </c>
-      <c r="I14" s="88">
+      <c r="I14" s="85">
         <f>RAWDATA!G14</f>
         <v>0</v>
       </c>
-      <c r="J14" s="35">
-        <f>RAWDATA!K14</f>
-        <v>0</v>
-      </c>
-      <c r="K14" s="33" t="str">
+      <c r="J14" s="32" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L14" s="35">
-        <f>RAWDATA!L14</f>
-        <v>0</v>
-      </c>
-      <c r="M14" s="4"/>
-      <c r="N14" s="22"/>
-      <c r="O14" s="2">
+      <c r="K14" s="4"/>
+      <c r="L14" s="22"/>
+      <c r="M14" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P14" s="2">
+      <c r="N14" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q14" s="11">
+      <c r="O14" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R14" s="1">
+      <c r="P14" s="1">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S14" s="1">
+      <c r="Q14" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" s="29">
         <f>RAWDATA!B15</f>
         <v>0</v>
@@ -3635,7 +3473,7 @@
         <f>RAWDATA!E15</f>
         <v>0</v>
       </c>
-      <c r="E15" s="34">
+      <c r="E15" s="33">
         <f>RAWDATA!F15</f>
         <v>0</v>
       </c>
@@ -3644,50 +3482,42 @@
         <v>KP</v>
       </c>
       <c r="G15" s="4"/>
-      <c r="H15" s="89">
+      <c r="H15" s="86">
         <f>RAWDATA!J15</f>
         <v>0</v>
       </c>
-      <c r="I15" s="88">
+      <c r="I15" s="85">
         <f>RAWDATA!G15</f>
         <v>0</v>
       </c>
-      <c r="J15" s="35">
-        <f>RAWDATA!K15</f>
-        <v>0</v>
-      </c>
-      <c r="K15" s="33" t="str">
+      <c r="J15" s="32" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L15" s="35">
-        <f>RAWDATA!L15</f>
-        <v>0</v>
-      </c>
-      <c r="M15" s="4"/>
-      <c r="N15" s="22"/>
-      <c r="O15" s="2">
+      <c r="K15" s="4"/>
+      <c r="L15" s="22"/>
+      <c r="M15" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P15" s="2">
+      <c r="N15" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q15" s="11">
+      <c r="O15" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R15" s="1">
+      <c r="P15" s="1">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S15" s="1">
+      <c r="Q15" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" s="29">
         <f>RAWDATA!B16</f>
         <v>0</v>
@@ -3704,7 +3534,7 @@
         <f>RAWDATA!E16</f>
         <v>0</v>
       </c>
-      <c r="E16" s="34">
+      <c r="E16" s="33">
         <f>RAWDATA!F16</f>
         <v>0</v>
       </c>
@@ -3713,50 +3543,42 @@
         <v>KP</v>
       </c>
       <c r="G16" s="4"/>
-      <c r="H16" s="89">
+      <c r="H16" s="86">
         <f>RAWDATA!J16</f>
         <v>0</v>
       </c>
-      <c r="I16" s="88">
+      <c r="I16" s="85">
         <f>RAWDATA!G16</f>
         <v>0</v>
       </c>
-      <c r="J16" s="35">
-        <f>RAWDATA!K16</f>
-        <v>0</v>
-      </c>
-      <c r="K16" s="33" t="str">
+      <c r="J16" s="32" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L16" s="35">
-        <f>RAWDATA!L16</f>
-        <v>0</v>
-      </c>
-      <c r="M16" s="4"/>
-      <c r="N16" s="22"/>
-      <c r="O16" s="2">
+      <c r="K16" s="4"/>
+      <c r="L16" s="22"/>
+      <c r="M16" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P16" s="2">
+      <c r="N16" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q16" s="11">
+      <c r="O16" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R16" s="1">
+      <c r="P16" s="1">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S16" s="1">
+      <c r="Q16" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" s="29">
         <f>RAWDATA!B17</f>
         <v>0</v>
@@ -3773,7 +3595,7 @@
         <f>RAWDATA!E17</f>
         <v>0</v>
       </c>
-      <c r="E17" s="34">
+      <c r="E17" s="33">
         <f>RAWDATA!F17</f>
         <v>0</v>
       </c>
@@ -3782,50 +3604,42 @@
         <v>KP</v>
       </c>
       <c r="G17" s="4"/>
-      <c r="H17" s="89">
+      <c r="H17" s="86">
         <f>RAWDATA!J17</f>
         <v>0</v>
       </c>
-      <c r="I17" s="88">
+      <c r="I17" s="85">
         <f>RAWDATA!G17</f>
         <v>0</v>
       </c>
-      <c r="J17" s="35">
-        <f>RAWDATA!K17</f>
-        <v>0</v>
-      </c>
-      <c r="K17" s="33" t="str">
+      <c r="J17" s="32" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L17" s="35">
-        <f>RAWDATA!L17</f>
-        <v>0</v>
-      </c>
-      <c r="M17" s="4"/>
-      <c r="N17" s="22"/>
-      <c r="O17" s="2">
+      <c r="K17" s="4"/>
+      <c r="L17" s="22"/>
+      <c r="M17" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P17" s="2">
+      <c r="N17" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q17" s="11">
+      <c r="O17" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R17" s="1">
+      <c r="P17" s="1">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S17" s="1">
+      <c r="Q17" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" s="29">
         <f>RAWDATA!B18</f>
         <v>0</v>
@@ -3842,7 +3656,7 @@
         <f>RAWDATA!E18</f>
         <v>0</v>
       </c>
-      <c r="E18" s="34">
+      <c r="E18" s="33">
         <f>RAWDATA!F18</f>
         <v>0</v>
       </c>
@@ -3851,50 +3665,42 @@
         <v>KP</v>
       </c>
       <c r="G18" s="4"/>
-      <c r="H18" s="89">
+      <c r="H18" s="86">
         <f>RAWDATA!J18</f>
         <v>0</v>
       </c>
-      <c r="I18" s="88">
+      <c r="I18" s="85">
         <f>RAWDATA!G18</f>
         <v>0</v>
       </c>
-      <c r="J18" s="35">
-        <f>RAWDATA!K18</f>
-        <v>0</v>
-      </c>
-      <c r="K18" s="33" t="str">
+      <c r="J18" s="32" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L18" s="35">
-        <f>RAWDATA!L18</f>
-        <v>0</v>
-      </c>
-      <c r="M18" s="4"/>
-      <c r="N18" s="22"/>
-      <c r="O18" s="2">
+      <c r="K18" s="4"/>
+      <c r="L18" s="22"/>
+      <c r="M18" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P18" s="2">
+      <c r="N18" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q18" s="11">
+      <c r="O18" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R18" s="1">
+      <c r="P18" s="1">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S18" s="1">
+      <c r="Q18" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" s="29">
         <f>RAWDATA!B19</f>
         <v>0</v>
@@ -3911,7 +3717,7 @@
         <f>RAWDATA!E19</f>
         <v>0</v>
       </c>
-      <c r="E19" s="34">
+      <c r="E19" s="33">
         <f>RAWDATA!F19</f>
         <v>0</v>
       </c>
@@ -3920,50 +3726,42 @@
         <v>KP</v>
       </c>
       <c r="G19" s="4"/>
-      <c r="H19" s="89">
+      <c r="H19" s="86">
         <f>RAWDATA!J19</f>
         <v>0</v>
       </c>
-      <c r="I19" s="88">
+      <c r="I19" s="85">
         <f>RAWDATA!G19</f>
         <v>0</v>
       </c>
-      <c r="J19" s="35">
-        <f>RAWDATA!K19</f>
-        <v>0</v>
-      </c>
-      <c r="K19" s="33" t="str">
+      <c r="J19" s="32" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L19" s="35">
-        <f>RAWDATA!L19</f>
-        <v>0</v>
-      </c>
-      <c r="M19" s="4"/>
-      <c r="N19" s="22"/>
-      <c r="O19" s="2">
+      <c r="K19" s="4"/>
+      <c r="L19" s="22"/>
+      <c r="M19" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P19" s="2">
+      <c r="N19" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q19" s="11">
+      <c r="O19" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R19" s="1">
+      <c r="P19" s="1">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S19" s="1">
+      <c r="Q19" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" s="29">
         <f>RAWDATA!B20</f>
         <v>0</v>
@@ -3980,7 +3778,7 @@
         <f>RAWDATA!E20</f>
         <v>0</v>
       </c>
-      <c r="E20" s="34">
+      <c r="E20" s="33">
         <f>RAWDATA!F20</f>
         <v>0</v>
       </c>
@@ -3989,50 +3787,42 @@
         <v>KP</v>
       </c>
       <c r="G20" s="4"/>
-      <c r="H20" s="89">
+      <c r="H20" s="86">
         <f>RAWDATA!J20</f>
         <v>0</v>
       </c>
-      <c r="I20" s="88">
+      <c r="I20" s="85">
         <f>RAWDATA!G20</f>
         <v>0</v>
       </c>
-      <c r="J20" s="35">
-        <f>RAWDATA!K20</f>
-        <v>0</v>
-      </c>
-      <c r="K20" s="33" t="str">
+      <c r="J20" s="32" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L20" s="35">
-        <f>RAWDATA!L20</f>
-        <v>0</v>
-      </c>
-      <c r="M20" s="4"/>
-      <c r="N20" s="22"/>
-      <c r="O20" s="2">
+      <c r="K20" s="4"/>
+      <c r="L20" s="22"/>
+      <c r="M20" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P20" s="2">
+      <c r="N20" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q20" s="11">
+      <c r="O20" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R20" s="1">
+      <c r="P20" s="1">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S20" s="1">
+      <c r="Q20" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" s="29">
         <f>RAWDATA!B21</f>
         <v>0</v>
@@ -4049,7 +3839,7 @@
         <f>RAWDATA!E21</f>
         <v>0</v>
       </c>
-      <c r="E21" s="34">
+      <c r="E21" s="33">
         <f>RAWDATA!F21</f>
         <v>0</v>
       </c>
@@ -4058,50 +3848,42 @@
         <v>KP</v>
       </c>
       <c r="G21" s="4"/>
-      <c r="H21" s="89">
+      <c r="H21" s="86">
         <f>RAWDATA!J21</f>
         <v>0</v>
       </c>
-      <c r="I21" s="88">
+      <c r="I21" s="85">
         <f>RAWDATA!G21</f>
         <v>0</v>
       </c>
-      <c r="J21" s="35">
-        <f>RAWDATA!K21</f>
-        <v>0</v>
-      </c>
-      <c r="K21" s="33" t="str">
+      <c r="J21" s="32" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L21" s="35">
-        <f>RAWDATA!L21</f>
-        <v>0</v>
-      </c>
-      <c r="M21" s="4"/>
-      <c r="N21" s="22"/>
-      <c r="O21" s="2">
+      <c r="K21" s="4"/>
+      <c r="L21" s="22"/>
+      <c r="M21" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P21" s="2">
+      <c r="N21" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q21" s="11">
+      <c r="O21" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R21" s="1">
+      <c r="P21" s="1">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S21" s="1">
+      <c r="Q21" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22" s="29">
         <f>RAWDATA!B22</f>
         <v>0</v>
@@ -4118,7 +3900,7 @@
         <f>RAWDATA!E22</f>
         <v>0</v>
       </c>
-      <c r="E22" s="34">
+      <c r="E22" s="33">
         <f>RAWDATA!F22</f>
         <v>0</v>
       </c>
@@ -4127,50 +3909,42 @@
         <v>KP</v>
       </c>
       <c r="G22" s="4"/>
-      <c r="H22" s="89">
+      <c r="H22" s="86">
         <f>RAWDATA!J22</f>
         <v>0</v>
       </c>
-      <c r="I22" s="88">
+      <c r="I22" s="85">
         <f>RAWDATA!G22</f>
         <v>0</v>
       </c>
-      <c r="J22" s="35">
-        <f>RAWDATA!K22</f>
-        <v>0</v>
-      </c>
-      <c r="K22" s="33" t="str">
+      <c r="J22" s="32" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L22" s="35">
-        <f>RAWDATA!L22</f>
-        <v>0</v>
-      </c>
-      <c r="M22" s="4"/>
-      <c r="N22" s="22"/>
-      <c r="O22" s="2">
+      <c r="K22" s="4"/>
+      <c r="L22" s="22"/>
+      <c r="M22" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P22" s="2">
+      <c r="N22" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q22" s="11">
+      <c r="O22" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R22" s="1">
+      <c r="P22" s="1">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S22" s="1">
+      <c r="Q22" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" s="29">
         <f>RAWDATA!B23</f>
         <v>0</v>
@@ -4187,7 +3961,7 @@
         <f>RAWDATA!E23</f>
         <v>0</v>
       </c>
-      <c r="E23" s="34">
+      <c r="E23" s="33">
         <f>RAWDATA!F23</f>
         <v>0</v>
       </c>
@@ -4196,50 +3970,42 @@
         <v>KP</v>
       </c>
       <c r="G23" s="4"/>
-      <c r="H23" s="89">
+      <c r="H23" s="86">
         <f>RAWDATA!J23</f>
         <v>0</v>
       </c>
-      <c r="I23" s="88">
+      <c r="I23" s="85">
         <f>RAWDATA!G23</f>
         <v>0</v>
       </c>
-      <c r="J23" s="35">
-        <f>RAWDATA!K23</f>
-        <v>0</v>
-      </c>
-      <c r="K23" s="33" t="str">
+      <c r="J23" s="32" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L23" s="35">
-        <f>RAWDATA!L23</f>
-        <v>0</v>
-      </c>
-      <c r="M23" s="4"/>
-      <c r="N23" s="22"/>
-      <c r="O23" s="2">
+      <c r="K23" s="4"/>
+      <c r="L23" s="22"/>
+      <c r="M23" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P23" s="2">
+      <c r="N23" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q23" s="11">
+      <c r="O23" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R23" s="1">
+      <c r="P23" s="1">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S23" s="1">
+      <c r="Q23" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" s="29">
         <f>RAWDATA!B24</f>
         <v>0</v>
@@ -4256,7 +4022,7 @@
         <f>RAWDATA!E24</f>
         <v>0</v>
       </c>
-      <c r="E24" s="34">
+      <c r="E24" s="33">
         <f>RAWDATA!F24</f>
         <v>0</v>
       </c>
@@ -4265,50 +4031,42 @@
         <v>KP</v>
       </c>
       <c r="G24" s="4"/>
-      <c r="H24" s="89">
+      <c r="H24" s="86">
         <f>RAWDATA!J24</f>
         <v>0</v>
       </c>
-      <c r="I24" s="88">
+      <c r="I24" s="85">
         <f>RAWDATA!G24</f>
         <v>0</v>
       </c>
-      <c r="J24" s="35">
-        <f>RAWDATA!K24</f>
-        <v>0</v>
-      </c>
-      <c r="K24" s="33" t="str">
+      <c r="J24" s="32" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L24" s="35">
-        <f>RAWDATA!L24</f>
-        <v>0</v>
-      </c>
-      <c r="M24" s="4"/>
-      <c r="N24" s="22"/>
-      <c r="O24" s="2">
+      <c r="K24" s="4"/>
+      <c r="L24" s="22"/>
+      <c r="M24" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P24" s="2">
+      <c r="N24" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q24" s="11">
+      <c r="O24" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R24" s="1">
+      <c r="P24" s="1">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S24" s="1">
+      <c r="Q24" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" s="29">
         <f>RAWDATA!B25</f>
         <v>0</v>
@@ -4325,7 +4083,7 @@
         <f>RAWDATA!E25</f>
         <v>0</v>
       </c>
-      <c r="E25" s="34">
+      <c r="E25" s="33">
         <f>RAWDATA!F25</f>
         <v>0</v>
       </c>
@@ -4334,50 +4092,42 @@
         <v>KP</v>
       </c>
       <c r="G25" s="4"/>
-      <c r="H25" s="89">
+      <c r="H25" s="86">
         <f>RAWDATA!J25</f>
         <v>0</v>
       </c>
-      <c r="I25" s="88">
+      <c r="I25" s="85">
         <f>RAWDATA!G25</f>
         <v>0</v>
       </c>
-      <c r="J25" s="35">
-        <f>RAWDATA!K25</f>
-        <v>0</v>
-      </c>
-      <c r="K25" s="33" t="str">
+      <c r="J25" s="32" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L25" s="35">
-        <f>RAWDATA!L25</f>
-        <v>0</v>
-      </c>
-      <c r="M25" s="4"/>
-      <c r="N25" s="22"/>
-      <c r="O25" s="2">
+      <c r="K25" s="4"/>
+      <c r="L25" s="22"/>
+      <c r="M25" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P25" s="2">
+      <c r="N25" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q25" s="11">
+      <c r="O25" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R25" s="1">
+      <c r="P25" s="1">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S25" s="1">
+      <c r="Q25" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" s="29">
         <f>RAWDATA!B26</f>
         <v>0</v>
@@ -4394,7 +4144,7 @@
         <f>RAWDATA!E26</f>
         <v>0</v>
       </c>
-      <c r="E26" s="34">
+      <c r="E26" s="33">
         <f>RAWDATA!F26</f>
         <v>0</v>
       </c>
@@ -4403,50 +4153,42 @@
         <v>KP</v>
       </c>
       <c r="G26" s="4"/>
-      <c r="H26" s="89">
+      <c r="H26" s="86">
         <f>RAWDATA!J26</f>
         <v>0</v>
       </c>
-      <c r="I26" s="88">
+      <c r="I26" s="85">
         <f>RAWDATA!G26</f>
         <v>0</v>
       </c>
-      <c r="J26" s="35">
-        <f>RAWDATA!K26</f>
-        <v>0</v>
-      </c>
-      <c r="K26" s="33" t="str">
+      <c r="J26" s="32" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L26" s="35">
-        <f>RAWDATA!L26</f>
-        <v>0</v>
-      </c>
-      <c r="M26" s="4"/>
-      <c r="N26" s="22"/>
-      <c r="O26" s="2">
+      <c r="K26" s="4"/>
+      <c r="L26" s="22"/>
+      <c r="M26" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P26" s="2">
+      <c r="N26" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q26" s="11">
+      <c r="O26" s="11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R26" s="1">
+      <c r="P26" s="1">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S26" s="1">
+      <c r="Q26" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" s="4"/>
       <c r="B27" s="4" t="s">
         <v>10</v>
@@ -4458,13 +4200,11 @@
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
       <c r="I27" s="5"/>
-      <c r="J27" s="4"/>
-      <c r="K27" s="5"/>
-      <c r="L27" s="4"/>
-      <c r="M27" s="4"/>
-      <c r="N27" s="22"/>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="J27" s="5"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="22"/>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B28" s="1" t="s">
         <v>25</v>
       </c>
@@ -4475,13 +4215,11 @@
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
       <c r="I28" s="5"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="5"/>
-      <c r="L28" s="4"/>
-      <c r="M28" s="4"/>
-      <c r="N28" s="22"/>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="J28" s="5"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="22"/>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" s="4"/>
       <c r="B29" s="4" t="s">
         <v>11</v>
@@ -4496,13 +4234,11 @@
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
       <c r="I29" s="5"/>
-      <c r="J29" s="4"/>
-      <c r="K29" s="5"/>
-      <c r="L29" s="4"/>
-      <c r="M29" s="4"/>
-      <c r="N29" s="22"/>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="J29" s="5"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="22"/>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A30" s="22"/>
       <c r="B30" s="22"/>
       <c r="C30" s="23"/>
@@ -4512,201 +4248,185 @@
       <c r="G30" s="22"/>
       <c r="H30" s="22"/>
       <c r="I30" s="25"/>
-      <c r="J30" s="22"/>
-      <c r="K30" s="25"/>
+      <c r="J30" s="25"/>
+      <c r="K30" s="22"/>
       <c r="L30" s="22"/>
-      <c r="M30" s="22"/>
-      <c r="N30" s="22"/>
-    </row>
-    <row r="31" spans="1:19" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C31" s="23"/>
-      <c r="D31" s="90" t="s">
-        <v>78</v>
-      </c>
-      <c r="E31" s="90"/>
-      <c r="F31" s="90"/>
-      <c r="G31" s="90"/>
-      <c r="H31" s="86"/>
+      <c r="D31" s="87" t="s">
+        <v>74</v>
+      </c>
+      <c r="E31" s="87"/>
+      <c r="F31" s="87"/>
+      <c r="G31" s="87"/>
+      <c r="H31" s="83"/>
       <c r="I31" s="25"/>
-      <c r="J31" s="31"/>
-      <c r="K31" s="25"/>
-      <c r="L31" s="31"/>
-      <c r="M31" s="31"/>
-      <c r="N31" s="22"/>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="J31" s="25"/>
+      <c r="K31" s="31"/>
+      <c r="L31" s="22"/>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B32" s="36" t="s">
-        <v>106</v>
+      <c r="B32" s="34" t="s">
+        <v>102</v>
       </c>
       <c r="C32" s="23"/>
-      <c r="D32" s="90"/>
-      <c r="E32" s="90"/>
-      <c r="F32" s="90"/>
-      <c r="G32" s="90"/>
-      <c r="H32" s="86"/>
+      <c r="D32" s="87"/>
+      <c r="E32" s="87"/>
+      <c r="F32" s="87"/>
+      <c r="G32" s="87"/>
+      <c r="H32" s="83"/>
       <c r="I32" s="25"/>
-      <c r="J32" s="31"/>
-      <c r="K32" s="25"/>
-      <c r="L32" s="31"/>
-      <c r="M32" s="31"/>
-      <c r="N32" s="22"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J32" s="25"/>
+      <c r="K32" s="31"/>
+      <c r="L32" s="22"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B33" s="36" t="s">
-        <v>107</v>
+      <c r="B33" s="34" t="s">
+        <v>103</v>
       </c>
       <c r="C33" s="23"/>
-      <c r="D33" s="90"/>
-      <c r="E33" s="90"/>
-      <c r="F33" s="90"/>
-      <c r="G33" s="90"/>
-      <c r="H33" s="86"/>
+      <c r="D33" s="87"/>
+      <c r="E33" s="87"/>
+      <c r="F33" s="87"/>
+      <c r="G33" s="87"/>
+      <c r="H33" s="83"/>
       <c r="I33" s="25"/>
-      <c r="J33" s="31"/>
-      <c r="K33" s="25"/>
-      <c r="L33" s="31"/>
-      <c r="M33" s="31"/>
-      <c r="N33" s="22"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J33" s="25"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="22"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>17</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C34" s="23"/>
-      <c r="D34" s="90"/>
-      <c r="E34" s="90"/>
-      <c r="F34" s="90"/>
-      <c r="G34" s="90"/>
-      <c r="H34" s="86"/>
+      <c r="D34" s="87"/>
+      <c r="E34" s="87"/>
+      <c r="F34" s="87"/>
+      <c r="G34" s="87"/>
+      <c r="H34" s="83"/>
       <c r="I34" s="25"/>
-      <c r="J34" s="31"/>
-      <c r="K34" s="25"/>
-      <c r="L34" s="31"/>
-      <c r="M34" s="31"/>
-      <c r="N34" s="22"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J34" s="25"/>
+      <c r="K34" s="31"/>
+      <c r="L34" s="22"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C35" s="23"/>
-      <c r="D35" s="90"/>
-      <c r="E35" s="90"/>
-      <c r="F35" s="90"/>
-      <c r="G35" s="90"/>
-      <c r="H35" s="86"/>
+      <c r="D35" s="87"/>
+      <c r="E35" s="87"/>
+      <c r="F35" s="87"/>
+      <c r="G35" s="87"/>
+      <c r="H35" s="83"/>
       <c r="I35" s="25"/>
-      <c r="J35" s="31"/>
-      <c r="K35" s="25"/>
-      <c r="L35" s="31"/>
-      <c r="M35" s="31"/>
-      <c r="N35" s="22"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J35" s="25"/>
+      <c r="K35" s="31"/>
+      <c r="L35" s="22"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C36" s="23"/>
-      <c r="D36" s="90"/>
-      <c r="E36" s="90"/>
-      <c r="F36" s="90"/>
-      <c r="G36" s="90"/>
-      <c r="H36" s="86"/>
+      <c r="D36" s="87"/>
+      <c r="E36" s="87"/>
+      <c r="F36" s="87"/>
+      <c r="G36" s="87"/>
+      <c r="H36" s="83"/>
       <c r="I36" s="25"/>
-      <c r="J36" s="31"/>
-      <c r="K36" s="25"/>
-      <c r="L36" s="31"/>
-      <c r="M36" s="31"/>
-      <c r="N36" s="22"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J36" s="25"/>
+      <c r="K36" s="31"/>
+      <c r="L36" s="22"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B37" s="63" t="s">
-        <v>109</v>
+        <v>50</v>
+      </c>
+      <c r="B37" s="60" t="s">
+        <v>105</v>
       </c>
       <c r="C37" s="23"/>
-      <c r="D37" s="90"/>
-      <c r="E37" s="90"/>
-      <c r="F37" s="90"/>
-      <c r="G37" s="90"/>
-      <c r="H37" s="86"/>
+      <c r="D37" s="87"/>
+      <c r="E37" s="87"/>
+      <c r="F37" s="87"/>
+      <c r="G37" s="87"/>
+      <c r="H37" s="83"/>
       <c r="I37" s="25"/>
-      <c r="J37" s="22"/>
-      <c r="K37" s="25"/>
+      <c r="J37" s="25"/>
+      <c r="K37" s="22"/>
       <c r="L37" s="22"/>
-      <c r="M37" s="22"/>
-      <c r="N37" s="22"/>
-    </row>
-    <row r="41" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="56"/>
-    </row>
-    <row r="42" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="56"/>
-    </row>
-    <row r="43" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="56"/>
-    </row>
-    <row r="44" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="56"/>
-    </row>
-    <row r="45" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="56"/>
-    </row>
-    <row r="46" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="56"/>
-    </row>
-    <row r="47" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="56"/>
-    </row>
-    <row r="48" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="56"/>
-    </row>
-    <row r="52" spans="1:1" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="56"/>
-    </row>
-    <row r="53" spans="1:1" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="56"/>
-    </row>
-    <row r="54" spans="1:1" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="56"/>
-    </row>
-    <row r="55" spans="1:1" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="56"/>
-    </row>
-    <row r="56" spans="1:1" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="56"/>
-    </row>
-    <row r="57" spans="1:1" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="56"/>
-    </row>
-    <row r="58" spans="1:1" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="56"/>
-    </row>
-    <row r="59" spans="1:1" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="56"/>
+    </row>
+    <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="53"/>
+    </row>
+    <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="53"/>
+    </row>
+    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="53"/>
+    </row>
+    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="53"/>
+    </row>
+    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="53"/>
+    </row>
+    <row r="46" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="53"/>
+    </row>
+    <row r="47" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="53"/>
+    </row>
+    <row r="48" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="53"/>
+    </row>
+    <row r="52" spans="1:1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="53"/>
+    </row>
+    <row r="53" spans="1:1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="53"/>
+    </row>
+    <row r="54" spans="1:1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="53"/>
+    </row>
+    <row r="55" spans="1:1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="53"/>
+    </row>
+    <row r="56" spans="1:1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="53"/>
+    </row>
+    <row r="57" spans="1:1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="53"/>
+    </row>
+    <row r="58" spans="1:1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="53"/>
+    </row>
+    <row r="59" spans="1:1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="53"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" formatColumns="0" selectLockedCells="1"/>
@@ -4715,7 +4435,7 @@
     <mergeCell ref="D31:G37"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="1">
-    <dataValidation errorStyle="information" allowBlank="1" showErrorMessage="1" errorTitle="Inkorrekte Semesterangabe" error="Bitte wählen Sie aus der Dropdown-Liste aus._x000a__x000a_Ihre Eingabe wird nicht automatisch korrigiert." promptTitle="Semester" prompt="Bitte geben Sie das entsprechende Semester an. Wählen Sie aus der Dropdown-Liste." sqref="B36" xr:uid="{00000000-0002-0000-0100-000000000000}"/>
+    <dataValidation errorStyle="information" allowBlank="1" showErrorMessage="1" errorTitle="Inkorrekte Semesterangabe" error="Bitte wählen Sie aus der Dropdown-Liste aus._x000a__x000a_Ihre Eingabe wird nicht automatisch korrigiert." promptTitle="Semester" prompt="Bitte geben Sie das entsprechende Semester an. Wählen Sie aus der Dropdown-Liste." sqref="B36"/>
   </dataValidations>
   <pageMargins left="0.78740157480314965" right="0.78740157480314965" top="1.2598425196850394" bottom="1.0629921259842521" header="0.59055118110236227" footer="0.78740157480314965"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4733,38 +4453,38 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L30"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="12.44140625" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="9.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="16.88671875" customWidth="1"/>
-    <col min="11" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.6640625" customWidth="1"/>
+    <col min="10" max="10" width="16.85546875" customWidth="1"/>
+    <col min="11" max="11" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="84" t="str">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="81" t="str">
         <f>Notenliste!B34</f>
         <v>course.name</v>
       </c>
-      <c r="E1" s="91" t="s">
-        <v>121</v>
-      </c>
-      <c r="F1" s="91"/>
-      <c r="G1" s="91"/>
-      <c r="H1" s="91"/>
-      <c r="I1" s="82"/>
-      <c r="J1" s="83" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E1" s="88" t="s">
+        <v>117</v>
+      </c>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="80" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="26" t="s">
         <v>0</v>
       </c>
@@ -4777,30 +4497,30 @@
       <c r="D2" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="81" t="s">
+      <c r="E2" s="78" t="s">
+        <v>110</v>
+      </c>
+      <c r="F2" s="78" t="s">
+        <v>111</v>
+      </c>
+      <c r="G2" s="78" t="s">
+        <v>112</v>
+      </c>
+      <c r="H2" s="78" t="s">
+        <v>113</v>
+      </c>
+      <c r="I2" s="27" t="s">
+        <v>115</v>
+      </c>
+      <c r="J2" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="K2" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="F2" s="81" t="s">
-        <v>115</v>
-      </c>
-      <c r="G2" s="81" t="s">
-        <v>116</v>
-      </c>
-      <c r="H2" s="81" t="s">
-        <v>117</v>
-      </c>
-      <c r="I2" s="27" t="s">
-        <v>119</v>
-      </c>
-      <c r="J2" s="27" t="s">
-        <v>122</v>
-      </c>
-      <c r="K2" s="28" t="s">
-        <v>118</v>
-      </c>
       <c r="L2" s="4"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="29" t="str">
         <f>RAWDATA!B2</f>
         <v>applicant.last_name</v>
@@ -4817,22 +4537,22 @@
         <f>RAWDATA!E2</f>
         <v>applicant.tag</v>
       </c>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="85">
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="82">
         <f>SUM(E3:H3)</f>
         <v>0</v>
       </c>
-      <c r="J3" s="34"/>
+      <c r="J3" s="33"/>
       <c r="K3" s="30">
         <f>SUM(I3:J3)</f>
         <v>0</v>
       </c>
       <c r="L3" s="4"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="29">
         <f>RAWDATA!B3</f>
         <v>0</v>
@@ -4849,22 +4569,22 @@
         <f>RAWDATA!E3</f>
         <v>0</v>
       </c>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="85">
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="82">
         <f t="shared" ref="I4:I27" si="0">SUM(E4:H4)</f>
         <v>0</v>
       </c>
-      <c r="J4" s="34"/>
+      <c r="J4" s="33"/>
       <c r="K4" s="30">
         <f t="shared" ref="K4:K27" si="1">SUM(I4:J4)</f>
         <v>0</v>
       </c>
       <c r="L4" s="4"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="29">
         <f>RAWDATA!B4</f>
         <v>0</v>
@@ -4881,22 +4601,22 @@
         <f>RAWDATA!E4</f>
         <v>0</v>
       </c>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="85">
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="82">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J5" s="34"/>
+      <c r="J5" s="33"/>
       <c r="K5" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L5" s="4"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="29">
         <f>RAWDATA!B5</f>
         <v>0</v>
@@ -4913,22 +4633,22 @@
         <f>RAWDATA!E5</f>
         <v>0</v>
       </c>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
-      <c r="H6" s="34"/>
-      <c r="I6" s="85">
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="82">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J6" s="34"/>
+      <c r="J6" s="33"/>
       <c r="K6" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L6" s="4"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="29">
         <f>RAWDATA!B6</f>
         <v>0</v>
@@ -4945,22 +4665,22 @@
         <f>RAWDATA!E6</f>
         <v>0</v>
       </c>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="34"/>
-      <c r="I7" s="85">
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
+      <c r="I7" s="82">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J7" s="34"/>
+      <c r="J7" s="33"/>
       <c r="K7" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L7" s="4"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="29">
         <f>RAWDATA!B7</f>
         <v>0</v>
@@ -4977,22 +4697,22 @@
         <f>RAWDATA!E7</f>
         <v>0</v>
       </c>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="34"/>
-      <c r="H8" s="34"/>
-      <c r="I8" s="85">
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="82">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J8" s="34"/>
+      <c r="J8" s="33"/>
       <c r="K8" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L8" s="4"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="29">
         <f>RAWDATA!B8</f>
         <v>0</v>
@@ -5009,22 +4729,22 @@
         <f>RAWDATA!E8</f>
         <v>0</v>
       </c>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="85">
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
+      <c r="I9" s="82">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J9" s="34"/>
+      <c r="J9" s="33"/>
       <c r="K9" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L9" s="4"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="29">
         <f>RAWDATA!B9</f>
         <v>0</v>
@@ -5041,22 +4761,22 @@
         <f>RAWDATA!E9</f>
         <v>0</v>
       </c>
-      <c r="E10" s="34"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="34"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="85">
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="82">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J10" s="34"/>
+      <c r="J10" s="33"/>
       <c r="K10" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L10" s="4"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="29">
         <f>RAWDATA!B10</f>
         <v>0</v>
@@ -5073,22 +4793,22 @@
         <f>RAWDATA!E10</f>
         <v>0</v>
       </c>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
-      <c r="H11" s="34"/>
-      <c r="I11" s="85">
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="82">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J11" s="34"/>
+      <c r="J11" s="33"/>
       <c r="K11" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L11" s="4"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="29">
         <f>RAWDATA!B11</f>
         <v>0</v>
@@ -5105,22 +4825,22 @@
         <f>RAWDATA!E11</f>
         <v>0</v>
       </c>
-      <c r="E12" s="34"/>
-      <c r="F12" s="34"/>
-      <c r="G12" s="34"/>
-      <c r="H12" s="34"/>
-      <c r="I12" s="85">
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="82">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J12" s="34"/>
+      <c r="J12" s="33"/>
       <c r="K12" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L12" s="4"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="29">
         <f>RAWDATA!B12</f>
         <v>0</v>
@@ -5137,22 +4857,22 @@
         <f>RAWDATA!E12</f>
         <v>0</v>
       </c>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="85">
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="33"/>
+      <c r="I13" s="82">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J13" s="34"/>
+      <c r="J13" s="33"/>
       <c r="K13" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L13" s="4"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="29">
         <f>RAWDATA!B13</f>
         <v>0</v>
@@ -5169,22 +4889,22 @@
         <f>RAWDATA!E13</f>
         <v>0</v>
       </c>
-      <c r="E14" s="34"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="34"/>
-      <c r="H14" s="34"/>
-      <c r="I14" s="85">
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="82">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J14" s="34"/>
+      <c r="J14" s="33"/>
       <c r="K14" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L14" s="4"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="29">
         <f>RAWDATA!B14</f>
         <v>0</v>
@@ -5201,22 +4921,22 @@
         <f>RAWDATA!E14</f>
         <v>0</v>
       </c>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="85">
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="82">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J15" s="34"/>
+      <c r="J15" s="33"/>
       <c r="K15" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L15" s="4"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="29">
         <f>RAWDATA!B15</f>
         <v>0</v>
@@ -5233,22 +4953,22 @@
         <f>RAWDATA!E15</f>
         <v>0</v>
       </c>
-      <c r="E16" s="34"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="34"/>
-      <c r="H16" s="34"/>
-      <c r="I16" s="85">
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="82">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J16" s="34"/>
+      <c r="J16" s="33"/>
       <c r="K16" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L16" s="4"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="29">
         <f>RAWDATA!B16</f>
         <v>0</v>
@@ -5265,22 +4985,22 @@
         <f>RAWDATA!E16</f>
         <v>0</v>
       </c>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="34"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="85">
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="82">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J17" s="34"/>
+      <c r="J17" s="33"/>
       <c r="K17" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L17" s="4"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="29">
         <f>RAWDATA!B17</f>
         <v>0</v>
@@ -5297,22 +5017,22 @@
         <f>RAWDATA!E17</f>
         <v>0</v>
       </c>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="34"/>
-      <c r="H18" s="34"/>
-      <c r="I18" s="85">
+      <c r="E18" s="33"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="82">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J18" s="34"/>
+      <c r="J18" s="33"/>
       <c r="K18" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L18" s="4"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="29">
         <f>RAWDATA!B18</f>
         <v>0</v>
@@ -5329,22 +5049,22 @@
         <f>RAWDATA!E18</f>
         <v>0</v>
       </c>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="34"/>
-      <c r="I19" s="85">
+      <c r="E19" s="33"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="33"/>
+      <c r="H19" s="33"/>
+      <c r="I19" s="82">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J19" s="34"/>
+      <c r="J19" s="33"/>
       <c r="K19" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L19" s="4"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="29">
         <f>RAWDATA!B19</f>
         <v>0</v>
@@ -5361,22 +5081,22 @@
         <f>RAWDATA!E19</f>
         <v>0</v>
       </c>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="85">
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="82">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J20" s="34"/>
+      <c r="J20" s="33"/>
       <c r="K20" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L20" s="4"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="29">
         <f>RAWDATA!B20</f>
         <v>0</v>
@@ -5393,22 +5113,22 @@
         <f>RAWDATA!E20</f>
         <v>0</v>
       </c>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="34"/>
-      <c r="H21" s="34"/>
-      <c r="I21" s="85">
+      <c r="E21" s="33"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="33"/>
+      <c r="H21" s="33"/>
+      <c r="I21" s="82">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J21" s="34"/>
+      <c r="J21" s="33"/>
       <c r="K21" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L21" s="4"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="29">
         <f>RAWDATA!B21</f>
         <v>0</v>
@@ -5425,22 +5145,22 @@
         <f>RAWDATA!E21</f>
         <v>0</v>
       </c>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="34"/>
-      <c r="H22" s="34"/>
-      <c r="I22" s="85">
+      <c r="E22" s="33"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="33"/>
+      <c r="H22" s="33"/>
+      <c r="I22" s="82">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J22" s="34"/>
+      <c r="J22" s="33"/>
       <c r="K22" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L22" s="4"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="29">
         <f>RAWDATA!B22</f>
         <v>0</v>
@@ -5457,22 +5177,22 @@
         <f>RAWDATA!E22</f>
         <v>0</v>
       </c>
-      <c r="E23" s="34"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="34"/>
-      <c r="H23" s="34"/>
-      <c r="I23" s="85">
+      <c r="E23" s="33"/>
+      <c r="F23" s="33"/>
+      <c r="G23" s="33"/>
+      <c r="H23" s="33"/>
+      <c r="I23" s="82">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J23" s="34"/>
+      <c r="J23" s="33"/>
       <c r="K23" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L23" s="4"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="29">
         <f>RAWDATA!B23</f>
         <v>0</v>
@@ -5489,22 +5209,22 @@
         <f>RAWDATA!E23</f>
         <v>0</v>
       </c>
-      <c r="E24" s="34"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="34"/>
-      <c r="H24" s="34"/>
-      <c r="I24" s="85">
+      <c r="E24" s="33"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="33"/>
+      <c r="H24" s="33"/>
+      <c r="I24" s="82">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J24" s="34"/>
+      <c r="J24" s="33"/>
       <c r="K24" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L24" s="4"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="29">
         <f>RAWDATA!B24</f>
         <v>0</v>
@@ -5521,22 +5241,22 @@
         <f>RAWDATA!E24</f>
         <v>0</v>
       </c>
-      <c r="E25" s="34"/>
-      <c r="F25" s="34"/>
-      <c r="G25" s="34"/>
-      <c r="H25" s="34"/>
-      <c r="I25" s="85">
+      <c r="E25" s="33"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="33"/>
+      <c r="H25" s="33"/>
+      <c r="I25" s="82">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J25" s="34"/>
+      <c r="J25" s="33"/>
       <c r="K25" s="30">
         <f>SUM(I25:J25)</f>
         <v>0</v>
       </c>
       <c r="L25" s="4"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="29">
         <f>RAWDATA!B25</f>
         <v>0</v>
@@ -5553,22 +5273,22 @@
         <f>RAWDATA!E25</f>
         <v>0</v>
       </c>
-      <c r="E26" s="34"/>
-      <c r="F26" s="34"/>
-      <c r="G26" s="34"/>
-      <c r="H26" s="34"/>
-      <c r="I26" s="85">
+      <c r="E26" s="33"/>
+      <c r="F26" s="33"/>
+      <c r="G26" s="33"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="82">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J26" s="34"/>
+      <c r="J26" s="33"/>
       <c r="K26" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L26" s="4"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="29">
         <f>RAWDATA!B26</f>
         <v>0</v>
@@ -5585,22 +5305,22 @@
         <f>RAWDATA!E26</f>
         <v>0</v>
       </c>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="34"/>
-      <c r="I27" s="85">
+      <c r="E27" s="33"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="33"/>
+      <c r="I27" s="82">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J27" s="34"/>
+      <c r="J27" s="33"/>
       <c r="K27" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L27" s="4"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
       <c r="B28" s="4" t="s">
         <v>10</v>
@@ -5616,7 +5336,7 @@
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1" t="s">
         <v>25</v>
@@ -5635,7 +5355,7 @@
       </c>
       <c r="L29" s="4"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="4"/>
       <c r="B30" s="4" t="s">
         <v>11</v>
@@ -5665,25 +5385,25 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" zeroHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.44140625" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" style="7" customWidth="1"/>
-    <col min="3" max="8" width="11.44140625" customWidth="1"/>
-    <col min="9" max="16384" width="11.44140625" hidden="1"/>
+    <col min="1" max="1" width="11.42578125" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" style="7" customWidth="1"/>
+    <col min="3" max="8" width="11.42578125" customWidth="1"/>
+    <col min="9" max="16384" width="11.42578125" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="92" t="str">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="89" t="str">
         <f>Notenliste!B34</f>
         <v>course.name</v>
       </c>
-      <c r="B1" s="92"/>
+      <c r="B1" s="89"/>
       <c r="C1" s="8" t="s">
         <v>13</v>
       </c>
@@ -5692,7 +5412,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>4</v>
       </c>
@@ -5700,7 +5420,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <v>1</v>
       </c>
@@ -5709,7 +5429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>1.3</v>
       </c>
@@ -5718,7 +5438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>1.7</v>
       </c>
@@ -5727,7 +5447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>2</v>
       </c>
@@ -5736,7 +5456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>2.2999999999999998</v>
       </c>
@@ -5745,7 +5465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>2.7</v>
       </c>
@@ -5754,7 +5474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <v>3</v>
       </c>
@@ -5763,7 +5483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <v>3.3</v>
       </c>
@@ -5772,7 +5492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <v>3.7</v>
       </c>
@@ -5781,7 +5501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
         <v>4</v>
       </c>
@@ -5790,9 +5510,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B13" s="7">
         <f>COUNTIF(Notenliste!$F$2:$F$26,A13)</f>
@@ -5815,69 +5535,64 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P34"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" zeroHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="25.6640625" customWidth="1"/>
-    <col min="4" max="5" width="10.6640625" style="20" customWidth="1"/>
-    <col min="6" max="7" width="30.6640625" customWidth="1"/>
-    <col min="8" max="8" width="10.6640625" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="9.109375" hidden="1" customWidth="1"/>
-    <col min="10" max="14" width="5.6640625" style="7" customWidth="1"/>
-    <col min="15" max="15" width="5.6640625" customWidth="1"/>
-    <col min="16" max="16" width="1.6640625" customWidth="1"/>
-    <col min="17" max="16384" width="11.44140625" hidden="1"/>
+    <col min="1" max="1" width="3.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="5" width="10.7109375" style="20" customWidth="1"/>
+    <col min="6" max="7" width="30.7109375" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" hidden="1" customWidth="1"/>
+    <col min="10" max="13" width="5.7109375" style="7" customWidth="1"/>
+    <col min="14" max="14" width="1.7109375" customWidth="1"/>
+    <col min="17" max="16384" width="11.42578125" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="61" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="93" t="str">
+    <row r="1" spans="1:13" s="58" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="90" t="str">
         <f>Notenliste!B34&amp;" / "&amp;Notenliste!B35</f>
         <v>course.name / course.name_english</v>
       </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
-      <c r="G1" s="93"/>
-      <c r="H1" s="93"/>
-      <c r="I1" s="93"/>
-      <c r="J1" s="93"/>
-      <c r="K1" s="93"/>
-      <c r="L1" s="93"/>
-      <c r="M1" s="93"/>
-      <c r="N1" s="93"/>
-      <c r="O1" s="93"/>
-    </row>
-    <row r="2" spans="1:15" s="61" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="94" t="str">
+      <c r="B1" s="90"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="90"/>
+      <c r="F1" s="90"/>
+      <c r="G1" s="90"/>
+      <c r="H1" s="90"/>
+      <c r="I1" s="90"/>
+      <c r="J1" s="90"/>
+      <c r="K1" s="90"/>
+      <c r="L1" s="90"/>
+      <c r="M1" s="90"/>
+    </row>
+    <row r="2" spans="1:13" s="58" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="91" t="str">
         <f>"Dozent/in: "&amp;Notenliste!B31</f>
         <v>Dozent/in: course.teacher_name</v>
       </c>
-      <c r="B2" s="94"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="94"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="95" t="str">
+      <c r="B2" s="91"/>
+      <c r="C2" s="91"/>
+      <c r="D2" s="91"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="92" t="str">
         <f>"Semster: "&amp;Notenliste!B36</f>
         <v>Semster: semester</v>
       </c>
-      <c r="G2" s="95"/>
-      <c r="H2" s="95"/>
-      <c r="I2" s="95"/>
-      <c r="J2" s="95"/>
-      <c r="K2" s="95"/>
-      <c r="L2" s="95"/>
-      <c r="M2" s="95"/>
-      <c r="N2" s="95"/>
-      <c r="O2" s="95"/>
-    </row>
-    <row r="3" spans="1:15" s="62" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="92"/>
+      <c r="L2" s="92"/>
+      <c r="M2" s="92"/>
+    </row>
+    <row r="3" spans="1:13" s="59" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>26</v>
       </c>
@@ -5888,7 +5603,7 @@
         <v>19</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E3" s="14" t="s">
         <v>29</v>
@@ -5906,25 +5621,19 @@
         <v>23</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="M3" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="N3" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="O3" s="21" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" s="61" customFormat="1" x14ac:dyDescent="0.3">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17">
         <v>1</v>
       </c>
@@ -5960,32 +5669,24 @@
         <f>RAWDATA!N2</f>
         <v>0</v>
       </c>
-      <c r="J4" s="17" t="str">
-        <f>IF(Notenliste!J2=0," ",UPPER(Notenliste!J2))</f>
-        <v>ATTENDANCE.TS_REQUESTED_STR</v>
+      <c r="J4" s="17" t="e">
+        <f>IF(OR(K4&lt;=4, K4="bestanden"),"X","")</f>
+        <v>#N/A</v>
       </c>
       <c r="K4" s="17" t="e">
-        <f>IF(OR(L4&lt;=4, L4="bestanden"),"X","")</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L4" s="17" t="e">
         <f>IF(Notenliste!F2="KP","",IF(OR(Notenliste!H2="x", Notenliste!H2="X"), "bestanden",Notenliste!F2))</f>
         <v>#N/A</v>
       </c>
-      <c r="M4" s="17" t="str">
+      <c r="L4" s="17" t="str">
         <f>Notenliste!E2</f>
         <v>attendance.sanitized_grade</v>
       </c>
-      <c r="N4" s="17" t="e">
+      <c r="M4" s="17" t="e">
         <f>IF(Notenliste!F2="KP","",Notenliste!I2)</f>
         <v>#N/A</v>
       </c>
-      <c r="O4" s="19" t="str">
-        <f>IF(Notenliste!L2=0," ",UPPER(Notenliste!L2))</f>
-        <v>ATTENDANCE.TS_RECEIVED_STR</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" s="61" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:13" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17">
         <v>2</v>
       </c>
@@ -6022,31 +5723,23 @@
         <v>0</v>
       </c>
       <c r="J5" s="17" t="str">
-        <f>IF(Notenliste!J3=0," ",UPPER(Notenliste!J3))</f>
-        <v xml:space="preserve"> </v>
+        <f t="shared" ref="J5:J28" si="0">IF(OR(K5&lt;=4, K5="bestanden"),"X","")</f>
+        <v/>
       </c>
       <c r="K5" s="17" t="str">
-        <f t="shared" ref="K5:K28" si="0">IF(OR(L5&lt;=4, L5="bestanden"),"X","")</f>
-        <v/>
-      </c>
-      <c r="L5" s="17" t="str">
         <f>IF(Notenliste!F3="KP","",IF(OR(Notenliste!H3="x", Notenliste!H3="X"), "bestanden",Notenliste!F3))</f>
         <v/>
       </c>
-      <c r="M5" s="17">
+      <c r="L5" s="17">
         <f>Notenliste!E3</f>
         <v>0</v>
       </c>
-      <c r="N5" s="17" t="str">
+      <c r="M5" s="17" t="str">
         <f>IF(Notenliste!F3="KP","",Notenliste!I3)</f>
         <v/>
       </c>
-      <c r="O5" s="19" t="str">
-        <f>IF(Notenliste!L3=0," ",UPPER(Notenliste!L3))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" s="61" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:13" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="17">
         <v>3</v>
       </c>
@@ -6083,31 +5776,23 @@
         <v>0</v>
       </c>
       <c r="J6" s="17" t="str">
-        <f>IF(Notenliste!J4=0," ",UPPER(Notenliste!J4))</f>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="K6" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L6" s="17" t="str">
         <f>IF(Notenliste!F4="KP","",IF(OR(Notenliste!H4="x", Notenliste!H4="X"), "bestanden",Notenliste!F4))</f>
         <v/>
       </c>
-      <c r="M6" s="17">
+      <c r="L6" s="17">
         <f>Notenliste!E4</f>
         <v>0</v>
       </c>
-      <c r="N6" s="17" t="str">
+      <c r="M6" s="17" t="str">
         <f>IF(Notenliste!F4="KP","",Notenliste!I4)</f>
         <v/>
       </c>
-      <c r="O6" s="19" t="str">
-        <f>IF(Notenliste!L4=0," ",UPPER(Notenliste!L4))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" s="61" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:13" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="17">
         <v>4</v>
       </c>
@@ -6144,31 +5829,23 @@
         <v>0</v>
       </c>
       <c r="J7" s="17" t="str">
-        <f>IF(Notenliste!J5=0," ",UPPER(Notenliste!J5))</f>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="K7" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L7" s="17" t="str">
         <f>IF(Notenliste!F5="KP","",IF(OR(Notenliste!H5="x", Notenliste!H5="X"), "bestanden",Notenliste!F5))</f>
         <v/>
       </c>
-      <c r="M7" s="17">
+      <c r="L7" s="17">
         <f>Notenliste!E5</f>
         <v>0</v>
       </c>
-      <c r="N7" s="17" t="str">
+      <c r="M7" s="17" t="str">
         <f>IF(Notenliste!F5="KP","",Notenliste!I5)</f>
         <v/>
       </c>
-      <c r="O7" s="19" t="str">
-        <f>IF(Notenliste!L5=0," ",UPPER(Notenliste!L5))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" s="61" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:13" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="17">
         <v>5</v>
       </c>
@@ -6205,31 +5882,23 @@
         <v>0</v>
       </c>
       <c r="J8" s="17" t="str">
-        <f>IF(Notenliste!J6=0," ",UPPER(Notenliste!J6))</f>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="K8" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L8" s="17" t="str">
         <f>IF(Notenliste!F6="KP","",IF(OR(Notenliste!H6="x", Notenliste!H6="X"), "bestanden",Notenliste!F6))</f>
         <v/>
       </c>
-      <c r="M8" s="17">
+      <c r="L8" s="17">
         <f>Notenliste!E6</f>
         <v>0</v>
       </c>
-      <c r="N8" s="17" t="str">
+      <c r="M8" s="17" t="str">
         <f>IF(Notenliste!F6="KP","",Notenliste!I6)</f>
         <v/>
       </c>
-      <c r="O8" s="19" t="str">
-        <f>IF(Notenliste!L6=0," ",UPPER(Notenliste!L6))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" s="61" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:13" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17">
         <v>6</v>
       </c>
@@ -6266,31 +5935,23 @@
         <v>0</v>
       </c>
       <c r="J9" s="17" t="str">
-        <f>IF(Notenliste!J7=0," ",UPPER(Notenliste!J7))</f>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="K9" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L9" s="17" t="str">
         <f>IF(Notenliste!F7="KP","",IF(OR(Notenliste!H7="x", Notenliste!H7="X"), "bestanden",Notenliste!F7))</f>
         <v/>
       </c>
-      <c r="M9" s="17">
+      <c r="L9" s="17">
         <f>Notenliste!E7</f>
         <v>0</v>
       </c>
-      <c r="N9" s="17" t="str">
+      <c r="M9" s="17" t="str">
         <f>IF(Notenliste!F7="KP","",Notenliste!I7)</f>
         <v/>
       </c>
-      <c r="O9" s="19" t="str">
-        <f>IF(Notenliste!L7=0," ",UPPER(Notenliste!L7))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" s="61" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:13" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
         <v>7</v>
       </c>
@@ -6327,31 +5988,23 @@
         <v>0</v>
       </c>
       <c r="J10" s="17" t="str">
-        <f>IF(Notenliste!J8=0," ",UPPER(Notenliste!J8))</f>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="K10" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L10" s="17" t="str">
         <f>IF(Notenliste!F8="KP","",IF(OR(Notenliste!H8="x", Notenliste!H8="X"), "bestanden",Notenliste!F8))</f>
         <v/>
       </c>
-      <c r="M10" s="17">
+      <c r="L10" s="17">
         <f>Notenliste!E8</f>
         <v>0</v>
       </c>
-      <c r="N10" s="17" t="str">
+      <c r="M10" s="17" t="str">
         <f>IF(Notenliste!F8="KP","",Notenliste!I8)</f>
         <v/>
       </c>
-      <c r="O10" s="19" t="str">
-        <f>IF(Notenliste!L8=0," ",UPPER(Notenliste!L8))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" s="61" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:13" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="17">
         <v>8</v>
       </c>
@@ -6388,31 +6041,23 @@
         <v>0</v>
       </c>
       <c r="J11" s="17" t="str">
-        <f>IF(Notenliste!J9=0," ",UPPER(Notenliste!J9))</f>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="K11" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L11" s="17" t="str">
         <f>IF(Notenliste!F9="KP","",IF(OR(Notenliste!H9="x", Notenliste!H9="X"), "bestanden",Notenliste!F9))</f>
         <v/>
       </c>
-      <c r="M11" s="17">
+      <c r="L11" s="17">
         <f>Notenliste!E9</f>
         <v>0</v>
       </c>
-      <c r="N11" s="17" t="str">
+      <c r="M11" s="17" t="str">
         <f>IF(Notenliste!F9="KP","",Notenliste!I9)</f>
         <v/>
       </c>
-      <c r="O11" s="19" t="str">
-        <f>IF(Notenliste!L9=0," ",UPPER(Notenliste!L9))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" s="61" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:13" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="17">
         <v>9</v>
       </c>
@@ -6449,31 +6094,23 @@
         <v>0</v>
       </c>
       <c r="J12" s="17" t="str">
-        <f>IF(Notenliste!J10=0," ",UPPER(Notenliste!J10))</f>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="K12" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L12" s="17" t="str">
         <f>IF(Notenliste!F10="KP","",IF(OR(Notenliste!H10="x", Notenliste!H10="X"), "bestanden",Notenliste!F10))</f>
         <v/>
       </c>
-      <c r="M12" s="17">
+      <c r="L12" s="17">
         <f>Notenliste!E10</f>
         <v>0</v>
       </c>
-      <c r="N12" s="17" t="str">
+      <c r="M12" s="17" t="str">
         <f>IF(Notenliste!F10="KP","",Notenliste!I10)</f>
         <v/>
       </c>
-      <c r="O12" s="19" t="str">
-        <f>IF(Notenliste!L10=0," ",UPPER(Notenliste!L10))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" s="61" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:13" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="17">
         <v>10</v>
       </c>
@@ -6510,31 +6147,23 @@
         <v>0</v>
       </c>
       <c r="J13" s="17" t="str">
-        <f>IF(Notenliste!J11=0," ",UPPER(Notenliste!J11))</f>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="K13" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L13" s="17" t="str">
         <f>IF(Notenliste!F11="KP","",IF(OR(Notenliste!H11="x", Notenliste!H11="X"), "bestanden",Notenliste!F11))</f>
         <v/>
       </c>
-      <c r="M13" s="17">
+      <c r="L13" s="17">
         <f>Notenliste!E11</f>
         <v>0</v>
       </c>
-      <c r="N13" s="17" t="str">
+      <c r="M13" s="17" t="str">
         <f>IF(Notenliste!F11="KP","",Notenliste!I11)</f>
         <v/>
       </c>
-      <c r="O13" s="19" t="str">
-        <f>IF(Notenliste!L11=0," ",UPPER(Notenliste!L11))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" s="61" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:13" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="17">
         <v>11</v>
       </c>
@@ -6571,31 +6200,23 @@
         <v>0</v>
       </c>
       <c r="J14" s="17" t="str">
-        <f>IF(Notenliste!J12=0," ",UPPER(Notenliste!J12))</f>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="K14" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L14" s="17" t="str">
         <f>IF(Notenliste!F12="KP","",IF(OR(Notenliste!H12="x", Notenliste!H12="X"), "bestanden",Notenliste!F12))</f>
         <v/>
       </c>
-      <c r="M14" s="17">
+      <c r="L14" s="17">
         <f>Notenliste!E12</f>
         <v>0</v>
       </c>
-      <c r="N14" s="17" t="str">
+      <c r="M14" s="17" t="str">
         <f>IF(Notenliste!F12="KP","",Notenliste!I12)</f>
         <v/>
       </c>
-      <c r="O14" s="19" t="str">
-        <f>IF(Notenliste!L12=0," ",UPPER(Notenliste!L12))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" s="61" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:13" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="17">
         <v>12</v>
       </c>
@@ -6632,31 +6253,23 @@
         <v>0</v>
       </c>
       <c r="J15" s="17" t="str">
-        <f>IF(Notenliste!J13=0," ",UPPER(Notenliste!J13))</f>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="K15" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L15" s="17" t="str">
         <f>IF(Notenliste!F13="KP","",IF(OR(Notenliste!H13="x", Notenliste!H13="X"), "bestanden",Notenliste!F13))</f>
         <v/>
       </c>
-      <c r="M15" s="17">
+      <c r="L15" s="17">
         <f>Notenliste!E13</f>
         <v>0</v>
       </c>
-      <c r="N15" s="17" t="str">
+      <c r="M15" s="17" t="str">
         <f>IF(Notenliste!F13="KP","",Notenliste!I13)</f>
         <v/>
       </c>
-      <c r="O15" s="19" t="str">
-        <f>IF(Notenliste!L13=0," ",UPPER(Notenliste!L13))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" s="61" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:13" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="17">
         <v>13</v>
       </c>
@@ -6693,31 +6306,23 @@
         <v>0</v>
       </c>
       <c r="J16" s="17" t="str">
-        <f>IF(Notenliste!J14=0," ",UPPER(Notenliste!J14))</f>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="K16" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L16" s="17" t="str">
         <f>IF(Notenliste!F14="KP","",IF(OR(Notenliste!H14="x", Notenliste!H14="X"), "bestanden",Notenliste!F14))</f>
         <v/>
       </c>
-      <c r="M16" s="17">
+      <c r="L16" s="17">
         <f>Notenliste!E14</f>
         <v>0</v>
       </c>
-      <c r="N16" s="17" t="str">
+      <c r="M16" s="17" t="str">
         <f>IF(Notenliste!F14="KP","",Notenliste!I14)</f>
         <v/>
       </c>
-      <c r="O16" s="19" t="str">
-        <f>IF(Notenliste!L14=0," ",UPPER(Notenliste!L14))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" s="61" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:13" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="17">
         <v>14</v>
       </c>
@@ -6754,31 +6359,23 @@
         <v>0</v>
       </c>
       <c r="J17" s="17" t="str">
-        <f>IF(Notenliste!J15=0," ",UPPER(Notenliste!J15))</f>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="K17" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L17" s="17" t="str">
         <f>IF(Notenliste!F15="KP","",IF(OR(Notenliste!H15="x", Notenliste!H15="X"), "bestanden",Notenliste!F15))</f>
         <v/>
       </c>
-      <c r="M17" s="17">
+      <c r="L17" s="17">
         <f>Notenliste!E15</f>
         <v>0</v>
       </c>
-      <c r="N17" s="17" t="str">
+      <c r="M17" s="17" t="str">
         <f>IF(Notenliste!F15="KP","",Notenliste!I15)</f>
         <v/>
       </c>
-      <c r="O17" s="19" t="str">
-        <f>IF(Notenliste!L15=0," ",UPPER(Notenliste!L15))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" s="61" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:13" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="17">
         <v>15</v>
       </c>
@@ -6815,31 +6412,23 @@
         <v>0</v>
       </c>
       <c r="J18" s="17" t="str">
-        <f>IF(Notenliste!J16=0," ",UPPER(Notenliste!J16))</f>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="K18" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L18" s="17" t="str">
         <f>IF(Notenliste!F16="KP","",IF(OR(Notenliste!H16="x", Notenliste!H16="X"), "bestanden",Notenliste!F16))</f>
         <v/>
       </c>
-      <c r="M18" s="17">
+      <c r="L18" s="17">
         <f>Notenliste!E16</f>
         <v>0</v>
       </c>
-      <c r="N18" s="17" t="str">
+      <c r="M18" s="17" t="str">
         <f>IF(Notenliste!F16="KP","",Notenliste!I16)</f>
         <v/>
       </c>
-      <c r="O18" s="19" t="str">
-        <f>IF(Notenliste!L16=0," ",UPPER(Notenliste!L16))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" s="61" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:13" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="17">
         <v>16</v>
       </c>
@@ -6876,31 +6465,23 @@
         <v>0</v>
       </c>
       <c r="J19" s="17" t="str">
-        <f>IF(Notenliste!J17=0," ",UPPER(Notenliste!J17))</f>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="K19" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L19" s="17" t="str">
         <f>IF(Notenliste!F17="KP","",IF(OR(Notenliste!H17="x", Notenliste!H17="X"), "bestanden",Notenliste!F17))</f>
         <v/>
       </c>
-      <c r="M19" s="17">
+      <c r="L19" s="17">
         <f>Notenliste!E17</f>
         <v>0</v>
       </c>
-      <c r="N19" s="17" t="str">
+      <c r="M19" s="17" t="str">
         <f>IF(Notenliste!F17="KP","",Notenliste!I17)</f>
         <v/>
       </c>
-      <c r="O19" s="19" t="str">
-        <f>IF(Notenliste!L17=0," ",UPPER(Notenliste!L17))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" s="61" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:13" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="17">
         <v>17</v>
       </c>
@@ -6937,31 +6518,23 @@
         <v>0</v>
       </c>
       <c r="J20" s="17" t="str">
-        <f>IF(Notenliste!J18=0," ",UPPER(Notenliste!J18))</f>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="K20" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L20" s="17" t="str">
         <f>IF(Notenliste!F18="KP","",IF(OR(Notenliste!H18="x", Notenliste!H18="X"), "bestanden",Notenliste!F18))</f>
         <v/>
       </c>
-      <c r="M20" s="17">
+      <c r="L20" s="17">
         <f>Notenliste!E18</f>
         <v>0</v>
       </c>
-      <c r="N20" s="17" t="str">
+      <c r="M20" s="17" t="str">
         <f>IF(Notenliste!F18="KP","",Notenliste!I18)</f>
         <v/>
       </c>
-      <c r="O20" s="19" t="str">
-        <f>IF(Notenliste!L18=0," ",UPPER(Notenliste!L18))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" s="61" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:13" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="17">
         <v>18</v>
       </c>
@@ -6998,31 +6571,23 @@
         <v>0</v>
       </c>
       <c r="J21" s="17" t="str">
-        <f>IF(Notenliste!J19=0," ",UPPER(Notenliste!J19))</f>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="K21" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L21" s="17" t="str">
         <f>IF(Notenliste!F19="KP","",IF(OR(Notenliste!H19="x", Notenliste!H19="X"), "bestanden",Notenliste!F19))</f>
         <v/>
       </c>
-      <c r="M21" s="17">
+      <c r="L21" s="17">
         <f>Notenliste!E19</f>
         <v>0</v>
       </c>
-      <c r="N21" s="17" t="str">
+      <c r="M21" s="17" t="str">
         <f>IF(Notenliste!F19="KP","",Notenliste!I19)</f>
         <v/>
       </c>
-      <c r="O21" s="19" t="str">
-        <f>IF(Notenliste!L19=0," ",UPPER(Notenliste!L19))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" s="61" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:13" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="17">
         <v>19</v>
       </c>
@@ -7059,31 +6624,23 @@
         <v>0</v>
       </c>
       <c r="J22" s="17" t="str">
-        <f>IF(Notenliste!J20=0," ",UPPER(Notenliste!J20))</f>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="K22" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L22" s="17" t="str">
         <f>IF(Notenliste!F20="KP","",IF(OR(Notenliste!H20="x", Notenliste!H20="X"), "bestanden",Notenliste!F20))</f>
         <v/>
       </c>
-      <c r="M22" s="17">
+      <c r="L22" s="17">
         <f>Notenliste!E20</f>
         <v>0</v>
       </c>
-      <c r="N22" s="17" t="str">
+      <c r="M22" s="17" t="str">
         <f>IF(Notenliste!F20="KP","",Notenliste!I20)</f>
         <v/>
       </c>
-      <c r="O22" s="19" t="str">
-        <f>IF(Notenliste!L20=0," ",UPPER(Notenliste!L20))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" s="61" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:13" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="17">
         <v>20</v>
       </c>
@@ -7120,31 +6677,23 @@
         <v>0</v>
       </c>
       <c r="J23" s="17" t="str">
-        <f>IF(Notenliste!J21=0," ",UPPER(Notenliste!J21))</f>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="K23" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L23" s="17" t="str">
         <f>IF(Notenliste!F21="KP","",IF(OR(Notenliste!H21="x", Notenliste!H21="X"), "bestanden",Notenliste!F21))</f>
         <v/>
       </c>
-      <c r="M23" s="17">
+      <c r="L23" s="17">
         <f>Notenliste!E21</f>
         <v>0</v>
       </c>
-      <c r="N23" s="17" t="str">
+      <c r="M23" s="17" t="str">
         <f>IF(Notenliste!F21="KP","",Notenliste!I21)</f>
         <v/>
       </c>
-      <c r="O23" s="19" t="str">
-        <f>IF(Notenliste!L21=0," ",UPPER(Notenliste!L21))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" s="61" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:13" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="17">
         <v>21</v>
       </c>
@@ -7181,31 +6730,23 @@
         <v>0</v>
       </c>
       <c r="J24" s="17" t="str">
-        <f>IF(Notenliste!J22=0," ",UPPER(Notenliste!J22))</f>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="K24" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L24" s="17" t="str">
         <f>IF(Notenliste!F22="KP","",IF(OR(Notenliste!H22="x", Notenliste!H22="X"), "bestanden",Notenliste!F22))</f>
         <v/>
       </c>
-      <c r="M24" s="17">
+      <c r="L24" s="17">
         <f>Notenliste!E22</f>
         <v>0</v>
       </c>
-      <c r="N24" s="17" t="str">
+      <c r="M24" s="17" t="str">
         <f>IF(Notenliste!F22="KP","",Notenliste!I22)</f>
         <v/>
       </c>
-      <c r="O24" s="19" t="str">
-        <f>IF(Notenliste!L22=0," ",UPPER(Notenliste!L22))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" s="61" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:13" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="17">
         <v>22</v>
       </c>
@@ -7242,31 +6783,23 @@
         <v>0</v>
       </c>
       <c r="J25" s="17" t="str">
-        <f>IF(Notenliste!J23=0," ",UPPER(Notenliste!J23))</f>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="K25" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L25" s="17" t="str">
         <f>IF(Notenliste!F23="KP","",IF(OR(Notenliste!H23="x", Notenliste!H23="X"), "bestanden",Notenliste!F23))</f>
         <v/>
       </c>
-      <c r="M25" s="17">
+      <c r="L25" s="17">
         <f>Notenliste!E23</f>
         <v>0</v>
       </c>
-      <c r="N25" s="17" t="str">
+      <c r="M25" s="17" t="str">
         <f>IF(Notenliste!F23="KP","",Notenliste!I23)</f>
         <v/>
       </c>
-      <c r="O25" s="19" t="str">
-        <f>IF(Notenliste!L23=0," ",UPPER(Notenliste!L23))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" s="61" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:13" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="17">
         <v>23</v>
       </c>
@@ -7303,31 +6836,23 @@
         <v>0</v>
       </c>
       <c r="J26" s="17" t="str">
-        <f>IF(Notenliste!J24=0," ",UPPER(Notenliste!J24))</f>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="K26" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L26" s="17" t="str">
         <f>IF(Notenliste!F24="KP","",IF(OR(Notenliste!H24="x", Notenliste!H24="X"), "bestanden",Notenliste!F24))</f>
         <v/>
       </c>
-      <c r="M26" s="17">
+      <c r="L26" s="17">
         <f>Notenliste!E24</f>
         <v>0</v>
       </c>
-      <c r="N26" s="17" t="str">
+      <c r="M26" s="17" t="str">
         <f>IF(Notenliste!F24="KP","",Notenliste!I24)</f>
         <v/>
       </c>
-      <c r="O26" s="19" t="str">
-        <f>IF(Notenliste!L24=0," ",UPPER(Notenliste!L24))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" s="61" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:13" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="17">
         <v>24</v>
       </c>
@@ -7364,31 +6889,23 @@
         <v>0</v>
       </c>
       <c r="J27" s="17" t="str">
-        <f>IF(Notenliste!J25=0," ",UPPER(Notenliste!J25))</f>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="K27" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L27" s="17" t="str">
         <f>IF(Notenliste!F25="KP","",IF(OR(Notenliste!H25="x", Notenliste!H25="X"), "bestanden",Notenliste!F25))</f>
         <v/>
       </c>
-      <c r="M27" s="17">
+      <c r="L27" s="17">
         <f>Notenliste!E25</f>
         <v>0</v>
       </c>
-      <c r="N27" s="17" t="str">
+      <c r="M27" s="17" t="str">
         <f>IF(Notenliste!F25="KP","",Notenliste!I25)</f>
         <v/>
       </c>
-      <c r="O27" s="19" t="str">
-        <f>IF(Notenliste!L25=0," ",UPPER(Notenliste!L25))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" s="61" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:13" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="17">
         <v>25</v>
       </c>
@@ -7425,148 +6942,125 @@
         <v>0</v>
       </c>
       <c r="J28" s="17" t="str">
-        <f>IF(Notenliste!J26=0," ",UPPER(Notenliste!J26))</f>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="K28" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L28" s="17" t="str">
         <f>IF(Notenliste!F26="KP","",IF(OR(Notenliste!H26="x", Notenliste!H26="X"), "bestanden",Notenliste!F26))</f>
         <v/>
       </c>
-      <c r="M28" s="17">
+      <c r="L28" s="17">
         <f>Notenliste!E26</f>
         <v>0</v>
       </c>
-      <c r="N28" s="17" t="str">
+      <c r="M28" s="17" t="str">
         <f>IF(Notenliste!F26="KP","",Notenliste!I26)</f>
         <v/>
       </c>
-      <c r="O28" s="19" t="str">
-        <f>IF(Notenliste!L26=0," ",UPPER(Notenliste!L26))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" s="61" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="58"/>
-      <c r="B29" s="59"/>
-      <c r="C29" s="59"/>
-      <c r="D29" s="60"/>
-      <c r="E29" s="60"/>
-      <c r="F29" s="59"/>
-      <c r="G29" s="59"/>
-      <c r="H29" s="57"/>
-      <c r="I29" s="57"/>
+    </row>
+    <row r="29" spans="1:13" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="55"/>
+      <c r="B29" s="56"/>
+      <c r="C29" s="56"/>
+      <c r="D29" s="57"/>
+      <c r="E29" s="57"/>
+      <c r="F29" s="56"/>
+      <c r="G29" s="56"/>
+      <c r="H29" s="54"/>
+      <c r="I29" s="54"/>
       <c r="J29" s="17">
         <f>COUNTIF(J4:J28,"X")</f>
         <v>0</v>
       </c>
-      <c r="K29" s="17">
-        <f>COUNTIF(K4:K28,"X")</f>
-        <v>0</v>
-      </c>
-      <c r="L29" s="58"/>
-      <c r="M29" s="58"/>
-      <c r="N29" s="58"/>
-      <c r="O29" s="60"/>
-    </row>
-    <row r="30" spans="1:15" s="61" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="96" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" s="96"/>
-      <c r="C30" s="96"/>
-      <c r="D30" s="96"/>
-      <c r="E30" s="96"/>
-      <c r="F30" s="96"/>
-      <c r="G30" s="96"/>
-      <c r="H30" s="96"/>
-      <c r="I30" s="96"/>
-      <c r="J30" s="96"/>
-      <c r="K30" s="96"/>
-      <c r="L30" s="96"/>
-      <c r="M30" s="96"/>
-      <c r="N30" s="96"/>
-      <c r="O30" s="96"/>
-    </row>
-    <row r="31" spans="1:15" s="61" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="96"/>
-      <c r="B31" s="96"/>
-      <c r="C31" s="96"/>
-      <c r="D31" s="96"/>
-      <c r="E31" s="96"/>
-      <c r="F31" s="96"/>
-      <c r="G31" s="96"/>
-      <c r="H31" s="96"/>
-      <c r="I31" s="96"/>
-      <c r="J31" s="96"/>
-      <c r="K31" s="96"/>
-      <c r="L31" s="96"/>
-      <c r="M31" s="96"/>
-      <c r="N31" s="96"/>
-      <c r="O31" s="96"/>
-    </row>
-    <row r="32" spans="1:15" s="61" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="96"/>
-      <c r="B32" s="96"/>
-      <c r="C32" s="96"/>
-      <c r="D32" s="96"/>
-      <c r="E32" s="96"/>
-      <c r="F32" s="96"/>
-      <c r="G32" s="96"/>
-      <c r="H32" s="96"/>
-      <c r="I32" s="96"/>
-      <c r="J32" s="96"/>
-      <c r="K32" s="96"/>
-      <c r="L32" s="96"/>
-      <c r="M32" s="96"/>
-      <c r="N32" s="96"/>
-      <c r="O32" s="96"/>
-    </row>
-    <row r="33" spans="1:16" s="61" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="96"/>
-      <c r="B33" s="96"/>
-      <c r="C33" s="96"/>
-      <c r="D33" s="96"/>
-      <c r="E33" s="96"/>
-      <c r="F33" s="96"/>
-      <c r="G33" s="96"/>
-      <c r="H33" s="96"/>
-      <c r="I33" s="96"/>
-      <c r="J33" s="96"/>
-      <c r="K33" s="96"/>
-      <c r="L33" s="96"/>
-      <c r="M33" s="96"/>
-      <c r="N33" s="96"/>
-      <c r="O33" s="96"/>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A34" s="96"/>
-      <c r="B34" s="96"/>
-      <c r="C34" s="96"/>
-      <c r="D34" s="96"/>
-      <c r="E34" s="96"/>
-      <c r="F34" s="96"/>
-      <c r="G34" s="96"/>
-      <c r="H34" s="96"/>
-      <c r="I34" s="96"/>
-      <c r="J34" s="96"/>
-      <c r="K34" s="96"/>
-      <c r="L34" s="96"/>
-      <c r="M34" s="96"/>
-      <c r="N34" s="96"/>
-      <c r="O34" s="96"/>
-      <c r="P34" s="61"/>
+      <c r="K29" s="55"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="55"/>
+    </row>
+    <row r="30" spans="1:13" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="93" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="93"/>
+      <c r="C30" s="93"/>
+      <c r="D30" s="93"/>
+      <c r="E30" s="93"/>
+      <c r="F30" s="93"/>
+      <c r="G30" s="93"/>
+      <c r="H30" s="93"/>
+      <c r="I30" s="93"/>
+      <c r="J30" s="93"/>
+      <c r="K30" s="93"/>
+      <c r="L30" s="93"/>
+      <c r="M30" s="93"/>
+    </row>
+    <row r="31" spans="1:13" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="93"/>
+      <c r="B31" s="93"/>
+      <c r="C31" s="93"/>
+      <c r="D31" s="93"/>
+      <c r="E31" s="93"/>
+      <c r="F31" s="93"/>
+      <c r="G31" s="93"/>
+      <c r="H31" s="93"/>
+      <c r="I31" s="93"/>
+      <c r="J31" s="93"/>
+      <c r="K31" s="93"/>
+      <c r="L31" s="93"/>
+      <c r="M31" s="93"/>
+    </row>
+    <row r="32" spans="1:13" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="93"/>
+      <c r="B32" s="93"/>
+      <c r="C32" s="93"/>
+      <c r="D32" s="93"/>
+      <c r="E32" s="93"/>
+      <c r="F32" s="93"/>
+      <c r="G32" s="93"/>
+      <c r="H32" s="93"/>
+      <c r="I32" s="93"/>
+      <c r="J32" s="93"/>
+      <c r="K32" s="93"/>
+      <c r="L32" s="93"/>
+      <c r="M32" s="93"/>
+    </row>
+    <row r="33" spans="1:14" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="93"/>
+      <c r="B33" s="93"/>
+      <c r="C33" s="93"/>
+      <c r="D33" s="93"/>
+      <c r="E33" s="93"/>
+      <c r="F33" s="93"/>
+      <c r="G33" s="93"/>
+      <c r="H33" s="93"/>
+      <c r="I33" s="93"/>
+      <c r="J33" s="93"/>
+      <c r="K33" s="93"/>
+      <c r="L33" s="93"/>
+      <c r="M33" s="93"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="93"/>
+      <c r="B34" s="93"/>
+      <c r="C34" s="93"/>
+      <c r="D34" s="93"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="93"/>
+      <c r="G34" s="93"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="93"/>
+      <c r="J34" s="93"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="93"/>
+      <c r="M34" s="93"/>
+      <c r="N34" s="58"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" selectLockedCells="1"/>
   <mergeCells count="4">
-    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A1:M1"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="F2:O2"/>
-    <mergeCell ref="A30:O34"/>
+    <mergeCell ref="F2:M2"/>
+    <mergeCell ref="A30:M34"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.9055118110236221" bottom="1.1023622047244095" header="0.70866141732283472" footer="0.55118110236220474"/>
   <pageSetup paperSize="9" scale="77" orientation="landscape" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -7584,132 +7078,128 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AE30"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.44140625" customWidth="1"/>
-    <col min="4" max="4" width="6.44140625" style="20" customWidth="1"/>
-    <col min="5" max="5" width="9.6640625" style="20" customWidth="1"/>
-    <col min="6" max="6" width="0.6640625" style="20" customWidth="1"/>
-    <col min="7" max="20" width="4.6640625" style="20" customWidth="1"/>
-    <col min="21" max="21" width="0.6640625" style="20" customWidth="1"/>
-    <col min="22" max="22" width="5.6640625" style="54" customWidth="1"/>
-    <col min="23" max="23" width="5.6640625" style="55" customWidth="1"/>
-    <col min="24" max="24" width="5.6640625" style="39" customWidth="1"/>
-    <col min="25" max="31" width="0" hidden="1" customWidth="1"/>
-    <col min="32" max="16384" width="11.44140625" hidden="1"/>
+    <col min="1" max="1" width="3.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" customWidth="1"/>
+    <col min="4" max="4" width="6.42578125" style="20" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" style="20" customWidth="1"/>
+    <col min="6" max="6" width="0.7109375" style="20" customWidth="1"/>
+    <col min="7" max="20" width="4.7109375" style="20" customWidth="1"/>
+    <col min="21" max="21" width="0.7109375" style="20" customWidth="1"/>
+    <col min="22" max="22" width="5.7109375" style="52" customWidth="1"/>
+    <col min="23" max="23" width="5.7109375" style="37" customWidth="1"/>
+    <col min="24" max="30" width="0" hidden="1" customWidth="1"/>
+    <col min="32" max="16384" width="11.42578125" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="99" t="str">
+    <row r="1" spans="1:23" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="96" t="str">
         <f>Notenliste!B34&amp;" / "&amp;Notenliste!B35</f>
         <v>course.name / course.name_english</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
-      <c r="V1" s="99"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="99"/>
-    </row>
-    <row r="2" spans="1:24" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="99" t="s">
-        <v>39</v>
-      </c>
-      <c r="B2" s="99"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
-      <c r="O2" s="99"/>
-      <c r="P2" s="99"/>
-      <c r="Q2" s="99"/>
-      <c r="R2" s="99"/>
-      <c r="S2" s="99"/>
-      <c r="T2" s="99"/>
-      <c r="U2" s="99"/>
-      <c r="V2" s="99"/>
-      <c r="W2" s="99"/>
-      <c r="X2" s="99"/>
-    </row>
-    <row r="3" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="100" t="str">
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
+      <c r="H1" s="96"/>
+      <c r="I1" s="96"/>
+      <c r="J1" s="96"/>
+      <c r="K1" s="96"/>
+      <c r="L1" s="96"/>
+      <c r="M1" s="96"/>
+      <c r="N1" s="96"/>
+      <c r="O1" s="96"/>
+      <c r="P1" s="96"/>
+      <c r="Q1" s="96"/>
+      <c r="R1" s="96"/>
+      <c r="S1" s="96"/>
+      <c r="T1" s="96"/>
+      <c r="U1" s="96"/>
+      <c r="V1" s="96"/>
+      <c r="W1" s="96"/>
+    </row>
+    <row r="2" spans="1:23" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="96" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="96"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="96"/>
+      <c r="G2" s="96"/>
+      <c r="H2" s="96"/>
+      <c r="I2" s="96"/>
+      <c r="J2" s="96"/>
+      <c r="K2" s="96"/>
+      <c r="L2" s="96"/>
+      <c r="M2" s="96"/>
+      <c r="N2" s="96"/>
+      <c r="O2" s="96"/>
+      <c r="P2" s="96"/>
+      <c r="Q2" s="96"/>
+      <c r="R2" s="96"/>
+      <c r="S2" s="96"/>
+      <c r="T2" s="96"/>
+      <c r="U2" s="96"/>
+      <c r="V2" s="96"/>
+      <c r="W2" s="96"/>
+    </row>
+    <row r="3" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="97" t="str">
         <f>"Dozent/in: "&amp;Notenliste!B31</f>
         <v>Dozent/in: course.teacher_name</v>
       </c>
-      <c r="B3" s="100"/>
-      <c r="C3" s="100"/>
-      <c r="D3" s="100"/>
-      <c r="E3" s="100"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="101"/>
-      <c r="H3" s="101"/>
-      <c r="I3" s="101"/>
-      <c r="J3" s="101"/>
-      <c r="K3" s="101"/>
-      <c r="L3" s="101"/>
-      <c r="M3" s="101"/>
-      <c r="N3" s="101"/>
-      <c r="O3" s="101"/>
-      <c r="P3" s="101"/>
-      <c r="Q3" s="101"/>
-      <c r="R3" s="101"/>
-      <c r="S3" s="101"/>
-      <c r="T3" s="101"/>
-      <c r="U3" s="101"/>
-      <c r="V3" s="101"/>
-      <c r="W3" s="101"/>
-      <c r="X3" s="101"/>
-    </row>
-    <row r="4" spans="1:24" s="16" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="102" t="s">
+      <c r="B3" s="97"/>
+      <c r="C3" s="97"/>
+      <c r="D3" s="97"/>
+      <c r="E3" s="97"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="98"/>
+      <c r="H3" s="98"/>
+      <c r="I3" s="98"/>
+      <c r="J3" s="98"/>
+      <c r="K3" s="98"/>
+      <c r="L3" s="98"/>
+      <c r="M3" s="98"/>
+      <c r="N3" s="98"/>
+      <c r="O3" s="98"/>
+      <c r="P3" s="98"/>
+      <c r="Q3" s="98"/>
+      <c r="R3" s="98"/>
+      <c r="S3" s="98"/>
+      <c r="T3" s="98"/>
+      <c r="U3" s="98"/>
+      <c r="V3" s="98"/>
+      <c r="W3" s="98"/>
+    </row>
+    <row r="4" spans="1:23" s="16" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="99" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="102" t="s">
+      <c r="B4" s="99" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="102" t="s">
+      <c r="C4" s="99" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="102" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" s="104" t="s">
+      <c r="D4" s="99" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="101" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="44"/>
-      <c r="G4" s="45"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="43"/>
       <c r="H4" s="14"/>
       <c r="I4" s="14"/>
       <c r="J4" s="14"/>
@@ -7723,25 +7213,22 @@
       <c r="R4" s="14"/>
       <c r="S4" s="14"/>
       <c r="T4" s="14"/>
-      <c r="U4" s="46"/>
-      <c r="V4" s="106" t="s">
-        <v>37</v>
-      </c>
-      <c r="W4" s="97" t="s">
-        <v>38</v>
-      </c>
-      <c r="X4" s="97" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" s="16" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="103"/>
-      <c r="B5" s="103"/>
-      <c r="C5" s="103"/>
-      <c r="D5" s="103"/>
-      <c r="E5" s="105"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="45">
+      <c r="U4" s="44"/>
+      <c r="V4" s="94" t="s">
+        <v>34</v>
+      </c>
+      <c r="W4" s="94" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="100"/>
+      <c r="B5" s="100"/>
+      <c r="C5" s="100"/>
+      <c r="D5" s="100"/>
+      <c r="E5" s="102"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="43">
         <v>1</v>
       </c>
       <c r="H5" s="14">
@@ -7783,12 +7270,11 @@
       <c r="T5" s="14">
         <v>14</v>
       </c>
-      <c r="U5" s="48"/>
-      <c r="V5" s="107"/>
-      <c r="W5" s="98"/>
-      <c r="X5" s="98"/>
-    </row>
-    <row r="6" spans="1:24" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="U5" s="46"/>
+      <c r="V5" s="95"/>
+      <c r="W5" s="95"/>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="17">
         <v>1</v>
       </c>
@@ -7808,27 +7294,26 @@
         <f>RAWDATA!E2</f>
         <v>applicant.tag</v>
       </c>
-      <c r="F6" s="49"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
-      <c r="J6" s="50"/>
-      <c r="K6" s="50"/>
-      <c r="L6" s="50"/>
-      <c r="M6" s="50"/>
-      <c r="N6" s="50"/>
-      <c r="O6" s="50"/>
-      <c r="P6" s="50"/>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50"/>
-      <c r="T6" s="50"/>
-      <c r="U6" s="49"/>
-      <c r="V6" s="50"/>
-      <c r="W6" s="51"/>
-      <c r="X6" s="51"/>
-    </row>
-    <row r="7" spans="1:24" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="F6" s="47"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="48"/>
+      <c r="L6" s="48"/>
+      <c r="M6" s="48"/>
+      <c r="N6" s="48"/>
+      <c r="O6" s="48"/>
+      <c r="P6" s="48"/>
+      <c r="Q6" s="48"/>
+      <c r="R6" s="48"/>
+      <c r="S6" s="48"/>
+      <c r="T6" s="48"/>
+      <c r="U6" s="47"/>
+      <c r="V6" s="49"/>
+      <c r="W6" s="49"/>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="17">
         <v>2</v>
       </c>
@@ -7848,27 +7333,26 @@
         <f>RAWDATA!E3</f>
         <v>0</v>
       </c>
-      <c r="F7" s="52"/>
-      <c r="G7" s="50"/>
-      <c r="H7" s="50"/>
-      <c r="I7" s="50"/>
-      <c r="J7" s="50"/>
-      <c r="K7" s="50"/>
-      <c r="L7" s="50"/>
-      <c r="M7" s="50"/>
-      <c r="N7" s="50"/>
-      <c r="O7" s="50"/>
-      <c r="P7" s="50"/>
-      <c r="Q7" s="50"/>
-      <c r="R7" s="50"/>
-      <c r="S7" s="50"/>
-      <c r="T7" s="50"/>
-      <c r="U7" s="52"/>
-      <c r="V7" s="50"/>
-      <c r="W7" s="51"/>
-      <c r="X7" s="51"/>
-    </row>
-    <row r="8" spans="1:24" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="F7" s="50"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="48"/>
+      <c r="K7" s="48"/>
+      <c r="L7" s="48"/>
+      <c r="M7" s="48"/>
+      <c r="N7" s="48"/>
+      <c r="O7" s="48"/>
+      <c r="P7" s="48"/>
+      <c r="Q7" s="48"/>
+      <c r="R7" s="48"/>
+      <c r="S7" s="48"/>
+      <c r="T7" s="48"/>
+      <c r="U7" s="50"/>
+      <c r="V7" s="49"/>
+      <c r="W7" s="49"/>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" s="17">
         <v>3</v>
       </c>
@@ -7888,27 +7372,26 @@
         <f>RAWDATA!E4</f>
         <v>0</v>
       </c>
-      <c r="F8" s="52"/>
-      <c r="G8" s="50"/>
-      <c r="H8" s="50"/>
-      <c r="I8" s="50"/>
-      <c r="J8" s="50"/>
-      <c r="K8" s="50"/>
-      <c r="L8" s="50"/>
-      <c r="M8" s="50"/>
-      <c r="N8" s="50"/>
-      <c r="O8" s="50"/>
-      <c r="P8" s="50"/>
-      <c r="Q8" s="50"/>
-      <c r="R8" s="50"/>
-      <c r="S8" s="50"/>
-      <c r="T8" s="50"/>
-      <c r="U8" s="52"/>
-      <c r="V8" s="50"/>
-      <c r="W8" s="51"/>
-      <c r="X8" s="51"/>
-    </row>
-    <row r="9" spans="1:24" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="F8" s="50"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="48"/>
+      <c r="I8" s="48"/>
+      <c r="J8" s="48"/>
+      <c r="K8" s="48"/>
+      <c r="L8" s="48"/>
+      <c r="M8" s="48"/>
+      <c r="N8" s="48"/>
+      <c r="O8" s="48"/>
+      <c r="P8" s="48"/>
+      <c r="Q8" s="48"/>
+      <c r="R8" s="48"/>
+      <c r="S8" s="48"/>
+      <c r="T8" s="48"/>
+      <c r="U8" s="50"/>
+      <c r="V8" s="49"/>
+      <c r="W8" s="49"/>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" s="17">
         <v>4</v>
       </c>
@@ -7928,27 +7411,26 @@
         <f>RAWDATA!E5</f>
         <v>0</v>
       </c>
-      <c r="F9" s="52"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="50"/>
-      <c r="I9" s="50"/>
-      <c r="J9" s="50"/>
-      <c r="K9" s="50"/>
-      <c r="L9" s="50"/>
-      <c r="M9" s="50"/>
-      <c r="N9" s="50"/>
-      <c r="O9" s="50"/>
-      <c r="P9" s="50"/>
-      <c r="Q9" s="50"/>
-      <c r="R9" s="50"/>
-      <c r="S9" s="50"/>
-      <c r="T9" s="50"/>
-      <c r="U9" s="52"/>
-      <c r="V9" s="50"/>
-      <c r="W9" s="51"/>
-      <c r="X9" s="51"/>
-    </row>
-    <row r="10" spans="1:24" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="F9" s="50"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="48"/>
+      <c r="J9" s="48"/>
+      <c r="K9" s="48"/>
+      <c r="L9" s="48"/>
+      <c r="M9" s="48"/>
+      <c r="N9" s="48"/>
+      <c r="O9" s="48"/>
+      <c r="P9" s="48"/>
+      <c r="Q9" s="48"/>
+      <c r="R9" s="48"/>
+      <c r="S9" s="48"/>
+      <c r="T9" s="48"/>
+      <c r="U9" s="50"/>
+      <c r="V9" s="49"/>
+      <c r="W9" s="49"/>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
         <v>5</v>
       </c>
@@ -7968,27 +7450,26 @@
         <f>RAWDATA!E6</f>
         <v>0</v>
       </c>
-      <c r="F10" s="52"/>
-      <c r="G10" s="50"/>
-      <c r="H10" s="50"/>
-      <c r="I10" s="50"/>
-      <c r="J10" s="50"/>
-      <c r="K10" s="50"/>
-      <c r="L10" s="50"/>
-      <c r="M10" s="50"/>
-      <c r="N10" s="50"/>
-      <c r="O10" s="50"/>
-      <c r="P10" s="50"/>
-      <c r="Q10" s="50"/>
-      <c r="R10" s="50"/>
-      <c r="S10" s="50"/>
-      <c r="T10" s="50"/>
-      <c r="U10" s="52"/>
-      <c r="V10" s="50"/>
-      <c r="W10" s="51"/>
-      <c r="X10" s="51"/>
-    </row>
-    <row r="11" spans="1:24" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="F10" s="50"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="48"/>
+      <c r="I10" s="48"/>
+      <c r="J10" s="48"/>
+      <c r="K10" s="48"/>
+      <c r="L10" s="48"/>
+      <c r="M10" s="48"/>
+      <c r="N10" s="48"/>
+      <c r="O10" s="48"/>
+      <c r="P10" s="48"/>
+      <c r="Q10" s="48"/>
+      <c r="R10" s="48"/>
+      <c r="S10" s="48"/>
+      <c r="T10" s="48"/>
+      <c r="U10" s="50"/>
+      <c r="V10" s="49"/>
+      <c r="W10" s="49"/>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" s="17">
         <v>6</v>
       </c>
@@ -8008,27 +7489,26 @@
         <f>RAWDATA!E7</f>
         <v>0</v>
       </c>
-      <c r="F11" s="52"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="50"/>
-      <c r="I11" s="50"/>
-      <c r="J11" s="50"/>
-      <c r="K11" s="50"/>
-      <c r="L11" s="50"/>
-      <c r="M11" s="50"/>
-      <c r="N11" s="50"/>
-      <c r="O11" s="50"/>
-      <c r="P11" s="50"/>
-      <c r="Q11" s="50"/>
-      <c r="R11" s="50"/>
-      <c r="S11" s="50"/>
-      <c r="T11" s="50"/>
-      <c r="U11" s="52"/>
-      <c r="V11" s="50"/>
-      <c r="W11" s="51"/>
-      <c r="X11" s="51"/>
-    </row>
-    <row r="12" spans="1:24" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="F11" s="50"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="48"/>
+      <c r="J11" s="48"/>
+      <c r="K11" s="48"/>
+      <c r="L11" s="48"/>
+      <c r="M11" s="48"/>
+      <c r="N11" s="48"/>
+      <c r="O11" s="48"/>
+      <c r="P11" s="48"/>
+      <c r="Q11" s="48"/>
+      <c r="R11" s="48"/>
+      <c r="S11" s="48"/>
+      <c r="T11" s="48"/>
+      <c r="U11" s="50"/>
+      <c r="V11" s="49"/>
+      <c r="W11" s="49"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" s="17">
         <v>7</v>
       </c>
@@ -8048,27 +7528,26 @@
         <f>RAWDATA!E8</f>
         <v>0</v>
       </c>
-      <c r="F12" s="52"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="50"/>
-      <c r="I12" s="50"/>
-      <c r="J12" s="50"/>
-      <c r="K12" s="50"/>
-      <c r="L12" s="50"/>
-      <c r="M12" s="50"/>
-      <c r="N12" s="50"/>
-      <c r="O12" s="50"/>
-      <c r="P12" s="50"/>
-      <c r="Q12" s="50"/>
-      <c r="R12" s="50"/>
-      <c r="S12" s="50"/>
-      <c r="T12" s="50"/>
-      <c r="U12" s="52"/>
-      <c r="V12" s="50"/>
-      <c r="W12" s="51"/>
-      <c r="X12" s="51"/>
-    </row>
-    <row r="13" spans="1:24" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="F12" s="50"/>
+      <c r="G12" s="48"/>
+      <c r="H12" s="48"/>
+      <c r="I12" s="48"/>
+      <c r="J12" s="48"/>
+      <c r="K12" s="48"/>
+      <c r="L12" s="48"/>
+      <c r="M12" s="48"/>
+      <c r="N12" s="48"/>
+      <c r="O12" s="48"/>
+      <c r="P12" s="48"/>
+      <c r="Q12" s="48"/>
+      <c r="R12" s="48"/>
+      <c r="S12" s="48"/>
+      <c r="T12" s="48"/>
+      <c r="U12" s="50"/>
+      <c r="V12" s="49"/>
+      <c r="W12" s="49"/>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" s="17">
         <v>8</v>
       </c>
@@ -8088,27 +7567,26 @@
         <f>RAWDATA!E9</f>
         <v>0</v>
       </c>
-      <c r="F13" s="52"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="50"/>
-      <c r="I13" s="50"/>
-      <c r="J13" s="50"/>
-      <c r="K13" s="50"/>
-      <c r="L13" s="50"/>
-      <c r="M13" s="50"/>
-      <c r="N13" s="50"/>
-      <c r="O13" s="50"/>
-      <c r="P13" s="50"/>
-      <c r="Q13" s="50"/>
-      <c r="R13" s="50"/>
-      <c r="S13" s="50"/>
-      <c r="T13" s="50"/>
-      <c r="U13" s="52"/>
-      <c r="V13" s="50"/>
-      <c r="W13" s="51"/>
-      <c r="X13" s="51"/>
-    </row>
-    <row r="14" spans="1:24" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="F13" s="50"/>
+      <c r="G13" s="48"/>
+      <c r="H13" s="48"/>
+      <c r="I13" s="48"/>
+      <c r="J13" s="48"/>
+      <c r="K13" s="48"/>
+      <c r="L13" s="48"/>
+      <c r="M13" s="48"/>
+      <c r="N13" s="48"/>
+      <c r="O13" s="48"/>
+      <c r="P13" s="48"/>
+      <c r="Q13" s="48"/>
+      <c r="R13" s="48"/>
+      <c r="S13" s="48"/>
+      <c r="T13" s="48"/>
+      <c r="U13" s="50"/>
+      <c r="V13" s="49"/>
+      <c r="W13" s="49"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" s="17">
         <v>9</v>
       </c>
@@ -8128,27 +7606,26 @@
         <f>RAWDATA!E10</f>
         <v>0</v>
       </c>
-      <c r="F14" s="52"/>
-      <c r="G14" s="50"/>
-      <c r="H14" s="50"/>
-      <c r="I14" s="50"/>
-      <c r="J14" s="50"/>
-      <c r="K14" s="50"/>
-      <c r="L14" s="50"/>
-      <c r="M14" s="50"/>
-      <c r="N14" s="50"/>
-      <c r="O14" s="50"/>
-      <c r="P14" s="50"/>
-      <c r="Q14" s="50"/>
-      <c r="R14" s="50"/>
-      <c r="S14" s="50"/>
-      <c r="T14" s="50"/>
-      <c r="U14" s="52"/>
-      <c r="V14" s="50"/>
-      <c r="W14" s="51"/>
-      <c r="X14" s="51"/>
-    </row>
-    <row r="15" spans="1:24" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="F14" s="50"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="48"/>
+      <c r="K14" s="48"/>
+      <c r="L14" s="48"/>
+      <c r="M14" s="48"/>
+      <c r="N14" s="48"/>
+      <c r="O14" s="48"/>
+      <c r="P14" s="48"/>
+      <c r="Q14" s="48"/>
+      <c r="R14" s="48"/>
+      <c r="S14" s="48"/>
+      <c r="T14" s="48"/>
+      <c r="U14" s="50"/>
+      <c r="V14" s="49"/>
+      <c r="W14" s="49"/>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" s="17">
         <v>10</v>
       </c>
@@ -8168,27 +7645,26 @@
         <f>RAWDATA!E11</f>
         <v>0</v>
       </c>
-      <c r="F15" s="52"/>
-      <c r="G15" s="50"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="50"/>
-      <c r="J15" s="50"/>
-      <c r="K15" s="50"/>
-      <c r="L15" s="50"/>
-      <c r="M15" s="50"/>
-      <c r="N15" s="50"/>
-      <c r="O15" s="50"/>
-      <c r="P15" s="50"/>
-      <c r="Q15" s="50"/>
-      <c r="R15" s="50"/>
-      <c r="S15" s="50"/>
-      <c r="T15" s="50"/>
-      <c r="U15" s="52"/>
-      <c r="V15" s="50"/>
-      <c r="W15" s="51"/>
-      <c r="X15" s="51"/>
-    </row>
-    <row r="16" spans="1:24" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="F15" s="50"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="48"/>
+      <c r="J15" s="48"/>
+      <c r="K15" s="48"/>
+      <c r="L15" s="48"/>
+      <c r="M15" s="48"/>
+      <c r="N15" s="48"/>
+      <c r="O15" s="48"/>
+      <c r="P15" s="48"/>
+      <c r="Q15" s="48"/>
+      <c r="R15" s="48"/>
+      <c r="S15" s="48"/>
+      <c r="T15" s="48"/>
+      <c r="U15" s="50"/>
+      <c r="V15" s="49"/>
+      <c r="W15" s="49"/>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" s="17">
         <v>11</v>
       </c>
@@ -8208,27 +7684,26 @@
         <f>RAWDATA!E12</f>
         <v>0</v>
       </c>
-      <c r="F16" s="52"/>
-      <c r="G16" s="50"/>
-      <c r="H16" s="50"/>
-      <c r="I16" s="50"/>
-      <c r="J16" s="50"/>
-      <c r="K16" s="50"/>
-      <c r="L16" s="50"/>
-      <c r="M16" s="50"/>
-      <c r="N16" s="50"/>
-      <c r="O16" s="50"/>
-      <c r="P16" s="50"/>
-      <c r="Q16" s="50"/>
-      <c r="R16" s="50"/>
-      <c r="S16" s="50"/>
-      <c r="T16" s="50"/>
-      <c r="U16" s="52"/>
-      <c r="V16" s="50"/>
-      <c r="W16" s="51"/>
-      <c r="X16" s="51"/>
-    </row>
-    <row r="17" spans="1:24" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="F16" s="50"/>
+      <c r="G16" s="48"/>
+      <c r="H16" s="48"/>
+      <c r="I16" s="48"/>
+      <c r="J16" s="48"/>
+      <c r="K16" s="48"/>
+      <c r="L16" s="48"/>
+      <c r="M16" s="48"/>
+      <c r="N16" s="48"/>
+      <c r="O16" s="48"/>
+      <c r="P16" s="48"/>
+      <c r="Q16" s="48"/>
+      <c r="R16" s="48"/>
+      <c r="S16" s="48"/>
+      <c r="T16" s="48"/>
+      <c r="U16" s="50"/>
+      <c r="V16" s="49"/>
+      <c r="W16" s="49"/>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" s="17">
         <v>12</v>
       </c>
@@ -8248,27 +7723,26 @@
         <f>RAWDATA!E13</f>
         <v>0</v>
       </c>
-      <c r="F17" s="52"/>
-      <c r="G17" s="50"/>
-      <c r="H17" s="50"/>
-      <c r="I17" s="50"/>
-      <c r="J17" s="50"/>
-      <c r="K17" s="50"/>
-      <c r="L17" s="50"/>
-      <c r="M17" s="50"/>
-      <c r="N17" s="50"/>
-      <c r="O17" s="50"/>
-      <c r="P17" s="50"/>
-      <c r="Q17" s="50"/>
-      <c r="R17" s="50"/>
-      <c r="S17" s="50"/>
-      <c r="T17" s="50"/>
-      <c r="U17" s="52"/>
-      <c r="V17" s="50"/>
-      <c r="W17" s="51"/>
-      <c r="X17" s="51"/>
-    </row>
-    <row r="18" spans="1:24" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="F17" s="50"/>
+      <c r="G17" s="48"/>
+      <c r="H17" s="48"/>
+      <c r="I17" s="48"/>
+      <c r="J17" s="48"/>
+      <c r="K17" s="48"/>
+      <c r="L17" s="48"/>
+      <c r="M17" s="48"/>
+      <c r="N17" s="48"/>
+      <c r="O17" s="48"/>
+      <c r="P17" s="48"/>
+      <c r="Q17" s="48"/>
+      <c r="R17" s="48"/>
+      <c r="S17" s="48"/>
+      <c r="T17" s="48"/>
+      <c r="U17" s="50"/>
+      <c r="V17" s="49"/>
+      <c r="W17" s="49"/>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" s="17">
         <v>13</v>
       </c>
@@ -8288,27 +7762,26 @@
         <f>RAWDATA!E14</f>
         <v>0</v>
       </c>
-      <c r="F18" s="52"/>
-      <c r="G18" s="50"/>
-      <c r="H18" s="50"/>
-      <c r="I18" s="50"/>
-      <c r="J18" s="50"/>
-      <c r="K18" s="50"/>
-      <c r="L18" s="50"/>
-      <c r="M18" s="50"/>
-      <c r="N18" s="50"/>
-      <c r="O18" s="50"/>
-      <c r="P18" s="50"/>
-      <c r="Q18" s="50"/>
-      <c r="R18" s="50"/>
-      <c r="S18" s="50"/>
-      <c r="T18" s="50"/>
-      <c r="U18" s="52"/>
-      <c r="V18" s="50"/>
-      <c r="W18" s="51"/>
-      <c r="X18" s="51"/>
-    </row>
-    <row r="19" spans="1:24" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="F18" s="50"/>
+      <c r="G18" s="48"/>
+      <c r="H18" s="48"/>
+      <c r="I18" s="48"/>
+      <c r="J18" s="48"/>
+      <c r="K18" s="48"/>
+      <c r="L18" s="48"/>
+      <c r="M18" s="48"/>
+      <c r="N18" s="48"/>
+      <c r="O18" s="48"/>
+      <c r="P18" s="48"/>
+      <c r="Q18" s="48"/>
+      <c r="R18" s="48"/>
+      <c r="S18" s="48"/>
+      <c r="T18" s="48"/>
+      <c r="U18" s="50"/>
+      <c r="V18" s="49"/>
+      <c r="W18" s="49"/>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" s="17">
         <v>14</v>
       </c>
@@ -8328,27 +7801,26 @@
         <f>RAWDATA!E15</f>
         <v>0</v>
       </c>
-      <c r="F19" s="52"/>
-      <c r="G19" s="50"/>
-      <c r="H19" s="50"/>
-      <c r="I19" s="50"/>
-      <c r="J19" s="50"/>
-      <c r="K19" s="50"/>
-      <c r="L19" s="50"/>
-      <c r="M19" s="50"/>
-      <c r="N19" s="50"/>
-      <c r="O19" s="50"/>
-      <c r="P19" s="50"/>
-      <c r="Q19" s="50"/>
-      <c r="R19" s="50"/>
-      <c r="S19" s="50"/>
-      <c r="T19" s="50"/>
-      <c r="U19" s="52"/>
-      <c r="V19" s="50"/>
-      <c r="W19" s="51"/>
-      <c r="X19" s="51"/>
-    </row>
-    <row r="20" spans="1:24" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="F19" s="50"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="48"/>
+      <c r="K19" s="48"/>
+      <c r="L19" s="48"/>
+      <c r="M19" s="48"/>
+      <c r="N19" s="48"/>
+      <c r="O19" s="48"/>
+      <c r="P19" s="48"/>
+      <c r="Q19" s="48"/>
+      <c r="R19" s="48"/>
+      <c r="S19" s="48"/>
+      <c r="T19" s="48"/>
+      <c r="U19" s="50"/>
+      <c r="V19" s="49"/>
+      <c r="W19" s="49"/>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" s="17">
         <v>15</v>
       </c>
@@ -8368,27 +7840,26 @@
         <f>RAWDATA!E16</f>
         <v>0</v>
       </c>
-      <c r="F20" s="52"/>
-      <c r="G20" s="50"/>
-      <c r="H20" s="50"/>
-      <c r="I20" s="50"/>
-      <c r="J20" s="50"/>
-      <c r="K20" s="50"/>
-      <c r="L20" s="50"/>
-      <c r="M20" s="50"/>
-      <c r="N20" s="50"/>
-      <c r="O20" s="50"/>
-      <c r="P20" s="50"/>
-      <c r="Q20" s="50"/>
-      <c r="R20" s="50"/>
-      <c r="S20" s="50"/>
-      <c r="T20" s="50"/>
-      <c r="U20" s="52"/>
-      <c r="V20" s="50"/>
-      <c r="W20" s="51"/>
-      <c r="X20" s="51"/>
-    </row>
-    <row r="21" spans="1:24" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="F20" s="50"/>
+      <c r="G20" s="48"/>
+      <c r="H20" s="48"/>
+      <c r="I20" s="48"/>
+      <c r="J20" s="48"/>
+      <c r="K20" s="48"/>
+      <c r="L20" s="48"/>
+      <c r="M20" s="48"/>
+      <c r="N20" s="48"/>
+      <c r="O20" s="48"/>
+      <c r="P20" s="48"/>
+      <c r="Q20" s="48"/>
+      <c r="R20" s="48"/>
+      <c r="S20" s="48"/>
+      <c r="T20" s="48"/>
+      <c r="U20" s="50"/>
+      <c r="V20" s="49"/>
+      <c r="W20" s="49"/>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" s="17">
         <v>16</v>
       </c>
@@ -8408,27 +7879,26 @@
         <f>RAWDATA!E17</f>
         <v>0</v>
       </c>
-      <c r="F21" s="52"/>
-      <c r="G21" s="50"/>
-      <c r="H21" s="50"/>
-      <c r="I21" s="50"/>
-      <c r="J21" s="50"/>
-      <c r="K21" s="50"/>
-      <c r="L21" s="50"/>
-      <c r="M21" s="50"/>
-      <c r="N21" s="50"/>
-      <c r="O21" s="50"/>
-      <c r="P21" s="50"/>
-      <c r="Q21" s="50"/>
-      <c r="R21" s="50"/>
-      <c r="S21" s="50"/>
-      <c r="T21" s="50"/>
-      <c r="U21" s="52"/>
-      <c r="V21" s="50"/>
-      <c r="W21" s="51"/>
-      <c r="X21" s="51"/>
-    </row>
-    <row r="22" spans="1:24" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="F21" s="50"/>
+      <c r="G21" s="48"/>
+      <c r="H21" s="48"/>
+      <c r="I21" s="48"/>
+      <c r="J21" s="48"/>
+      <c r="K21" s="48"/>
+      <c r="L21" s="48"/>
+      <c r="M21" s="48"/>
+      <c r="N21" s="48"/>
+      <c r="O21" s="48"/>
+      <c r="P21" s="48"/>
+      <c r="Q21" s="48"/>
+      <c r="R21" s="48"/>
+      <c r="S21" s="48"/>
+      <c r="T21" s="48"/>
+      <c r="U21" s="50"/>
+      <c r="V21" s="49"/>
+      <c r="W21" s="49"/>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" s="17">
         <v>17</v>
       </c>
@@ -8448,27 +7918,26 @@
         <f>RAWDATA!E18</f>
         <v>0</v>
       </c>
-      <c r="F22" s="52"/>
-      <c r="G22" s="50"/>
-      <c r="H22" s="50"/>
-      <c r="I22" s="50"/>
-      <c r="J22" s="50"/>
-      <c r="K22" s="50"/>
-      <c r="L22" s="50"/>
-      <c r="M22" s="50"/>
-      <c r="N22" s="50"/>
-      <c r="O22" s="50"/>
-      <c r="P22" s="50"/>
-      <c r="Q22" s="50"/>
-      <c r="R22" s="50"/>
-      <c r="S22" s="50"/>
-      <c r="T22" s="50"/>
-      <c r="U22" s="52"/>
-      <c r="V22" s="50"/>
-      <c r="W22" s="51"/>
-      <c r="X22" s="51"/>
-    </row>
-    <row r="23" spans="1:24" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="F22" s="50"/>
+      <c r="G22" s="48"/>
+      <c r="H22" s="48"/>
+      <c r="I22" s="48"/>
+      <c r="J22" s="48"/>
+      <c r="K22" s="48"/>
+      <c r="L22" s="48"/>
+      <c r="M22" s="48"/>
+      <c r="N22" s="48"/>
+      <c r="O22" s="48"/>
+      <c r="P22" s="48"/>
+      <c r="Q22" s="48"/>
+      <c r="R22" s="48"/>
+      <c r="S22" s="48"/>
+      <c r="T22" s="48"/>
+      <c r="U22" s="50"/>
+      <c r="V22" s="49"/>
+      <c r="W22" s="49"/>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23" s="17">
         <v>18</v>
       </c>
@@ -8488,27 +7957,26 @@
         <f>RAWDATA!E19</f>
         <v>0</v>
       </c>
-      <c r="F23" s="52"/>
-      <c r="G23" s="50"/>
-      <c r="H23" s="50"/>
-      <c r="I23" s="50"/>
-      <c r="J23" s="50"/>
-      <c r="K23" s="50"/>
-      <c r="L23" s="50"/>
-      <c r="M23" s="50"/>
-      <c r="N23" s="50"/>
-      <c r="O23" s="50"/>
-      <c r="P23" s="50"/>
-      <c r="Q23" s="50"/>
-      <c r="R23" s="50"/>
-      <c r="S23" s="50"/>
-      <c r="T23" s="50"/>
-      <c r="U23" s="52"/>
-      <c r="V23" s="50"/>
-      <c r="W23" s="51"/>
-      <c r="X23" s="51"/>
-    </row>
-    <row r="24" spans="1:24" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="F23" s="50"/>
+      <c r="G23" s="48"/>
+      <c r="H23" s="48"/>
+      <c r="I23" s="48"/>
+      <c r="J23" s="48"/>
+      <c r="K23" s="48"/>
+      <c r="L23" s="48"/>
+      <c r="M23" s="48"/>
+      <c r="N23" s="48"/>
+      <c r="O23" s="48"/>
+      <c r="P23" s="48"/>
+      <c r="Q23" s="48"/>
+      <c r="R23" s="48"/>
+      <c r="S23" s="48"/>
+      <c r="T23" s="48"/>
+      <c r="U23" s="50"/>
+      <c r="V23" s="49"/>
+      <c r="W23" s="49"/>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24" s="17">
         <v>19</v>
       </c>
@@ -8528,27 +7996,26 @@
         <f>RAWDATA!E20</f>
         <v>0</v>
       </c>
-      <c r="F24" s="52"/>
-      <c r="G24" s="50"/>
-      <c r="H24" s="50"/>
-      <c r="I24" s="50"/>
-      <c r="J24" s="50"/>
-      <c r="K24" s="50"/>
-      <c r="L24" s="50"/>
-      <c r="M24" s="50"/>
-      <c r="N24" s="50"/>
-      <c r="O24" s="50"/>
-      <c r="P24" s="50"/>
-      <c r="Q24" s="50"/>
-      <c r="R24" s="50"/>
-      <c r="S24" s="50"/>
-      <c r="T24" s="50"/>
-      <c r="U24" s="52"/>
-      <c r="V24" s="50"/>
-      <c r="W24" s="51"/>
-      <c r="X24" s="51"/>
-    </row>
-    <row r="25" spans="1:24" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="F24" s="50"/>
+      <c r="G24" s="48"/>
+      <c r="H24" s="48"/>
+      <c r="I24" s="48"/>
+      <c r="J24" s="48"/>
+      <c r="K24" s="48"/>
+      <c r="L24" s="48"/>
+      <c r="M24" s="48"/>
+      <c r="N24" s="48"/>
+      <c r="O24" s="48"/>
+      <c r="P24" s="48"/>
+      <c r="Q24" s="48"/>
+      <c r="R24" s="48"/>
+      <c r="S24" s="48"/>
+      <c r="T24" s="48"/>
+      <c r="U24" s="50"/>
+      <c r="V24" s="49"/>
+      <c r="W24" s="49"/>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" s="17">
         <v>20</v>
       </c>
@@ -8568,27 +8035,26 @@
         <f>RAWDATA!E21</f>
         <v>0</v>
       </c>
-      <c r="F25" s="52"/>
-      <c r="G25" s="50"/>
-      <c r="H25" s="50"/>
-      <c r="I25" s="50"/>
-      <c r="J25" s="50"/>
-      <c r="K25" s="50"/>
-      <c r="L25" s="50"/>
-      <c r="M25" s="50"/>
-      <c r="N25" s="50"/>
-      <c r="O25" s="50"/>
-      <c r="P25" s="50"/>
-      <c r="Q25" s="50"/>
-      <c r="R25" s="50"/>
-      <c r="S25" s="50"/>
-      <c r="T25" s="50"/>
-      <c r="U25" s="52"/>
-      <c r="V25" s="50"/>
-      <c r="W25" s="51"/>
-      <c r="X25" s="51"/>
-    </row>
-    <row r="26" spans="1:24" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="F25" s="50"/>
+      <c r="G25" s="48"/>
+      <c r="H25" s="48"/>
+      <c r="I25" s="48"/>
+      <c r="J25" s="48"/>
+      <c r="K25" s="48"/>
+      <c r="L25" s="48"/>
+      <c r="M25" s="48"/>
+      <c r="N25" s="48"/>
+      <c r="O25" s="48"/>
+      <c r="P25" s="48"/>
+      <c r="Q25" s="48"/>
+      <c r="R25" s="48"/>
+      <c r="S25" s="48"/>
+      <c r="T25" s="48"/>
+      <c r="U25" s="50"/>
+      <c r="V25" s="49"/>
+      <c r="W25" s="49"/>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26" s="17">
         <v>21</v>
       </c>
@@ -8608,27 +8074,26 @@
         <f>RAWDATA!E22</f>
         <v>0</v>
       </c>
-      <c r="F26" s="52"/>
-      <c r="G26" s="50"/>
-      <c r="H26" s="50"/>
-      <c r="I26" s="50"/>
-      <c r="J26" s="50"/>
-      <c r="K26" s="50"/>
-      <c r="L26" s="50"/>
-      <c r="M26" s="50"/>
-      <c r="N26" s="50"/>
-      <c r="O26" s="50"/>
-      <c r="P26" s="50"/>
-      <c r="Q26" s="50"/>
-      <c r="R26" s="50"/>
-      <c r="S26" s="50"/>
-      <c r="T26" s="50"/>
-      <c r="U26" s="52"/>
-      <c r="V26" s="50"/>
-      <c r="W26" s="51"/>
-      <c r="X26" s="51"/>
-    </row>
-    <row r="27" spans="1:24" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="F26" s="50"/>
+      <c r="G26" s="48"/>
+      <c r="H26" s="48"/>
+      <c r="I26" s="48"/>
+      <c r="J26" s="48"/>
+      <c r="K26" s="48"/>
+      <c r="L26" s="48"/>
+      <c r="M26" s="48"/>
+      <c r="N26" s="48"/>
+      <c r="O26" s="48"/>
+      <c r="P26" s="48"/>
+      <c r="Q26" s="48"/>
+      <c r="R26" s="48"/>
+      <c r="S26" s="48"/>
+      <c r="T26" s="48"/>
+      <c r="U26" s="50"/>
+      <c r="V26" s="49"/>
+      <c r="W26" s="49"/>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27" s="17">
         <v>22</v>
       </c>
@@ -8648,27 +8113,26 @@
         <f>RAWDATA!E23</f>
         <v>0</v>
       </c>
-      <c r="F27" s="52"/>
-      <c r="G27" s="50"/>
-      <c r="H27" s="50"/>
-      <c r="I27" s="50"/>
-      <c r="J27" s="50"/>
-      <c r="K27" s="50"/>
-      <c r="L27" s="50"/>
-      <c r="M27" s="50"/>
-      <c r="N27" s="50"/>
-      <c r="O27" s="50"/>
-      <c r="P27" s="50"/>
-      <c r="Q27" s="50"/>
-      <c r="R27" s="50"/>
-      <c r="S27" s="50"/>
-      <c r="T27" s="50"/>
-      <c r="U27" s="52"/>
-      <c r="V27" s="50"/>
-      <c r="W27" s="51"/>
-      <c r="X27" s="51"/>
-    </row>
-    <row r="28" spans="1:24" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="F27" s="50"/>
+      <c r="G27" s="48"/>
+      <c r="H27" s="48"/>
+      <c r="I27" s="48"/>
+      <c r="J27" s="48"/>
+      <c r="K27" s="48"/>
+      <c r="L27" s="48"/>
+      <c r="M27" s="48"/>
+      <c r="N27" s="48"/>
+      <c r="O27" s="48"/>
+      <c r="P27" s="48"/>
+      <c r="Q27" s="48"/>
+      <c r="R27" s="48"/>
+      <c r="S27" s="48"/>
+      <c r="T27" s="48"/>
+      <c r="U27" s="50"/>
+      <c r="V27" s="49"/>
+      <c r="W27" s="49"/>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A28" s="17">
         <v>23</v>
       </c>
@@ -8688,27 +8152,26 @@
         <f>RAWDATA!E24</f>
         <v>0</v>
       </c>
-      <c r="F28" s="52"/>
-      <c r="G28" s="50"/>
-      <c r="H28" s="50"/>
-      <c r="I28" s="50"/>
-      <c r="J28" s="50"/>
-      <c r="K28" s="50"/>
-      <c r="L28" s="50"/>
-      <c r="M28" s="50"/>
-      <c r="N28" s="50"/>
-      <c r="O28" s="50"/>
-      <c r="P28" s="50"/>
-      <c r="Q28" s="50"/>
-      <c r="R28" s="50"/>
-      <c r="S28" s="50"/>
-      <c r="T28" s="50"/>
-      <c r="U28" s="52"/>
-      <c r="V28" s="50"/>
-      <c r="W28" s="51"/>
-      <c r="X28" s="51"/>
-    </row>
-    <row r="29" spans="1:24" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="F28" s="50"/>
+      <c r="G28" s="48"/>
+      <c r="H28" s="48"/>
+      <c r="I28" s="48"/>
+      <c r="J28" s="48"/>
+      <c r="K28" s="48"/>
+      <c r="L28" s="48"/>
+      <c r="M28" s="48"/>
+      <c r="N28" s="48"/>
+      <c r="O28" s="48"/>
+      <c r="P28" s="48"/>
+      <c r="Q28" s="48"/>
+      <c r="R28" s="48"/>
+      <c r="S28" s="48"/>
+      <c r="T28" s="48"/>
+      <c r="U28" s="50"/>
+      <c r="V28" s="49"/>
+      <c r="W28" s="49"/>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29" s="17">
         <v>24</v>
       </c>
@@ -8728,27 +8191,26 @@
         <f>RAWDATA!E25</f>
         <v>0</v>
       </c>
-      <c r="F29" s="52"/>
-      <c r="G29" s="50"/>
-      <c r="H29" s="50"/>
-      <c r="I29" s="50"/>
-      <c r="J29" s="50"/>
-      <c r="K29" s="50"/>
-      <c r="L29" s="50"/>
-      <c r="M29" s="50"/>
-      <c r="N29" s="50"/>
-      <c r="O29" s="50"/>
-      <c r="P29" s="50"/>
-      <c r="Q29" s="50"/>
-      <c r="R29" s="50"/>
-      <c r="S29" s="50"/>
-      <c r="T29" s="50"/>
-      <c r="U29" s="52"/>
-      <c r="V29" s="50"/>
-      <c r="W29" s="51"/>
-      <c r="X29" s="51"/>
-    </row>
-    <row r="30" spans="1:24" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="F29" s="50"/>
+      <c r="G29" s="48"/>
+      <c r="H29" s="48"/>
+      <c r="I29" s="48"/>
+      <c r="J29" s="48"/>
+      <c r="K29" s="48"/>
+      <c r="L29" s="48"/>
+      <c r="M29" s="48"/>
+      <c r="N29" s="48"/>
+      <c r="O29" s="48"/>
+      <c r="P29" s="48"/>
+      <c r="Q29" s="48"/>
+      <c r="R29" s="48"/>
+      <c r="S29" s="48"/>
+      <c r="T29" s="48"/>
+      <c r="U29" s="50"/>
+      <c r="V29" s="49"/>
+      <c r="W29" s="49"/>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A30" s="17">
         <v>25</v>
       </c>
@@ -8768,41 +8230,39 @@
         <f>RAWDATA!E26</f>
         <v>0</v>
       </c>
-      <c r="F30" s="53"/>
-      <c r="G30" s="50"/>
-      <c r="H30" s="50"/>
-      <c r="I30" s="50"/>
-      <c r="J30" s="50"/>
-      <c r="K30" s="50"/>
-      <c r="L30" s="50"/>
-      <c r="M30" s="50"/>
-      <c r="N30" s="50"/>
-      <c r="O30" s="50"/>
-      <c r="P30" s="50"/>
-      <c r="Q30" s="50"/>
-      <c r="R30" s="50"/>
-      <c r="S30" s="50"/>
-      <c r="T30" s="50"/>
-      <c r="U30" s="53"/>
-      <c r="V30" s="50"/>
-      <c r="W30" s="51"/>
-      <c r="X30" s="51"/>
+      <c r="F30" s="51"/>
+      <c r="G30" s="48"/>
+      <c r="H30" s="48"/>
+      <c r="I30" s="48"/>
+      <c r="J30" s="48"/>
+      <c r="K30" s="48"/>
+      <c r="L30" s="48"/>
+      <c r="M30" s="48"/>
+      <c r="N30" s="48"/>
+      <c r="O30" s="48"/>
+      <c r="P30" s="48"/>
+      <c r="Q30" s="48"/>
+      <c r="R30" s="48"/>
+      <c r="S30" s="48"/>
+      <c r="T30" s="48"/>
+      <c r="U30" s="51"/>
+      <c r="V30" s="49"/>
+      <c r="W30" s="49"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" formatColumns="0" selectLockedCells="1"/>
-  <mergeCells count="12">
+  <mergeCells count="11">
+    <mergeCell ref="V4:V5"/>
     <mergeCell ref="W4:W5"/>
-    <mergeCell ref="X4:X5"/>
-    <mergeCell ref="A1:X1"/>
-    <mergeCell ref="A2:X2"/>
+    <mergeCell ref="A1:W1"/>
+    <mergeCell ref="A2:W2"/>
     <mergeCell ref="A3:E3"/>
-    <mergeCell ref="G3:X3"/>
+    <mergeCell ref="G3:W3"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="E4:E5"/>
-    <mergeCell ref="V4:V5"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="1.299212598425197" bottom="1.1023622047244095" header="0.70866141732283472" footer="0.55118110236220474"/>
   <headerFooter>
@@ -8819,47 +8279,47 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18" style="64" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="67" customWidth="1"/>
-    <col min="5" max="5" width="18.109375" style="66" customWidth="1"/>
-    <col min="6" max="6" width="35.44140625" customWidth="1"/>
-    <col min="7" max="7" width="31.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="46.44140625" customWidth="1"/>
+    <col min="1" max="1" width="18" style="61" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="64" customWidth="1"/>
+    <col min="5" max="5" width="18.140625" style="63" customWidth="1"/>
+    <col min="6" max="6" width="35.42578125" customWidth="1"/>
+    <col min="7" max="7" width="31.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="64" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="61" t="s">
         <v>27</v>
       </c>
       <c r="B1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="62" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="63" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1" t="s">
         <v>55</v>
       </c>
-      <c r="C1" t="s">
+      <c r="H1" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="65" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="66" t="s">
-        <v>57</v>
-      </c>
-      <c r="F1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="64" t="str">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="61" t="str">
         <f>IF(Notenliste!D2=0," ",Notenliste!D2)</f>
         <v>applicant.tag</v>
       </c>
@@ -8867,17 +8327,17 @@
         <f>IF(Notenliste!D2&lt;&gt;0,IF(Notenliste!I2&lt;&gt;0,Notenliste!I2,Notenliste!$B$33)," ")</f>
         <v>attendance.ects_points</v>
       </c>
-      <c r="D2" s="68" t="e">
+      <c r="D2" s="65" t="e">
         <f>IF(Notenliste!D2=0," ",IF(Notenliste!F2="KP"," ",IF(Notenliste!F2="NB","nicht bestanden",IF(OR(Notenliste!H2="x", Notenliste!H2="X"),"bestanden",Notenliste!F2))))</f>
         <v>#N/A</v>
       </c>
-      <c r="E2" s="66" t="str">
+      <c r="E2" s="63" t="str">
         <f>IF(Notenliste!D2&lt;&gt;0,Notenliste!$B$37," ")</f>
         <v>exam_date</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="64" t="str">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="61" t="str">
         <f>IF(Notenliste!D3=0," ",Notenliste!D3)</f>
         <v xml:space="preserve"> </v>
       </c>
@@ -8885,17 +8345,17 @@
         <f>IF(Notenliste!D3&lt;&gt;0,IF(Notenliste!I3&lt;&gt;0,Notenliste!I3,Notenliste!$B$33)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D3" s="68" t="str">
+      <c r="D3" s="65" t="str">
         <f>IF(Notenliste!D3=0," ",IF(Notenliste!F3="KP"," ",IF(Notenliste!F3="NB","nicht bestanden",IF(OR(Notenliste!H3="x", Notenliste!H3="X"),"bestanden",Notenliste!F3))))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="E3" s="66" t="str">
+      <c r="E3" s="63" t="str">
         <f>IF(Notenliste!D3&lt;&gt;0,Notenliste!$B$37," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="64" t="str">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="61" t="str">
         <f>IF(Notenliste!D4=0," ",Notenliste!D4)</f>
         <v xml:space="preserve"> </v>
       </c>
@@ -8903,17 +8363,17 @@
         <f>IF(Notenliste!D4&lt;&gt;0,IF(Notenliste!I4&lt;&gt;0,Notenliste!I4,Notenliste!$B$33)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D4" s="68" t="str">
+      <c r="D4" s="65" t="str">
         <f>IF(Notenliste!D4=0," ",IF(Notenliste!F4="KP"," ",IF(Notenliste!F4="NB","nicht bestanden",IF(OR(Notenliste!H4="x", Notenliste!H4="X"),"bestanden",Notenliste!F4))))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="E4" s="66" t="str">
+      <c r="E4" s="63" t="str">
         <f>IF(Notenliste!D4&lt;&gt;0,Notenliste!$B$37," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="64" t="str">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="61" t="str">
         <f>IF(Notenliste!D5=0," ",Notenliste!D5)</f>
         <v xml:space="preserve"> </v>
       </c>
@@ -8921,17 +8381,17 @@
         <f>IF(Notenliste!D5&lt;&gt;0,IF(Notenliste!I5&lt;&gt;0,Notenliste!I5,Notenliste!$B$33)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D5" s="68" t="str">
+      <c r="D5" s="65" t="str">
         <f>IF(Notenliste!D5=0," ",IF(Notenliste!F5="KP"," ",IF(Notenliste!F5="NB","nicht bestanden",IF(OR(Notenliste!H5="x", Notenliste!H5="X"),"bestanden",Notenliste!F5))))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="E5" s="66" t="str">
+      <c r="E5" s="63" t="str">
         <f>IF(Notenliste!D5&lt;&gt;0,Notenliste!$B$37," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="64" t="str">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="61" t="str">
         <f>IF(Notenliste!D6=0," ",Notenliste!D6)</f>
         <v xml:space="preserve"> </v>
       </c>
@@ -8939,17 +8399,17 @@
         <f>IF(Notenliste!D6&lt;&gt;0,IF(Notenliste!I6&lt;&gt;0,Notenliste!I6,Notenliste!$B$33)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D6" s="68" t="str">
+      <c r="D6" s="65" t="str">
         <f>IF(Notenliste!D6=0," ",IF(Notenliste!F6="KP"," ",IF(Notenliste!F6="NB","nicht bestanden",IF(OR(Notenliste!H6="x", Notenliste!H6="X"),"bestanden",Notenliste!F6))))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="E6" s="66" t="str">
+      <c r="E6" s="63" t="str">
         <f>IF(Notenliste!D6&lt;&gt;0,Notenliste!$B$37," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="64" t="str">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="61" t="str">
         <f>IF(Notenliste!D7=0," ",Notenliste!D7)</f>
         <v xml:space="preserve"> </v>
       </c>
@@ -8957,17 +8417,17 @@
         <f>IF(Notenliste!D7&lt;&gt;0,IF(Notenliste!I7&lt;&gt;0,Notenliste!I7,Notenliste!$B$33)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D7" s="68" t="str">
+      <c r="D7" s="65" t="str">
         <f>IF(Notenliste!D7=0," ",IF(Notenliste!F7="KP"," ",IF(Notenliste!F7="NB","nicht bestanden",IF(OR(Notenliste!H7="x", Notenliste!H7="X"),"bestanden",Notenliste!F7))))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="E7" s="66" t="str">
+      <c r="E7" s="63" t="str">
         <f>IF(Notenliste!D7&lt;&gt;0,Notenliste!$B$37," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="64" t="str">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="61" t="str">
         <f>IF(Notenliste!D8=0," ",Notenliste!D8)</f>
         <v xml:space="preserve"> </v>
       </c>
@@ -8975,17 +8435,17 @@
         <f>IF(Notenliste!D8&lt;&gt;0,IF(Notenliste!I8&lt;&gt;0,Notenliste!I8,Notenliste!$B$33)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D8" s="68" t="str">
+      <c r="D8" s="65" t="str">
         <f>IF(Notenliste!D8=0," ",IF(Notenliste!F8="KP"," ",IF(Notenliste!F8="NB","nicht bestanden",IF(OR(Notenliste!H8="x", Notenliste!H8="X"),"bestanden",Notenliste!F8))))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="E8" s="66" t="str">
+      <c r="E8" s="63" t="str">
         <f>IF(Notenliste!D8&lt;&gt;0,Notenliste!$B$37," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="64" t="str">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="61" t="str">
         <f>IF(Notenliste!D9=0," ",Notenliste!D9)</f>
         <v xml:space="preserve"> </v>
       </c>
@@ -8993,17 +8453,17 @@
         <f>IF(Notenliste!D9&lt;&gt;0,IF(Notenliste!I9&lt;&gt;0,Notenliste!I9,Notenliste!$B$33)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D9" s="68" t="str">
+      <c r="D9" s="65" t="str">
         <f>IF(Notenliste!D9=0," ",IF(Notenliste!F9="KP"," ",IF(Notenliste!F9="NB","nicht bestanden",IF(OR(Notenliste!H9="x", Notenliste!H9="X"),"bestanden",Notenliste!F9))))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="E9" s="66" t="str">
+      <c r="E9" s="63" t="str">
         <f>IF(Notenliste!D9&lt;&gt;0,Notenliste!$B$37," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="64" t="str">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="61" t="str">
         <f>IF(Notenliste!D10=0," ",Notenliste!D10)</f>
         <v xml:space="preserve"> </v>
       </c>
@@ -9011,17 +8471,17 @@
         <f>IF(Notenliste!D10&lt;&gt;0,IF(Notenliste!I10&lt;&gt;0,Notenliste!I10,Notenliste!$B$33)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D10" s="68" t="str">
+      <c r="D10" s="65" t="str">
         <f>IF(Notenliste!D10=0," ",IF(Notenliste!F10="KP"," ",IF(Notenliste!F10="NB","nicht bestanden",IF(OR(Notenliste!H10="x", Notenliste!H10="X"),"bestanden",Notenliste!F10))))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="E10" s="66" t="str">
+      <c r="E10" s="63" t="str">
         <f>IF(Notenliste!D10&lt;&gt;0,Notenliste!$B$37," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="64" t="str">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="61" t="str">
         <f>IF(Notenliste!D11=0," ",Notenliste!D11)</f>
         <v xml:space="preserve"> </v>
       </c>
@@ -9029,17 +8489,17 @@
         <f>IF(Notenliste!D11&lt;&gt;0,IF(Notenliste!I11&lt;&gt;0,Notenliste!I11,Notenliste!$B$33)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D11" s="68" t="str">
+      <c r="D11" s="65" t="str">
         <f>IF(Notenliste!D11=0," ",IF(Notenliste!F11="KP"," ",IF(Notenliste!F11="NB","nicht bestanden",IF(OR(Notenliste!H11="x", Notenliste!H11="X"),"bestanden",Notenliste!F11))))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="E11" s="66" t="str">
+      <c r="E11" s="63" t="str">
         <f>IF(Notenliste!D11&lt;&gt;0,Notenliste!$B$37," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="64" t="str">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="61" t="str">
         <f>IF(Notenliste!D12=0," ",Notenliste!D12)</f>
         <v xml:space="preserve"> </v>
       </c>
@@ -9047,17 +8507,17 @@
         <f>IF(Notenliste!D12&lt;&gt;0,IF(Notenliste!I12&lt;&gt;0,Notenliste!I12,Notenliste!$B$33)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D12" s="68" t="str">
+      <c r="D12" s="65" t="str">
         <f>IF(Notenliste!D12=0," ",IF(Notenliste!F12="KP"," ",IF(Notenliste!F12="NB","nicht bestanden",IF(OR(Notenliste!H12="x", Notenliste!H12="X"),"bestanden",Notenliste!F12))))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="E12" s="66" t="str">
+      <c r="E12" s="63" t="str">
         <f>IF(Notenliste!D12&lt;&gt;0,Notenliste!$B$37," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="64" t="str">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="61" t="str">
         <f>IF(Notenliste!D13=0," ",Notenliste!D13)</f>
         <v xml:space="preserve"> </v>
       </c>
@@ -9065,17 +8525,17 @@
         <f>IF(Notenliste!D13&lt;&gt;0,IF(Notenliste!I13&lt;&gt;0,Notenliste!I13,Notenliste!$B$33)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D13" s="68" t="str">
+      <c r="D13" s="65" t="str">
         <f>IF(Notenliste!D13=0," ",IF(Notenliste!F13="KP"," ",IF(Notenliste!F13="NB","nicht bestanden",IF(OR(Notenliste!H13="x", Notenliste!H13="X"),"bestanden",Notenliste!F13))))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="E13" s="66" t="str">
+      <c r="E13" s="63" t="str">
         <f>IF(Notenliste!D13&lt;&gt;0,Notenliste!$B$37," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="64" t="str">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="61" t="str">
         <f>IF(Notenliste!D14=0," ",Notenliste!D14)</f>
         <v xml:space="preserve"> </v>
       </c>
@@ -9083,17 +8543,17 @@
         <f>IF(Notenliste!D14&lt;&gt;0,IF(Notenliste!I14&lt;&gt;0,Notenliste!I14,Notenliste!$B$33)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D14" s="68" t="str">
+      <c r="D14" s="65" t="str">
         <f>IF(Notenliste!D14=0," ",IF(Notenliste!F14="KP"," ",IF(Notenliste!F14="NB","nicht bestanden",IF(OR(Notenliste!H14="x", Notenliste!H14="X"),"bestanden",Notenliste!F14))))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="E14" s="66" t="str">
+      <c r="E14" s="63" t="str">
         <f>IF(Notenliste!D14&lt;&gt;0,Notenliste!$B$37," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="64" t="str">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="61" t="str">
         <f>IF(Notenliste!D15=0," ",Notenliste!D15)</f>
         <v xml:space="preserve"> </v>
       </c>
@@ -9101,17 +8561,17 @@
         <f>IF(Notenliste!D15&lt;&gt;0,IF(Notenliste!I15&lt;&gt;0,Notenliste!I15,Notenliste!$B$33)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D15" s="68" t="str">
+      <c r="D15" s="65" t="str">
         <f>IF(Notenliste!D15=0," ",IF(Notenliste!F15="KP"," ",IF(Notenliste!F15="NB","nicht bestanden",IF(OR(Notenliste!H15="x", Notenliste!H15="X"),"bestanden",Notenliste!F15))))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="E15" s="66" t="str">
+      <c r="E15" s="63" t="str">
         <f>IF(Notenliste!D15&lt;&gt;0,Notenliste!$B$37," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="64" t="str">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="61" t="str">
         <f>IF(Notenliste!D16=0," ",Notenliste!D16)</f>
         <v xml:space="preserve"> </v>
       </c>
@@ -9119,17 +8579,17 @@
         <f>IF(Notenliste!D16&lt;&gt;0,IF(Notenliste!I16&lt;&gt;0,Notenliste!I16,Notenliste!$B$33)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D16" s="68" t="str">
+      <c r="D16" s="65" t="str">
         <f>IF(Notenliste!D16=0," ",IF(Notenliste!F16="KP"," ",IF(Notenliste!F16="NB","nicht bestanden",IF(OR(Notenliste!H16="x", Notenliste!H16="X"),"bestanden",Notenliste!F16))))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="E16" s="66" t="str">
+      <c r="E16" s="63" t="str">
         <f>IF(Notenliste!D16&lt;&gt;0,Notenliste!$B$37," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="64" t="str">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="61" t="str">
         <f>IF(Notenliste!D17=0," ",Notenliste!D17)</f>
         <v xml:space="preserve"> </v>
       </c>
@@ -9137,17 +8597,17 @@
         <f>IF(Notenliste!D17&lt;&gt;0,IF(Notenliste!I17&lt;&gt;0,Notenliste!I17,Notenliste!$B$33)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D17" s="68" t="str">
+      <c r="D17" s="65" t="str">
         <f>IF(Notenliste!D17=0," ",IF(Notenliste!F17="KP"," ",IF(Notenliste!F17="NB","nicht bestanden",IF(OR(Notenliste!H17="x", Notenliste!H17="X"),"bestanden",Notenliste!F17))))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="E17" s="66" t="str">
+      <c r="E17" s="63" t="str">
         <f>IF(Notenliste!D17&lt;&gt;0,Notenliste!$B$37," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="64" t="str">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="61" t="str">
         <f>IF(Notenliste!D18=0," ",Notenliste!D18)</f>
         <v xml:space="preserve"> </v>
       </c>
@@ -9155,17 +8615,17 @@
         <f>IF(Notenliste!D18&lt;&gt;0,IF(Notenliste!I18&lt;&gt;0,Notenliste!I18,Notenliste!$B$33)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D18" s="68" t="str">
+      <c r="D18" s="65" t="str">
         <f>IF(Notenliste!D18=0," ",IF(Notenliste!F18="KP"," ",IF(Notenliste!F18="NB","nicht bestanden",IF(OR(Notenliste!H18="x", Notenliste!H18="X"),"bestanden",Notenliste!F18))))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="E18" s="66" t="str">
+      <c r="E18" s="63" t="str">
         <f>IF(Notenliste!D18&lt;&gt;0,Notenliste!$B$37," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="64" t="str">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="61" t="str">
         <f>IF(Notenliste!D19=0," ",Notenliste!D19)</f>
         <v xml:space="preserve"> </v>
       </c>
@@ -9173,17 +8633,17 @@
         <f>IF(Notenliste!D19&lt;&gt;0,IF(Notenliste!I19&lt;&gt;0,Notenliste!I19,Notenliste!$B$33)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D19" s="68" t="str">
+      <c r="D19" s="65" t="str">
         <f>IF(Notenliste!D19=0," ",IF(Notenliste!F19="KP"," ",IF(Notenliste!F19="NB","nicht bestanden",IF(OR(Notenliste!H19="x", Notenliste!H19="X"),"bestanden",Notenliste!F19))))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="E19" s="66" t="str">
+      <c r="E19" s="63" t="str">
         <f>IF(Notenliste!D19&lt;&gt;0,Notenliste!$B$37," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="64" t="str">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="61" t="str">
         <f>IF(Notenliste!D20=0," ",Notenliste!D20)</f>
         <v xml:space="preserve"> </v>
       </c>
@@ -9191,17 +8651,17 @@
         <f>IF(Notenliste!D20&lt;&gt;0,IF(Notenliste!I20&lt;&gt;0,Notenliste!I20,Notenliste!$B$33)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D20" s="68" t="str">
+      <c r="D20" s="65" t="str">
         <f>IF(Notenliste!D20=0," ",IF(Notenliste!F20="KP"," ",IF(Notenliste!F20="NB","nicht bestanden",IF(OR(Notenliste!H20="x", Notenliste!H20="X"),"bestanden",Notenliste!F20))))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="E20" s="66" t="str">
+      <c r="E20" s="63" t="str">
         <f>IF(Notenliste!D20&lt;&gt;0,Notenliste!$B$37," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="64" t="str">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="61" t="str">
         <f>IF(Notenliste!D21=0," ",Notenliste!D21)</f>
         <v xml:space="preserve"> </v>
       </c>
@@ -9209,17 +8669,17 @@
         <f>IF(Notenliste!D21&lt;&gt;0,IF(Notenliste!I21&lt;&gt;0,Notenliste!I21,Notenliste!$B$33)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D21" s="68" t="str">
+      <c r="D21" s="65" t="str">
         <f>IF(Notenliste!D21=0," ",IF(Notenliste!F21="KP"," ",IF(Notenliste!F21="NB","nicht bestanden",IF(OR(Notenliste!H21="x", Notenliste!H21="X"),"bestanden",Notenliste!F21))))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="E21" s="66" t="str">
+      <c r="E21" s="63" t="str">
         <f>IF(Notenliste!D21&lt;&gt;0,Notenliste!$B$37," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="64" t="str">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="61" t="str">
         <f>IF(Notenliste!D22=0," ",Notenliste!D22)</f>
         <v xml:space="preserve"> </v>
       </c>
@@ -9227,17 +8687,17 @@
         <f>IF(Notenliste!D22&lt;&gt;0,IF(Notenliste!I22&lt;&gt;0,Notenliste!I22,Notenliste!$B$33)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D22" s="68" t="str">
+      <c r="D22" s="65" t="str">
         <f>IF(Notenliste!D22=0," ",IF(Notenliste!F22="KP"," ",IF(Notenliste!F22="NB","nicht bestanden",IF(OR(Notenliste!H22="x", Notenliste!H22="X"),"bestanden",Notenliste!F22))))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="E22" s="66" t="str">
+      <c r="E22" s="63" t="str">
         <f>IF(Notenliste!D22&lt;&gt;0,Notenliste!$B$37," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="64" t="str">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="61" t="str">
         <f>IF(Notenliste!D23=0," ",Notenliste!D23)</f>
         <v xml:space="preserve"> </v>
       </c>
@@ -9245,17 +8705,17 @@
         <f>IF(Notenliste!D23&lt;&gt;0,IF(Notenliste!I23&lt;&gt;0,Notenliste!I23,Notenliste!$B$33)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D23" s="68" t="str">
+      <c r="D23" s="65" t="str">
         <f>IF(Notenliste!D23=0," ",IF(Notenliste!F23="KP"," ",IF(Notenliste!F23="NB","nicht bestanden",IF(OR(Notenliste!H23="x", Notenliste!H23="X"),"bestanden",Notenliste!F23))))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="E23" s="66" t="str">
+      <c r="E23" s="63" t="str">
         <f>IF(Notenliste!D23&lt;&gt;0,Notenliste!$B$37," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="64" t="str">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="61" t="str">
         <f>IF(Notenliste!D24=0," ",Notenliste!D24)</f>
         <v xml:space="preserve"> </v>
       </c>
@@ -9263,17 +8723,17 @@
         <f>IF(Notenliste!D24&lt;&gt;0,IF(Notenliste!I24&lt;&gt;0,Notenliste!I24,Notenliste!$B$33)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D24" s="68" t="str">
+      <c r="D24" s="65" t="str">
         <f>IF(Notenliste!D24=0," ",IF(Notenliste!F24="KP"," ",IF(Notenliste!F24="NB","nicht bestanden",IF(OR(Notenliste!H24="x", Notenliste!H24="X"),"bestanden",Notenliste!F24))))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="E24" s="66" t="str">
+      <c r="E24" s="63" t="str">
         <f>IF(Notenliste!D24&lt;&gt;0,Notenliste!$B$37," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="64" t="str">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="61" t="str">
         <f>IF(Notenliste!D25=0," ",Notenliste!D25)</f>
         <v xml:space="preserve"> </v>
       </c>
@@ -9281,17 +8741,17 @@
         <f>IF(Notenliste!D25&lt;&gt;0,IF(Notenliste!I25&lt;&gt;0,Notenliste!I25,Notenliste!$B$33)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D25" s="68" t="str">
+      <c r="D25" s="65" t="str">
         <f>IF(Notenliste!D25=0," ",IF(Notenliste!F25="KP"," ",IF(Notenliste!F25="NB","nicht bestanden",IF(OR(Notenliste!H25="x", Notenliste!H25="X"),"bestanden",Notenliste!F25))))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="E25" s="66" t="str">
+      <c r="E25" s="63" t="str">
         <f>IF(Notenliste!D25&lt;&gt;0,Notenliste!$B$37," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="64" t="str">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="61" t="str">
         <f>IF(Notenliste!D26=0," ",Notenliste!D26)</f>
         <v xml:space="preserve"> </v>
       </c>
@@ -9299,11 +8759,11 @@
         <f>IF(Notenliste!D26&lt;&gt;0,IF(Notenliste!I26&lt;&gt;0,Notenliste!I26,Notenliste!$B$33)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D26" s="68" t="str">
+      <c r="D26" s="65" t="str">
         <f>IF(Notenliste!D26=0," ",IF(Notenliste!F26="KP"," ",IF(Notenliste!F26="NB","nicht bestanden",IF(OR(Notenliste!H26="x", Notenliste!H26="X"),"bestanden",Notenliste!F26))))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="E26" s="66" t="str">
+      <c r="E26" s="63" t="str">
         <f>IF(Notenliste!D26&lt;&gt;0,Notenliste!$B$37," ")</f>
         <v xml:space="preserve"> </v>
       </c>
@@ -9311,21 +8771,21 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" insertRows="0" deleteRows="0" sort="0" autoFilter="0"/>
   <dataValidations disablePrompts="1" count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1" xr:uid="{00000000-0002-0000-0600-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1">
       <formula1>Anmeldestatus</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{00000000-0002-0000-0600-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1">
       <formula1>Notenskala</formula1>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1 C27:C1048576" xr:uid="{00000000-0002-0000-0600-000002000000}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1 C27:C1048576">
       <formula1>0</formula1>
       <formula2>120</formula2>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1 E27:E1048576" xr:uid="{00000000-0002-0000-0600-000003000000}">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1 E27:E1048576">
       <formula1>41275</formula1>
       <formula2>73050</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1 A27:A1048576" xr:uid="{00000000-0002-0000-0600-000004000000}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1 A27:A1048576">
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
@@ -9343,255 +8803,255 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H18"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.44140625" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" customWidth="1"/>
-    <col min="5" max="5" width="2.6640625" customWidth="1"/>
-    <col min="6" max="6" width="25.6640625" customWidth="1"/>
-    <col min="7" max="7" width="2.44140625" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" style="20"/>
+    <col min="1" max="1" width="33.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" customWidth="1"/>
+    <col min="5" max="5" width="2.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="2.42578125" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="69" t="s">
+    <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="69" t="s">
+      <c r="B1" s="66" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="66" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="66" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1" s="67" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="73" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="76" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" s="77" t="s">
+        <v>63</v>
+      </c>
+      <c r="F2" s="77" t="s">
+        <v>59</v>
+      </c>
+      <c r="H2" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="69" t="s">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="74" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="F1" s="69" t="s">
+      <c r="F3" s="68" t="s">
+        <v>75</v>
+      </c>
+      <c r="H3" s="69" t="s">
         <v>66</v>
       </c>
-      <c r="H1" s="70" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="76" t="s">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="74" t="s">
+        <v>93</v>
+      </c>
+      <c r="B4" s="75" t="s">
+        <v>94</v>
+      </c>
+      <c r="D4" s="68" t="s">
+        <v>67</v>
+      </c>
+      <c r="F4" s="68" t="s">
+        <v>76</v>
+      </c>
+      <c r="H4" s="69"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="74" t="s">
+        <v>95</v>
+      </c>
+      <c r="B5" s="75" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="68" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" s="68" t="s">
+        <v>77</v>
+      </c>
+      <c r="H5" s="70"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="74" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="75" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="F6" s="68" t="s">
+        <v>119</v>
+      </c>
+      <c r="H6" s="70"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="74" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="75" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="68" t="s">
+        <v>70</v>
+      </c>
+      <c r="F7" s="68" t="s">
+        <v>78</v>
+      </c>
+      <c r="H7" s="70"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="75" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="79" t="s">
-        <v>61</v>
-      </c>
-      <c r="D2" s="80" t="s">
-        <v>67</v>
-      </c>
-      <c r="F2" s="80" t="s">
-        <v>63</v>
-      </c>
-      <c r="H2" s="72" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="77" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" s="78" t="s">
-        <v>43</v>
-      </c>
-      <c r="D3" s="71" t="s">
-        <v>69</v>
-      </c>
-      <c r="F3" s="71" t="s">
+      <c r="B8" s="75" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="68" t="s">
+        <v>91</v>
+      </c>
+      <c r="F8" s="68" t="s">
         <v>79</v>
       </c>
-      <c r="H3" s="72" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="77" t="s">
-        <v>97</v>
-      </c>
-      <c r="B4" s="78" t="s">
-        <v>98</v>
-      </c>
-      <c r="D4" s="71" t="s">
+      <c r="H8" s="70"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="68" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="68" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="68" t="s">
+        <v>92</v>
+      </c>
+      <c r="F9" s="68" t="s">
+        <v>90</v>
+      </c>
+      <c r="H9" s="70"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="68"/>
+      <c r="B10" s="68"/>
+      <c r="D10" s="68" t="s">
         <v>71</v>
       </c>
-      <c r="F4" s="71" t="s">
+      <c r="F10" s="68" t="s">
         <v>80</v>
       </c>
-      <c r="H4" s="72"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="77" t="s">
-        <v>99</v>
-      </c>
-      <c r="B5" s="78" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="71" t="s">
+      <c r="H10" s="70"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="68"/>
+      <c r="B11" s="68"/>
+      <c r="D11" s="68" t="s">
         <v>72</v>
       </c>
-      <c r="F5" s="71" t="s">
+      <c r="F11" s="68" t="s">
         <v>81</v>
       </c>
-      <c r="H5" s="73"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="77" t="s">
-        <v>51</v>
-      </c>
-      <c r="B6" s="78" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" s="71" t="s">
-        <v>73</v>
-      </c>
-      <c r="F6" s="71" t="s">
-        <v>123</v>
-      </c>
-      <c r="H6" s="73"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="77" t="s">
-        <v>42</v>
-      </c>
-      <c r="B7" s="78" t="s">
-        <v>47</v>
-      </c>
-      <c r="D7" s="71" t="s">
-        <v>74</v>
-      </c>
-      <c r="F7" s="71" t="s">
+      <c r="H11" s="70"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="68"/>
+      <c r="B12" s="68"/>
+      <c r="D12" s="68" t="s">
+        <v>86</v>
+      </c>
+      <c r="F12" s="68" t="s">
         <v>82</v>
       </c>
-      <c r="H7" s="73"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="78" t="s">
-        <v>53</v>
-      </c>
-      <c r="B8" s="78" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" s="71" t="s">
-        <v>95</v>
-      </c>
-      <c r="F8" s="71" t="s">
+      <c r="H12" s="70"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="68"/>
+      <c r="B13" s="68"/>
+      <c r="D13" s="68" t="s">
+        <v>87</v>
+      </c>
+      <c r="F13" s="68" t="s">
         <v>83</v>
       </c>
-      <c r="H8" s="73"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="71" t="s">
-        <v>52</v>
-      </c>
-      <c r="B9" s="71" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" s="71" t="s">
-        <v>96</v>
-      </c>
-      <c r="F9" s="71" t="s">
-        <v>94</v>
-      </c>
-      <c r="H9" s="73"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="71"/>
-      <c r="B10" s="71"/>
-      <c r="D10" s="71" t="s">
-        <v>75</v>
-      </c>
-      <c r="F10" s="71" t="s">
+      <c r="H13" s="70"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="68"/>
+      <c r="B14" s="68"/>
+      <c r="D14" s="68" t="s">
+        <v>88</v>
+      </c>
+      <c r="F14" s="68" t="s">
+        <v>109</v>
+      </c>
+      <c r="H14" s="70"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="68"/>
+      <c r="B15" s="68"/>
+      <c r="D15" s="68" t="s">
+        <v>58</v>
+      </c>
+      <c r="F15" s="68" t="s">
         <v>84</v>
       </c>
-      <c r="H10" s="73"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="71"/>
-      <c r="B11" s="71"/>
-      <c r="D11" s="71" t="s">
-        <v>76</v>
-      </c>
-      <c r="F11" s="71" t="s">
+      <c r="H15" s="70"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="68"/>
+      <c r="B16" s="68"/>
+      <c r="D16" s="68" t="s">
+        <v>89</v>
+      </c>
+      <c r="F16" s="68" t="s">
         <v>85</v>
       </c>
-      <c r="H11" s="73"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="71"/>
-      <c r="B12" s="71"/>
-      <c r="D12" s="71" t="s">
-        <v>90</v>
-      </c>
-      <c r="F12" s="71" t="s">
-        <v>86</v>
-      </c>
-      <c r="H12" s="73"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="71"/>
-      <c r="B13" s="71"/>
-      <c r="D13" s="71" t="s">
-        <v>91</v>
-      </c>
-      <c r="F13" s="71" t="s">
-        <v>87</v>
-      </c>
-      <c r="H13" s="73"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="71"/>
-      <c r="B14" s="71"/>
-      <c r="D14" s="71" t="s">
-        <v>92</v>
-      </c>
-      <c r="F14" s="71" t="s">
-        <v>113</v>
-      </c>
-      <c r="H14" s="73"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="71"/>
-      <c r="B15" s="71"/>
-      <c r="D15" s="71" t="s">
-        <v>62</v>
-      </c>
-      <c r="F15" s="71" t="s">
-        <v>88</v>
-      </c>
-      <c r="H15" s="73"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="71"/>
-      <c r="B16" s="71"/>
-      <c r="D16" s="71" t="s">
-        <v>93</v>
-      </c>
-      <c r="F16" s="71" t="s">
-        <v>89</v>
-      </c>
-      <c r="H16" s="73"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="71"/>
-      <c r="B17" s="71"/>
-      <c r="D17" s="71"/>
-      <c r="F17" s="71" t="s">
-        <v>112</v>
-      </c>
-      <c r="H17" s="73"/>
-    </row>
-    <row r="18" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="74"/>
-      <c r="B18" s="74"/>
-      <c r="D18" s="74"/>
-      <c r="F18" s="74" t="s">
-        <v>124</v>
-      </c>
-      <c r="H18" s="75"/>
+      <c r="H16" s="70"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="68"/>
+      <c r="B17" s="68"/>
+      <c r="D17" s="68"/>
+      <c r="F17" s="68" t="s">
+        <v>108</v>
+      </c>
+      <c r="H17" s="70"/>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="71"/>
+      <c r="B18" s="71"/>
+      <c r="D18" s="71"/>
+      <c r="F18" s="71" t="s">
+        <v>120</v>
+      </c>
+      <c r="H18" s="72"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
